--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -6001,7 +6001,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6011,19 +6011,19 @@
         <v>31.63</v>
       </c>
       <c r="D66" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="E66" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0007</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I66" t="n">
         <v>31.46</v>
@@ -6087,25 +6087,25 @@
         </is>
       </c>
       <c r="I67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.6</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.6</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.62</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.62</v>
       </c>
       <c r="N67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.62</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>31.63</v>
+        <v>31.64</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,72 +641,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="K2" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="L2" t="n">
         <v>31.52</v>
       </c>
-      <c r="C2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K2" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>31.58</v>
       </c>
-      <c r="M2" t="n">
-        <v>31.68</v>
-      </c>
       <c r="N2" t="n">
-        <v>31.78</v>
+        <v>31.64</v>
       </c>
       <c r="O2" t="n">
-        <v>31.75</v>
+        <v>31.73</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -718,59 +716,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.56</v>
+        <v>31.64</v>
       </c>
       <c r="C3" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="D3" t="n">
         <v>31.53</v>
       </c>
       <c r="E3" t="n">
-        <v>31.56</v>
+        <v>31.64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>31.33</v>
+        <v>31.45</v>
       </c>
       <c r="J3" t="n">
-        <v>31.38</v>
+        <v>31.48</v>
       </c>
       <c r="K3" t="n">
-        <v>31.45</v>
+        <v>31.52</v>
       </c>
       <c r="L3" t="n">
-        <v>31.52</v>
+        <v>31.57</v>
       </c>
       <c r="M3" t="n">
-        <v>31.58</v>
+        <v>31.6</v>
       </c>
       <c r="N3" t="n">
         <v>31.64</v>
       </c>
       <c r="O3" t="n">
-        <v>31.73</v>
+        <v>31.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -781,18 +775,20 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -807,50 +803,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>31.64</v>
       </c>
       <c r="C4" t="n">
-        <v>31.65</v>
+        <v>31.7</v>
       </c>
       <c r="D4" t="n">
-        <v>31.53</v>
+        <v>31.58</v>
       </c>
       <c r="E4" t="n">
         <v>31.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0001</v>
       </c>
       <c r="H4" t="n">
         <v>0.12</v>
       </c>
       <c r="I4" t="n">
-        <v>31.45</v>
+        <v>31.42</v>
       </c>
       <c r="J4" t="n">
-        <v>31.48</v>
+        <v>31.54</v>
       </c>
       <c r="K4" t="n">
-        <v>31.52</v>
+        <v>31.58</v>
       </c>
       <c r="L4" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="M4" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="N4" t="n">
-        <v>31.64</v>
+        <v>31.78</v>
       </c>
       <c r="O4" t="n">
-        <v>31.7</v>
+        <v>31.77</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,12 +854,14 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -871,10 +869,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -884,16 +880,20 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="C5" t="n">
         <v>31.7</v>
@@ -902,37 +902,37 @@
         <v>31.58</v>
       </c>
       <c r="E5" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H5" t="n">
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>31.42</v>
+        <v>31.46</v>
       </c>
       <c r="J5" t="n">
-        <v>31.54</v>
+        <v>31.52</v>
       </c>
       <c r="K5" t="n">
         <v>31.58</v>
       </c>
       <c r="L5" t="n">
-        <v>31.62</v>
+        <v>31.64</v>
       </c>
       <c r="M5" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="N5" t="n">
-        <v>31.78</v>
+        <v>31.75</v>
       </c>
       <c r="O5" t="n">
-        <v>31.77</v>
+        <v>31.81</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,19 +940,17 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -966,78 +964,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="C6" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="D6" t="n">
         <v>31.58</v>
       </c>
       <c r="E6" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>31.46</v>
+        <v>31.47</v>
       </c>
       <c r="J6" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="K6" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="L6" t="n">
-        <v>31.64</v>
+        <v>31.67</v>
       </c>
       <c r="M6" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N6" t="n">
-        <v>31.75</v>
+        <v>31.85</v>
       </c>
       <c r="O6" t="n">
-        <v>31.81</v>
+        <v>31.82</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1050,76 +1046,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C7" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D7" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E7" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I7" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J7" t="n">
         <v>31.61</v>
       </c>
       <c r="K7" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L7" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M7" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N7" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O7" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1132,59 +1130,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L8" t="n">
         <v>31.7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="M8" t="n">
         <v>31.77</v>
       </c>
-      <c r="D8" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E8" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K8" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L8" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N8" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O8" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,18 +1189,20 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1221,50 +1217,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C9" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D9" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E9" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F9" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H9" t="n">
         <v>0.11</v>
       </c>
       <c r="I9" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J9" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K9" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L9" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M9" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N9" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O9" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,20 +1271,18 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1303,50 +1297,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C10" t="n">
         <v>31.91</v>
       </c>
       <c r="D10" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E10" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J10" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K10" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L10" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M10" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N10" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O10" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,13 +1353,11 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1378,37 +1370,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C11" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D11" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E11" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J11" t="n">
         <v>31.75</v>
@@ -1420,13 +1416,13 @@
         <v>31.85</v>
       </c>
       <c r="M11" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N11" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O11" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,16 +1430,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,57 +1458,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C12" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D12" t="n">
         <v>31.79</v>
       </c>
       <c r="E12" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I12" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J12" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K12" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L12" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M12" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N12" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O12" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1551,50 +1551,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C13" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D13" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E13" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H13" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I13" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J13" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K13" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L13" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M13" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N13" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,21 +1602,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1628,59 +1626,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C14" t="n">
         <v>31.96</v>
       </c>
       <c r="D14" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E14" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I14" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L14" t="n">
         <v>31.89</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I14" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J14" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K14" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L14" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M14" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N14" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O14" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,7 +1685,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1717,50 +1711,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>31.93</v>
       </c>
       <c r="C15" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D15" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E15" t="n">
         <v>31.93</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I15" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J15" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K15" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L15" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M15" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N15" t="n">
         <v>32.03</v>
       </c>
       <c r="O15" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,76 +1765,84 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C16" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D16" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H16" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J16" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K16" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L16" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M16" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N16" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O16" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,14 +1853,14 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -1866,69 +1868,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C17" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E17" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F17" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H17" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I17" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J17" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K17" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L17" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M17" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N17" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O17" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,10 +1932,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1949,10 +1947,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1962,55 +1958,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C18" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D18" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E18" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H18" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I18" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J18" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K18" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L18" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M18" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N18" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O18" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,20 +2018,16 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2053,47 +2049,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C19" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D19" t="n">
         <v>32.04</v>
       </c>
       <c r="E19" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H19" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J19" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K19" t="n">
         <v>32.02</v>
       </c>
       <c r="L19" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M19" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N19" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O19" t="n">
         <v>32.41</v>
@@ -2109,7 +2105,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2128,57 +2124,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>32.1</v>
       </c>
       <c r="C20" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D20" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E20" t="n">
         <v>32.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H20" t="n">
         <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J20" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K20" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L20" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M20" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N20" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O20" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,13 +2185,15 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2210,42 +2208,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C21" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D21" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E21" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I21" t="n">
         <v>31.9</v>
       </c>
       <c r="J21" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K21" t="n">
         <v>32.03</v>
@@ -2260,7 +2258,7 @@
         <v>32.23</v>
       </c>
       <c r="O21" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,12 +2271,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2292,59 +2290,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C22" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D22" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E22" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I22" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J22" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K22" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L22" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M22" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N22" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O22" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2357,13 +2351,11 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2376,55 +2368,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C23" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D23" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E23" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H23" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I23" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J23" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K23" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L23" t="n">
         <v>32.15</v>
       </c>
       <c r="M23" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N23" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O23" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,14 +2433,18 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2454,59 +2454,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C24" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D24" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E24" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I24" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J24" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K24" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L24" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M24" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N24" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O24" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,7 +2513,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2545,50 +2541,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C25" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D25" t="n">
         <v>32.26</v>
       </c>
-      <c r="C25" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D25" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E25" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F25" t="n">
         <v>0.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H25" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I25" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J25" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K25" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L25" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M25" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N25" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O25" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2599,14 +2595,14 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
@@ -2627,50 +2623,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C26" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D26" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E26" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H26" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J26" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K26" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L26" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M26" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N26" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O26" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2678,23 +2674,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2704,34 +2698,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D27" t="n">
         <v>32.28</v>
       </c>
-      <c r="C27" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D27" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E27" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H27" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I27" t="n">
         <v>32.09</v>
@@ -2740,19 +2738,19 @@
         <v>32.12</v>
       </c>
       <c r="K27" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L27" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M27" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N27" t="n">
         <v>32.4</v>
       </c>
-      <c r="N27" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O27" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,21 +2758,23 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2784,59 +2784,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C28" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D28" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E28" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F28" t="n">
         <v>0.05</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I28" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J28" t="n">
         <v>32.09</v>
       </c>
-      <c r="J28" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K28" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L28" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M28" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N28" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O28" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2847,20 +2843,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2870,55 +2862,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C29" t="n">
         <v>32.38</v>
       </c>
       <c r="D29" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E29" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H29" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I29" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J29" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K29" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L29" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M29" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N29" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O29" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2926,12 +2922,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2950,57 +2948,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C30" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D30" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E30" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I30" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J30" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K30" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L30" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M30" t="n">
         <v>32.34</v>
       </c>
-      <c r="M30" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N30" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O30" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3008,21 +3006,23 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3041,50 +3041,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C31" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D31" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E31" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I31" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J31" t="n">
         <v>32.19</v>
       </c>
       <c r="K31" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L31" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M31" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N31" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O31" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3105,10 +3105,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3127,50 +3125,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C32" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D32" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E32" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I32" t="n">
         <v>32.16</v>
       </c>
       <c r="J32" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K32" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L32" t="n">
         <v>32.33</v>
       </c>
       <c r="M32" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N32" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O32" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,16 +3181,18 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3202,59 +3202,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C33" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D33" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E33" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H33" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I33" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J33" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K33" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L33" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M33" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N33" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O33" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3267,12 +3263,12 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
@@ -3288,55 +3284,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C34" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D34" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E34" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H34" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I34" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J34" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K34" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L34" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M34" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N34" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O34" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3344,12 +3344,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3357,10 +3359,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3379,50 +3379,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C35" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D35" t="n">
         <v>32.21</v>
       </c>
       <c r="E35" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H35" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I35" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J35" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K35" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L35" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M35" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N35" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O35" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3432,18 +3432,16 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3458,57 +3456,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C36" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D36" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E36" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H36" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I36" t="n">
         <v>31.93</v>
       </c>
       <c r="J36" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K36" t="n">
         <v>32.15</v>
       </c>
-      <c r="K36" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L36" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M36" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N36" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O36" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3516,18 +3514,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3549,69 +3547,73 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>32.4</v>
       </c>
       <c r="C37" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D37" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E37" t="n">
         <v>32.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I37" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J37" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K37" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L37" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M37" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N37" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O37" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>32.57</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3626,62 +3628,60 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C38" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D38" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E38" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F38" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H38" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I38" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J38" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K38" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L38" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M38" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N38" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O38" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3714,57 +3714,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C39" t="n">
         <v>32.31</v>
       </c>
       <c r="D39" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E39" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H39" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I39" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J39" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K39" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L39" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M39" t="n">
         <v>32.33</v>
       </c>
-      <c r="M39" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N39" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O39" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3779,7 +3779,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3807,67 +3807,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C40" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D40" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E40" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H40" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J40" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K40" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L40" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M40" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N40" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O40" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3886,57 +3882,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C41" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D41" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E41" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H41" t="n">
         <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J41" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K41" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L41" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M41" t="n">
         <v>32.29</v>
       </c>
       <c r="N41" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O41" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3949,11 +3945,13 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3975,35 +3973,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C42" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D42" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E42" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I42" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J42" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K42" t="n">
         <v>32.18</v>
@@ -4012,13 +4010,13 @@
         <v>32.23</v>
       </c>
       <c r="M42" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N42" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O42" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4026,18 +4024,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4052,70 +4050,74 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C43" t="n">
         <v>32.21</v>
       </c>
-      <c r="C43" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D43" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E43" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H43" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J43" t="n">
         <v>32.12</v>
       </c>
       <c r="K43" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L43" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M43" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N43" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O43" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4143,50 +4145,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C44" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D44" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E44" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H44" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I44" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J44" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K44" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L44" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M44" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N44" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O44" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -4200,12 +4202,12 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4231,67 +4233,65 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C45" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D45" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E45" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H45" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J45" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K45" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L45" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M45" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N45" t="n">
         <v>32.38</v>
       </c>
       <c r="O45" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4319,65 +4319,65 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C46" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D46" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E46" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H46" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I46" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J46" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K46" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L46" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M46" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N46" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O46" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4398,78 +4398,76 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C47" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D47" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E47" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H47" t="n">
         <v>0.17</v>
       </c>
       <c r="I47" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J47" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K47" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L47" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M47" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N47" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O47" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4482,59 +4480,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C48" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D48" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E48" t="n">
         <v>31.82</v>
       </c>
-      <c r="E48" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F48" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H48" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I48" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J48" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K48" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L48" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M48" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N48" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O48" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4542,18 +4536,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4566,55 +4560,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C49" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D49" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E49" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I49" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J49" t="n">
         <v>31.65</v>
       </c>
-      <c r="J49" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K49" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L49" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M49" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N49" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O49" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,18 +4620,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4648,57 +4646,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C50" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D50" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E50" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H50" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I50" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J50" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K50" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L50" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M50" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N50" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O50" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,18 +4704,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4732,57 +4730,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C51" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D51" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E51" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H51" t="n">
         <v>0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J51" t="n">
         <v>31.72</v>
       </c>
       <c r="K51" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L51" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M51" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N51" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O51" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4790,18 +4788,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4816,57 +4814,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C52" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D52" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E52" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I52" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J52" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K52" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L52" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M52" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N52" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O52" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,7 +4877,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4900,76 +4898,80 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J53" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K53" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L53" t="n">
         <v>31.84</v>
       </c>
-      <c r="C53" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D53" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E53" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I53" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J53" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K53" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L53" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M53" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N53" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O53" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>31.99</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4984,74 +4986,72 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C54" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D54" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E54" t="n">
         <v>31.66</v>
       </c>
-      <c r="E54" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F54" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H54" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I54" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J54" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K54" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L54" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M54" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N54" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O54" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5065,85 +5065,79 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C55" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D55" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E55" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H55" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I55" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J55" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K55" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L55" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M55" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N55" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O55" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5156,55 +5150,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C56" t="n">
         <v>31.73</v>
       </c>
       <c r="D56" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E56" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I56" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J56" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K56" t="n">
         <v>31.57</v>
       </c>
-      <c r="K56" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L56" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M56" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N56" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O56" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5217,16 +5215,18 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5238,57 +5238,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C57" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D57" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E57" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H57" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I57" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J57" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K57" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L57" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M57" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N57" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O57" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5299,20 +5299,18 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5324,57 +5322,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C58" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D58" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E58" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H58" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I58" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J58" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K58" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L58" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M58" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N58" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O58" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5385,14 +5383,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5408,76 +5406,78 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C59" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D59" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E59" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J59" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K59" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L59" t="n">
         <v>31.72</v>
       </c>
-      <c r="C59" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D59" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E59" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I59" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J59" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K59" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L59" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M59" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N59" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O59" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5490,59 +5490,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C60" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D60" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E60" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H60" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I60" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J60" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K60" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L60" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M60" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N60" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O60" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5554,12 +5550,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5581,65 +5577,65 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C61" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D61" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J61" t="n">
         <v>31.49</v>
       </c>
-      <c r="E61" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I61" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J61" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K61" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L61" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M61" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N61" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O61" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5663,58 +5659,56 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>31.5</v>
       </c>
       <c r="C62" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D62" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E62" t="n">
         <v>31.5</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H62" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I62" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J62" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K62" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L62" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M62" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N62" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O62" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q62" s="6" t="n">
+        <v/>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
@@ -5723,7 +5717,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5745,50 +5739,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C63" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D63" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E63" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H63" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I63" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J63" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K63" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L63" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M63" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N63" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O63" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5798,77 +5792,87 @@
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C64" t="n">
         <v>31.69</v>
       </c>
       <c r="D64" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E64" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H64" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I64" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J64" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K64" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L64" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M64" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N64" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O64" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5876,30 +5880,26 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="11" t="inlineStr">
         <is>
@@ -5915,50 +5915,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C65" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D65" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E65" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I65" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K65" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L65" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M65" t="n">
         <v>31.69</v>
       </c>
-      <c r="D65" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E65" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I65" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J65" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K65" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L65" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M65" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N65" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O65" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5969,23 +5969,25 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="10" t="inlineStr">
+      <c r="S65" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W65" s="11" t="inlineStr">
         <is>
@@ -5994,118 +5996,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="C66" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="D66" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="E66" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="F66" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I66" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="J66" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K66" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="L66" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="M66" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="N66" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="O66" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="P66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W66" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I67" s="13" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="K67" s="13" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L67" s="13" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M67" s="13" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="O67" s="13" t="n">
-        <v>31.64</v>
+      <c r="I66" s="13" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>32.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.56</v>
+        <v>31.64</v>
       </c>
       <c r="C2" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="D2" t="n">
         <v>31.53</v>
       </c>
       <c r="E2" t="n">
-        <v>31.56</v>
+        <v>31.64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="I2" t="n">
-        <v>31.33</v>
+        <v>31.45</v>
       </c>
       <c r="J2" t="n">
-        <v>31.38</v>
+        <v>31.48</v>
       </c>
       <c r="K2" t="n">
-        <v>31.45</v>
+        <v>31.52</v>
       </c>
       <c r="L2" t="n">
-        <v>31.52</v>
+        <v>31.57</v>
       </c>
       <c r="M2" t="n">
-        <v>31.58</v>
+        <v>31.6</v>
       </c>
       <c r="N2" t="n">
         <v>31.64</v>
       </c>
       <c r="O2" t="n">
-        <v>31.73</v>
+        <v>31.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,11 +705,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -721,50 +726,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>31.64</v>
       </c>
       <c r="C3" t="n">
-        <v>31.65</v>
+        <v>31.7</v>
       </c>
       <c r="D3" t="n">
-        <v>31.53</v>
+        <v>31.58</v>
       </c>
       <c r="E3" t="n">
         <v>31.64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0001</v>
       </c>
       <c r="H3" t="n">
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>31.45</v>
+        <v>31.42</v>
       </c>
       <c r="J3" t="n">
-        <v>31.48</v>
+        <v>31.54</v>
       </c>
       <c r="K3" t="n">
-        <v>31.52</v>
+        <v>31.58</v>
       </c>
       <c r="L3" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="M3" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="N3" t="n">
-        <v>31.64</v>
+        <v>31.78</v>
       </c>
       <c r="O3" t="n">
-        <v>31.7</v>
+        <v>31.77</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,12 +777,14 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -785,10 +792,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -798,16 +803,20 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="C4" t="n">
         <v>31.7</v>
@@ -816,37 +825,37 @@
         <v>31.58</v>
       </c>
       <c r="E4" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H4" t="n">
         <v>0.12</v>
       </c>
       <c r="I4" t="n">
-        <v>31.42</v>
+        <v>31.46</v>
       </c>
       <c r="J4" t="n">
-        <v>31.54</v>
+        <v>31.52</v>
       </c>
       <c r="K4" t="n">
         <v>31.58</v>
       </c>
       <c r="L4" t="n">
-        <v>31.62</v>
+        <v>31.64</v>
       </c>
       <c r="M4" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="N4" t="n">
-        <v>31.78</v>
+        <v>31.75</v>
       </c>
       <c r="O4" t="n">
-        <v>31.77</v>
+        <v>31.81</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,19 +863,17 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -880,78 +887,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="C5" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="D5" t="n">
         <v>31.58</v>
       </c>
       <c r="E5" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>31.46</v>
+        <v>31.47</v>
       </c>
       <c r="J5" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="K5" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="L5" t="n">
-        <v>31.64</v>
+        <v>31.67</v>
       </c>
       <c r="M5" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N5" t="n">
-        <v>31.75</v>
+        <v>31.85</v>
       </c>
       <c r="O5" t="n">
-        <v>31.81</v>
+        <v>31.82</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -964,76 +969,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C6" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D6" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E6" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J6" t="n">
         <v>31.61</v>
       </c>
       <c r="K6" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L6" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M6" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N6" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O6" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1046,59 +1053,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E7" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L7" t="n">
         <v>31.7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="M7" t="n">
         <v>31.77</v>
       </c>
-      <c r="D7" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E7" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I7" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K7" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L7" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M7" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N7" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O7" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1116,11 +1119,13 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1135,50 +1140,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D8" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E8" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F8" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H8" t="n">
         <v>0.11</v>
       </c>
       <c r="I8" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J8" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K8" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L8" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M8" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N8" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O8" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1196,13 +1201,11 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1217,50 +1220,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C9" t="n">
         <v>31.91</v>
       </c>
       <c r="D9" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E9" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I9" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J9" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K9" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L9" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M9" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N9" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O9" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,15 +1274,13 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1292,37 +1293,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C10" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D10" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E10" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J10" t="n">
         <v>31.75</v>
@@ -1334,13 +1339,13 @@
         <v>31.85</v>
       </c>
       <c r="M10" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N10" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O10" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,16 +1353,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1372,57 +1381,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C11" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D11" t="n">
         <v>31.79</v>
       </c>
       <c r="E11" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I11" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J11" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K11" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L11" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M11" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N11" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O11" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,12 +1441,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1465,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C12" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D12" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E12" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I12" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J12" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K12" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L12" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M12" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N12" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,21 +1525,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1542,59 +1549,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C13" t="n">
         <v>31.96</v>
       </c>
       <c r="D13" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E13" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K13" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L13" t="n">
         <v>31.89</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I13" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L13" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M13" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N13" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O13" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1631,50 +1634,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>31.93</v>
       </c>
       <c r="C14" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D14" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E14" t="n">
         <v>31.93</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I14" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J14" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K14" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L14" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M14" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N14" t="n">
         <v>32.03</v>
       </c>
       <c r="O14" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,74 +1690,82 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C15" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D15" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H15" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J15" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K15" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L15" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M15" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N15" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O15" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,12 +1778,12 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -1780,69 +1791,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C16" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E16" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F16" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H16" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I16" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J16" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K16" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L16" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M16" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N16" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O16" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1850,8 +1855,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -1863,10 +1870,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1876,55 +1881,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C17" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D17" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E17" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H17" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I17" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J17" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K17" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L17" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M17" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N17" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O17" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1932,20 +1941,16 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1967,47 +1972,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C18" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D18" t="n">
         <v>32.04</v>
       </c>
       <c r="E18" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H18" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J18" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K18" t="n">
         <v>32.02</v>
       </c>
       <c r="L18" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M18" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O18" t="n">
         <v>32.41</v>
@@ -2021,9 +2026,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2042,57 +2047,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>32.1</v>
       </c>
       <c r="C19" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D19" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E19" t="n">
         <v>32.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H19" t="n">
         <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J19" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K19" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L19" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M19" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N19" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O19" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,8 +2113,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2124,42 +2131,42 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C20" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D20" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E20" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="n">
         <v>31.9</v>
       </c>
       <c r="J20" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K20" t="n">
         <v>32.03</v>
@@ -2174,7 +2181,7 @@
         <v>32.23</v>
       </c>
       <c r="O20" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,14 +2192,14 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2206,59 +2213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C21" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D21" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E21" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H21" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I21" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J21" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K21" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L21" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M21" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N21" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O21" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,15 +2272,13 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2290,55 +2291,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C22" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D22" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E22" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H22" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J22" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K22" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L22" t="n">
         <v>32.15</v>
       </c>
       <c r="M22" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N22" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O22" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,16 +2354,20 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2368,59 +2377,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C23" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D23" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E23" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I23" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J23" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K23" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L23" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M23" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N23" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2459,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D24" t="n">
         <v>32.26</v>
       </c>
-      <c r="C24" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D24" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E24" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F24" t="n">
         <v>0.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H24" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I24" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J24" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K24" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L24" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M24" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N24" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O24" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,12 +2520,12 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -2541,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C25" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D25" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E25" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J25" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K25" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L25" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M25" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N25" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O25" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2592,23 +2597,21 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2618,34 +2621,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C26" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D26" t="n">
         <v>32.28</v>
       </c>
-      <c r="C26" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D26" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E26" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H26" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I26" t="n">
         <v>32.09</v>
@@ -2654,19 +2661,19 @@
         <v>32.12</v>
       </c>
       <c r="K26" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L26" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M26" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N26" t="n">
         <v>32.4</v>
       </c>
-      <c r="N26" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O26" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2674,21 +2681,23 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2698,59 +2707,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C27" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D27" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E27" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F27" t="n">
         <v>0.05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I27" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J27" t="n">
         <v>32.09</v>
       </c>
-      <c r="J27" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K27" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L27" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M27" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N27" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O27" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2763,18 +2768,14 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2784,55 +2785,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C28" t="n">
         <v>32.38</v>
       </c>
       <c r="D28" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E28" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H28" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I28" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J28" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K28" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L28" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M28" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N28" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O28" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2840,12 +2845,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2864,57 +2871,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C29" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D29" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E29" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I29" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J29" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K29" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L29" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M29" t="n">
         <v>32.34</v>
       </c>
-      <c r="M29" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N29" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O29" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2922,21 +2929,23 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2955,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C30" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D30" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E30" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I30" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J30" t="n">
         <v>32.19</v>
       </c>
       <c r="K30" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L30" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M30" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N30" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O30" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3009,9 +3018,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3019,10 +3028,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3041,50 +3048,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C31" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D31" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E31" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H31" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I31" t="n">
         <v>32.16</v>
       </c>
       <c r="J31" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K31" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L31" t="n">
         <v>32.33</v>
       </c>
       <c r="M31" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N31" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O31" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3095,18 +3102,20 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3116,59 +3125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C32" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D32" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E32" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H32" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I32" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J32" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K32" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L32" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M32" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N32" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O32" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3179,14 +3184,14 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -3202,55 +3207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C33" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D33" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E33" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H33" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I33" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J33" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K33" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L33" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M33" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N33" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O33" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3258,12 +3267,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3271,10 +3282,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3293,50 +3302,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C34" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D34" t="n">
         <v>32.21</v>
       </c>
       <c r="E34" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H34" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I34" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J34" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K34" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L34" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M34" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N34" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O34" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3346,18 +3355,16 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3372,57 +3379,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C35" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D35" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E35" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H35" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I35" t="n">
         <v>31.93</v>
       </c>
       <c r="J35" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K35" t="n">
         <v>32.15</v>
       </c>
-      <c r="K35" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L35" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M35" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N35" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O35" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3430,18 +3437,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3463,69 +3470,73 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>32.4</v>
       </c>
       <c r="C36" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D36" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E36" t="n">
         <v>32.4</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I36" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J36" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K36" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L36" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M36" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N36" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O36" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3540,62 +3551,60 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C37" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D37" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E37" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F37" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H37" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I37" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J37" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K37" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L37" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M37" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N37" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O37" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
@@ -3604,12 +3613,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3628,57 +3637,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C38" t="n">
         <v>32.31</v>
       </c>
       <c r="D38" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E38" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H38" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I38" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J38" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K38" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L38" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M38" t="n">
         <v>32.33</v>
       </c>
-      <c r="M38" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N38" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O38" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3721,67 +3730,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C39" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D39" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E39" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H39" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J39" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K39" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L39" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M39" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N39" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O39" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3800,57 +3805,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C40" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D40" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E40" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H40" t="n">
         <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J40" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K40" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L40" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M40" t="n">
         <v>32.29</v>
       </c>
       <c r="N40" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O40" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3861,13 +3866,15 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3889,35 +3896,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C41" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D41" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E41" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I41" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J41" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K41" t="n">
         <v>32.18</v>
@@ -3926,13 +3933,13 @@
         <v>32.23</v>
       </c>
       <c r="M41" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N41" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O41" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3940,18 +3947,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3966,63 +3973,67 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C42" t="n">
         <v>32.21</v>
       </c>
-      <c r="C42" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D42" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E42" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J42" t="n">
         <v>32.12</v>
       </c>
       <c r="K42" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L42" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M42" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N42" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O42" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4057,50 +4068,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C43" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D43" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E43" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H43" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I43" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J43" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K43" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L43" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M43" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N43" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O43" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -4114,12 +4125,12 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4145,64 +4156,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C44" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D44" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E44" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H44" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I44" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J44" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K44" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L44" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M44" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N44" t="n">
         <v>32.38</v>
       </c>
       <c r="O44" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4233,64 +4242,64 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C45" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D45" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E45" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H45" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I45" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J45" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K45" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L45" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M45" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N45" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O45" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4312,78 +4321,76 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C46" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D46" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E46" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H46" t="n">
         <v>0.17</v>
       </c>
       <c r="I46" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J46" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K46" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L46" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M46" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N46" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O46" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4396,59 +4403,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C47" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D47" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E47" t="n">
         <v>31.82</v>
       </c>
-      <c r="E47" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F47" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H47" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I47" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J47" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K47" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L47" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M47" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N47" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O47" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,18 +4459,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4480,55 +4483,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C48" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D48" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E48" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I48" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J48" t="n">
         <v>31.65</v>
       </c>
-      <c r="J48" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K48" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L48" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M48" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N48" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O48" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4536,18 +4543,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4562,57 +4569,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C49" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D49" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E49" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H49" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J49" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K49" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L49" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M49" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N49" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O49" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4620,18 +4627,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4646,57 +4653,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C50" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D50" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E50" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H50" t="n">
         <v>0.1</v>
       </c>
       <c r="I50" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J50" t="n">
         <v>31.72</v>
       </c>
       <c r="K50" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L50" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M50" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N50" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O50" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4704,18 +4711,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4730,57 +4737,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C51" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D51" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E51" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I51" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J51" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K51" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L51" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M51" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N51" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O51" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4791,9 +4798,9 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4814,76 +4821,80 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C52" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D52" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I52" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J52" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K52" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L52" t="n">
         <v>31.84</v>
       </c>
-      <c r="C52" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D52" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E52" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I52" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J52" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K52" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L52" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M52" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N52" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O52" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4898,71 +4909,69 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C53" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D53" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E53" t="n">
         <v>31.66</v>
       </c>
-      <c r="E53" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F53" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H53" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I53" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J53" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K53" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L53" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M53" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N53" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O53" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4979,85 +4988,79 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C54" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D54" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E54" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H54" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I54" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J54" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K54" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L54" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M54" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N54" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O54" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5070,55 +5073,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C55" t="n">
         <v>31.73</v>
       </c>
       <c r="D55" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E55" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H55" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I55" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J55" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K55" t="n">
         <v>31.57</v>
       </c>
-      <c r="K55" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L55" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M55" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N55" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O55" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5129,18 +5136,20 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5152,57 +5161,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C56" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D56" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E56" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H56" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I56" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J56" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K56" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L56" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M56" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N56" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O56" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,18 +5224,16 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5238,57 +5245,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C57" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D57" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E57" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H57" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I57" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J57" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K57" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L57" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M57" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N57" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O57" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5301,12 +5308,12 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5322,76 +5329,78 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C58" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D58" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E58" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I58" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J58" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K58" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L58" t="n">
         <v>31.72</v>
       </c>
-      <c r="C58" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D58" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E58" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I58" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J58" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K58" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L58" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M58" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N58" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O58" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5404,59 +5413,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C59" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D59" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E59" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H59" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I59" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J59" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K59" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L59" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M59" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N59" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O59" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5468,12 +5473,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5495,62 +5500,62 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C60" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D60" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E60" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I60" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J60" t="n">
         <v>31.49</v>
       </c>
-      <c r="E60" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I60" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K60" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L60" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M60" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N60" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O60" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
@@ -5577,67 +5582,65 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>31.5</v>
       </c>
       <c r="C61" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D61" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E61" t="n">
         <v>31.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H61" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I61" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J61" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K61" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L61" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M61" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N61" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O61" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5659,50 +5662,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C62" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D62" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E62" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H62" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I62" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J62" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K62" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L62" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M62" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N62" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O62" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5712,77 +5715,87 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C63" t="n">
         <v>31.69</v>
       </c>
       <c r="D63" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E63" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H63" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I63" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J63" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K63" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L63" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M63" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N63" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O63" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5790,30 +5803,26 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
@@ -5829,50 +5838,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C64" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D64" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E64" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I64" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J64" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K64" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L64" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M64" t="n">
         <v>31.69</v>
       </c>
-      <c r="D64" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E64" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I64" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J64" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K64" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L64" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M64" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N64" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O64" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5890,16 +5899,18 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W64" s="11" t="inlineStr">
         <is>
@@ -5908,60 +5919,62 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>31.68</v>
       </c>
       <c r="C65" t="n">
-        <v>31.87</v>
+        <v>31.79</v>
       </c>
       <c r="D65" t="n">
-        <v>31.61</v>
+        <v>31.67</v>
       </c>
       <c r="E65" t="n">
-        <v>31.68</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>0.04</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0013</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="I65" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J65" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K65" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L65" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M65" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N65" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O65" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+        <v>32.13</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5969,25 +5982,19 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="11" t="inlineStr">
         <is>
@@ -5996,36 +6003,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="13" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="K66" s="13" t="n">
+      <c r="I66" s="14" t="n">
         <v>31.55</v>
       </c>
-      <c r="L66" s="13" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>32.13</v>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>31.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5933,7 +5933,7 @@
         <v>31.68</v>
       </c>
       <c r="C65" t="n">
-        <v>31.79</v>
+        <v>31.81</v>
       </c>
       <c r="D65" t="n">
         <v>31.67</v>
@@ -5948,7 +5948,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I65" t="n">
         <v>31.35</v>
@@ -5987,8 +5987,10 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T65" s="8" t="n">
-        <v/>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U65" s="8" t="n">
         <v/>
@@ -6014,7 +6016,7 @@
         </is>
       </c>
       <c r="I66" s="14" t="n">
-        <v>31.55</v>
+        <v>31.53</v>
       </c>
       <c r="J66" s="14" t="n">
         <v/>
@@ -6032,7 +6034,7 @@
         <v/>
       </c>
       <c r="O66" s="14" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5933,7 +5933,7 @@
         <v>31.68</v>
       </c>
       <c r="C65" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="D65" t="n">
         <v>31.67</v>
@@ -5948,7 +5948,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I65" t="n">
         <v>31.35</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="I66" s="14" t="n">
-        <v>31.53</v>
+        <v>31.51</v>
       </c>
       <c r="J66" s="14" t="n">
         <v/>
@@ -6034,7 +6034,7 @@
         <v/>
       </c>
       <c r="O66" s="14" t="n">
-        <v>31.96</v>
+        <v>31.99</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5930,25 +5927,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C65" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="D65" t="n">
-        <v>31.67</v>
+        <v>31.69</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.72</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>0.0013</v>
       </c>
       <c r="H65" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="I65" t="n">
         <v>31.35</v>
@@ -5971,10 +5968,8 @@
       <c r="O65" t="n">
         <v>32.13</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P65" s="6" t="n">
+        <v/>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5982,9 +5977,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
@@ -5992,8 +5987,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U65" s="8" t="n">
-        <v/>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -6005,36 +6002,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
-        <v>31.99</v>
+      <c r="I66" s="13" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>32.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>31.64</v>
       </c>
       <c r="C2" t="n">
-        <v>31.65</v>
+        <v>31.7</v>
       </c>
       <c r="D2" t="n">
-        <v>31.53</v>
+        <v>31.58</v>
       </c>
       <c r="E2" t="n">
         <v>31.64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0001</v>
       </c>
       <c r="H2" t="n">
         <v>0.12</v>
       </c>
       <c r="I2" t="n">
-        <v>31.45</v>
+        <v>31.42</v>
       </c>
       <c r="J2" t="n">
-        <v>31.48</v>
+        <v>31.54</v>
       </c>
       <c r="K2" t="n">
-        <v>31.52</v>
+        <v>31.58</v>
       </c>
       <c r="L2" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="M2" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="N2" t="n">
-        <v>31.64</v>
+        <v>31.78</v>
       </c>
       <c r="O2" t="n">
-        <v>31.7</v>
+        <v>31.77</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,12 +695,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -705,10 +710,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -718,16 +721,20 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="C3" t="n">
         <v>31.7</v>
@@ -736,37 +743,37 @@
         <v>31.58</v>
       </c>
       <c r="E3" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H3" t="n">
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>31.42</v>
+        <v>31.46</v>
       </c>
       <c r="J3" t="n">
-        <v>31.54</v>
+        <v>31.52</v>
       </c>
       <c r="K3" t="n">
         <v>31.58</v>
       </c>
       <c r="L3" t="n">
-        <v>31.62</v>
+        <v>31.64</v>
       </c>
       <c r="M3" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="N3" t="n">
-        <v>31.78</v>
+        <v>31.75</v>
       </c>
       <c r="O3" t="n">
-        <v>31.77</v>
+        <v>31.81</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,19 +781,17 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -800,78 +805,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="C4" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="D4" t="n">
         <v>31.58</v>
       </c>
       <c r="E4" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I4" t="n">
-        <v>31.46</v>
+        <v>31.47</v>
       </c>
       <c r="J4" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="K4" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="L4" t="n">
-        <v>31.64</v>
+        <v>31.67</v>
       </c>
       <c r="M4" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N4" t="n">
-        <v>31.75</v>
+        <v>31.85</v>
       </c>
       <c r="O4" t="n">
-        <v>31.81</v>
+        <v>31.82</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -884,76 +887,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C5" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E5" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I5" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J5" t="n">
         <v>31.61</v>
       </c>
       <c r="K5" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L5" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M5" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N5" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O5" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -966,59 +971,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C6" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L6" t="n">
         <v>31.7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="M6" t="n">
         <v>31.77</v>
       </c>
-      <c r="D6" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E6" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I6" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K6" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M6" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N6" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O6" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1036,11 +1037,13 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1055,50 +1058,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C7" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D7" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E7" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F7" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H7" t="n">
         <v>0.11</v>
       </c>
       <c r="I7" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J7" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K7" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L7" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M7" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N7" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O7" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1116,13 +1119,11 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1137,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C8" t="n">
         <v>31.91</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E8" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I8" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J8" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K8" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L8" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M8" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N8" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O8" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,15 +1192,13 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1212,37 +1211,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C9" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D9" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E9" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J9" t="n">
         <v>31.75</v>
@@ -1254,13 +1257,13 @@
         <v>31.85</v>
       </c>
       <c r="M9" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N9" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O9" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,16 +1271,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1292,57 +1299,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C10" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D10" t="n">
         <v>31.79</v>
       </c>
       <c r="E10" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I10" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J10" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K10" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L10" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M10" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N10" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O10" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,12 +1359,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1385,50 +1392,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C11" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D11" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E11" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H11" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I11" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J11" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K11" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L11" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M11" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N11" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,21 +1443,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1462,59 +1467,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C12" t="n">
         <v>31.96</v>
       </c>
       <c r="D12" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E12" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I12" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K12" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L12" t="n">
         <v>31.89</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I12" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J12" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K12" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L12" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M12" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N12" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O12" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1551,50 +1552,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>31.93</v>
       </c>
       <c r="C13" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D13" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E13" t="n">
         <v>31.93</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I13" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J13" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K13" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L13" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M13" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N13" t="n">
         <v>32.03</v>
       </c>
       <c r="O13" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,74 +1608,82 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C14" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D14" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J14" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K14" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L14" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M14" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N14" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O14" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,12 +1696,12 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -1700,69 +1709,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E15" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F15" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H15" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I15" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J15" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K15" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L15" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M15" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N15" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O15" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1770,8 +1773,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
@@ -1783,10 +1788,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1796,55 +1799,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C16" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D16" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E16" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H16" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I16" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J16" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K16" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L16" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N16" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O16" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,20 +1859,16 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1887,47 +1890,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C17" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D17" t="n">
         <v>32.04</v>
       </c>
       <c r="E17" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I17" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J17" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K17" t="n">
         <v>32.02</v>
       </c>
       <c r="L17" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M17" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N17" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O17" t="n">
         <v>32.41</v>
@@ -1941,9 +1944,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1962,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>32.1</v>
       </c>
       <c r="C18" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D18" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E18" t="n">
         <v>32.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H18" t="n">
         <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J18" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K18" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L18" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M18" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N18" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O18" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,8 +2031,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2044,42 +2049,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C19" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D19" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E19" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
         <v>31.9</v>
       </c>
       <c r="J19" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K19" t="n">
         <v>32.03</v>
@@ -2094,7 +2099,7 @@
         <v>32.23</v>
       </c>
       <c r="O19" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2105,14 +2110,14 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2126,59 +2131,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C20" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D20" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E20" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H20" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I20" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J20" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K20" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L20" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M20" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N20" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O20" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,15 +2190,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2210,55 +2209,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C21" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D21" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E21" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H21" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I21" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J21" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K21" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L21" t="n">
         <v>32.15</v>
       </c>
       <c r="M21" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N21" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O21" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,16 +2272,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2288,59 +2295,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C22" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D22" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E22" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I22" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J22" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K22" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L22" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M22" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N22" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O22" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2379,50 +2382,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C23" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D23" t="n">
         <v>32.26</v>
       </c>
-      <c r="C23" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D23" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E23" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F23" t="n">
         <v>0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H23" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I23" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J23" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K23" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L23" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M23" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N23" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O23" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,12 +2438,12 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -2461,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C24" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D24" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E24" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H24" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I24" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J24" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K24" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L24" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M24" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N24" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O24" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2512,23 +2515,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2538,34 +2539,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C25" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D25" t="n">
         <v>32.28</v>
       </c>
-      <c r="C25" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D25" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E25" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I25" t="n">
         <v>32.09</v>
@@ -2574,19 +2579,19 @@
         <v>32.12</v>
       </c>
       <c r="K25" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L25" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M25" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N25" t="n">
         <v>32.4</v>
       </c>
-      <c r="N25" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O25" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2594,21 +2599,23 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2618,59 +2625,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C26" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D26" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E26" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F26" t="n">
         <v>0.05</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J26" t="n">
         <v>32.09</v>
       </c>
-      <c r="J26" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K26" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L26" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M26" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N26" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O26" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,18 +2686,14 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2704,55 +2703,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C27" t="n">
         <v>32.38</v>
       </c>
       <c r="D27" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E27" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H27" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I27" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J27" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K27" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L27" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M27" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N27" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O27" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,12 +2763,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2784,57 +2789,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C28" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D28" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E28" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I28" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J28" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K28" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L28" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M28" t="n">
         <v>32.34</v>
       </c>
-      <c r="M28" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N28" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O28" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2842,21 +2847,23 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2875,50 +2882,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C29" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D29" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E29" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I29" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J29" t="n">
         <v>32.19</v>
       </c>
       <c r="K29" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L29" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M29" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N29" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O29" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2929,9 +2936,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2939,10 +2946,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2961,50 +2966,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C30" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D30" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E30" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H30" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
         <v>32.16</v>
       </c>
       <c r="J30" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K30" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L30" t="n">
         <v>32.33</v>
       </c>
       <c r="M30" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N30" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O30" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3015,18 +3020,20 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3036,59 +3043,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C31" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D31" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E31" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H31" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I31" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J31" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K31" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L31" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M31" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N31" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O31" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3099,14 +3102,14 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -3122,55 +3125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C32" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D32" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E32" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H32" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I32" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J32" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K32" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L32" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M32" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N32" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O32" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3178,12 +3185,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3191,10 +3200,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3213,50 +3220,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C33" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D33" t="n">
         <v>32.21</v>
       </c>
       <c r="E33" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H33" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I33" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J33" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K33" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L33" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M33" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N33" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O33" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3266,18 +3273,16 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3292,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C34" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D34" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E34" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H34" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I34" t="n">
         <v>31.93</v>
       </c>
       <c r="J34" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K34" t="n">
         <v>32.15</v>
       </c>
-      <c r="K34" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L34" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M34" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N34" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O34" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,18 +3355,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,69 +3388,73 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>32.4</v>
       </c>
       <c r="C35" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D35" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E35" t="n">
         <v>32.4</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I35" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J35" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K35" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L35" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M35" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N35" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O35" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3460,62 +3469,60 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C36" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D36" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E36" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F36" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I36" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J36" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K36" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L36" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M36" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N36" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
@@ -3524,12 +3531,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3548,57 +3555,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C37" t="n">
         <v>32.31</v>
       </c>
       <c r="D37" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E37" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H37" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I37" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J37" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K37" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L37" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M37" t="n">
         <v>32.33</v>
       </c>
-      <c r="M37" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N37" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O37" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3641,67 +3648,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C38" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D38" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E38" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H38" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J38" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K38" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L38" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M38" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N38" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O38" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3720,57 +3723,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C39" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D39" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E39" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F39" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H39" t="n">
         <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J39" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K39" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L39" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M39" t="n">
         <v>32.29</v>
       </c>
       <c r="N39" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O39" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3781,13 +3784,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3809,35 +3814,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C40" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D40" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E40" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I40" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J40" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K40" t="n">
         <v>32.18</v>
@@ -3846,13 +3851,13 @@
         <v>32.23</v>
       </c>
       <c r="M40" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N40" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O40" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3860,18 +3865,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3886,63 +3891,67 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C41" t="n">
         <v>32.21</v>
       </c>
-      <c r="C41" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D41" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E41" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I41" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J41" t="n">
         <v>32.12</v>
       </c>
       <c r="K41" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L41" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M41" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N41" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O41" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3977,50 +3986,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C42" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D42" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E42" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H42" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I42" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J42" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K42" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L42" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M42" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N42" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O42" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -4034,12 +4043,12 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4065,64 +4074,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C43" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D43" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E43" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H43" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I43" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J43" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K43" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L43" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M43" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N43" t="n">
         <v>32.38</v>
       </c>
       <c r="O43" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4153,64 +4160,64 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C44" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D44" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E44" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H44" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I44" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J44" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K44" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L44" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M44" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N44" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O44" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4232,78 +4239,76 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C45" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D45" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E45" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H45" t="n">
         <v>0.17</v>
       </c>
       <c r="I45" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J45" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K45" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L45" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M45" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N45" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O45" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4316,59 +4321,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C46" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D46" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E46" t="n">
         <v>31.82</v>
       </c>
-      <c r="E46" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F46" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H46" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I46" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J46" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K46" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L46" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M46" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N46" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O46" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4376,18 +4377,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4400,55 +4401,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C47" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D47" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E47" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I47" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J47" t="n">
         <v>31.65</v>
       </c>
-      <c r="J47" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K47" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L47" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M47" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N47" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O47" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,18 +4461,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4482,57 +4487,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C48" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D48" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E48" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H48" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I48" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J48" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K48" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L48" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M48" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N48" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O48" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4540,18 +4545,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4566,57 +4571,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C49" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D49" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E49" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H49" t="n">
         <v>0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J49" t="n">
         <v>31.72</v>
       </c>
       <c r="K49" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L49" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M49" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N49" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O49" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4624,18 +4629,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4650,57 +4655,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C50" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D50" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E50" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I50" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J50" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K50" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L50" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M50" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N50" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O50" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,9 +4716,9 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4734,76 +4739,80 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C51" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J51" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K51" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L51" t="n">
         <v>31.84</v>
       </c>
-      <c r="C51" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D51" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E51" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I51" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J51" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K51" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L51" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M51" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N51" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O51" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4818,71 +4827,69 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C52" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D52" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E52" t="n">
         <v>31.66</v>
       </c>
-      <c r="E52" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F52" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H52" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I52" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J52" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K52" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L52" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M52" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N52" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O52" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4899,85 +4906,79 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C53" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D53" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E53" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H53" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I53" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J53" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K53" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L53" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M53" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N53" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O53" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4990,55 +4991,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C54" t="n">
         <v>31.73</v>
       </c>
       <c r="D54" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E54" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H54" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I54" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J54" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K54" t="n">
         <v>31.57</v>
       </c>
-      <c r="K54" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L54" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M54" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N54" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O54" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,18 +5054,20 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5072,57 +5079,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C55" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D55" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E55" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H55" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I55" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J55" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K55" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L55" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M55" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N55" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O55" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5135,18 +5142,16 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5158,57 +5163,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C56" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D56" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E56" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H56" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I56" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J56" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K56" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L56" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M56" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N56" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O56" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5221,12 +5226,12 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5242,76 +5247,78 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C57" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D57" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E57" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I57" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J57" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K57" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L57" t="n">
         <v>31.72</v>
       </c>
-      <c r="C57" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E57" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I57" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J57" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K57" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L57" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M57" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N57" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O57" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5324,59 +5331,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C58" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D58" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E58" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H58" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I58" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J58" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K58" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L58" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M58" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N58" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O58" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5388,12 +5391,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5415,62 +5418,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C59" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D59" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E59" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J59" t="n">
         <v>31.49</v>
       </c>
-      <c r="E59" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I59" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J59" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K59" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L59" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M59" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N59" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O59" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
@@ -5497,67 +5500,65 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>31.5</v>
       </c>
       <c r="C60" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D60" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E60" t="n">
         <v>31.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H60" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I60" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J60" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K60" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L60" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M60" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N60" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O60" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5579,50 +5580,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C61" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D61" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E61" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I61" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J61" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K61" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L61" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M61" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N61" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O61" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5632,77 +5633,87 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C62" t="n">
         <v>31.69</v>
       </c>
       <c r="D62" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E62" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I62" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J62" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K62" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L62" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M62" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N62" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O62" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5710,30 +5721,26 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
@@ -5749,50 +5756,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C63" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D63" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I63" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J63" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K63" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L63" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M63" t="n">
         <v>31.69</v>
       </c>
-      <c r="D63" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I63" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J63" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K63" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L63" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M63" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N63" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O63" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5810,16 +5817,18 @@
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
@@ -5828,27 +5837,27 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C64" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D64" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E64" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F64" t="n">
         <v>0.04</v>
@@ -5857,28 +5866,28 @@
         <v>0.0013</v>
       </c>
       <c r="H64" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I64" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J64" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K64" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L64" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M64" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N64" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O64" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5891,12 +5900,12 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -5904,10 +5913,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="11" t="inlineStr">
         <is>
@@ -5923,53 +5930,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.72</v>
+        <v>31.8</v>
       </c>
       <c r="C65" t="n">
-        <v>31.91</v>
+        <v>31.92</v>
       </c>
       <c r="D65" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="E65" t="n">
-        <v>31.72</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>0.04</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0013</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="I65" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J65" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K65" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L65" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M65" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N65" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O65" t="n">
         <v>32.13</v>
       </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5977,9 +5986,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
@@ -6002,36 +6011,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="13" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L66" s="13" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>31.83</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>32.13</v>
+      <c r="I66" s="14" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>32.08</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5940,7 +5940,7 @@
         <v>31.92</v>
       </c>
       <c r="D65" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="E65" t="n">
         <v/>
@@ -5952,7 +5952,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="I65" t="n">
         <v>31.47</v>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="I66" s="14" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="J66" s="14" t="n">
         <v/>
@@ -6040,7 +6040,7 @@
         <v/>
       </c>
       <c r="O66" s="14" t="n">
-        <v>32.08</v>
+        <v>32.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5934,25 +5931,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.8</v>
+        <v>31.76</v>
       </c>
       <c r="C65" t="n">
-        <v>31.92</v>
+        <v>31.9</v>
       </c>
       <c r="D65" t="n">
-        <v>31.71</v>
+        <v>31.72</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.77</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>0.0018</v>
       </c>
       <c r="H65" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="I65" t="n">
         <v>31.47</v>
@@ -5975,10 +5972,8 @@
       <c r="O65" t="n">
         <v>32.13</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P65" s="6" t="n">
+        <v/>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5986,9 +5981,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
@@ -6016,31 +6011,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
-        <v>32.13</v>
+      <c r="I66" s="13" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>32.08</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,11 +644,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="C2" t="n">
         <v>31.7</v>
@@ -654,37 +657,37 @@
         <v>31.58</v>
       </c>
       <c r="E2" t="n">
-        <v>31.64</v>
+        <v>31.7</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H2" t="n">
         <v>0.12</v>
       </c>
       <c r="I2" t="n">
-        <v>31.42</v>
+        <v>31.46</v>
       </c>
       <c r="J2" t="n">
-        <v>31.54</v>
+        <v>31.52</v>
       </c>
       <c r="K2" t="n">
         <v>31.58</v>
       </c>
       <c r="L2" t="n">
-        <v>31.62</v>
+        <v>31.64</v>
       </c>
       <c r="M2" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="N2" t="n">
-        <v>31.78</v>
+        <v>31.75</v>
       </c>
       <c r="O2" t="n">
-        <v>31.77</v>
+        <v>31.81</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,19 +695,17 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -718,78 +719,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="C3" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="D3" t="n">
         <v>31.58</v>
       </c>
       <c r="E3" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I3" t="n">
-        <v>31.46</v>
+        <v>31.47</v>
       </c>
       <c r="J3" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="K3" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="L3" t="n">
-        <v>31.64</v>
+        <v>31.67</v>
       </c>
       <c r="M3" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N3" t="n">
-        <v>31.75</v>
+        <v>31.85</v>
       </c>
       <c r="O3" t="n">
-        <v>31.81</v>
+        <v>31.82</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -802,76 +801,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C4" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D4" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E4" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J4" t="n">
         <v>31.61</v>
       </c>
       <c r="K4" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L4" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M4" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N4" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O4" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -884,59 +885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K5" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L5" t="n">
         <v>31.7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="M5" t="n">
         <v>31.77</v>
       </c>
-      <c r="D5" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E5" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I5" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J5" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K5" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L5" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M5" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N5" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O5" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -954,11 +951,13 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -973,50 +972,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C6" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D6" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E6" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F6" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H6" t="n">
         <v>0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J6" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K6" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L6" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M6" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N6" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O6" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1034,13 +1033,11 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1055,50 +1052,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C7" t="n">
         <v>31.91</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E7" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J7" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K7" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L7" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M7" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N7" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O7" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,15 +1106,13 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1130,37 +1125,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C8" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D8" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E8" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J8" t="n">
         <v>31.75</v>
@@ -1172,13 +1171,13 @@
         <v>31.85</v>
       </c>
       <c r="M8" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N8" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O8" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,16 +1185,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1210,57 +1213,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C9" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D9" t="n">
         <v>31.79</v>
       </c>
       <c r="E9" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I9" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J9" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K9" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L9" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M9" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N9" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O9" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,12 +1273,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -1303,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D10" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E10" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I10" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J10" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K10" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L10" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M10" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N10" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,21 +1357,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1380,59 +1381,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C11" t="n">
         <v>31.96</v>
       </c>
       <c r="D11" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E11" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K11" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L11" t="n">
         <v>31.89</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I11" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J11" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K11" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L11" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M11" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N11" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O11" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1469,50 +1466,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>31.93</v>
       </c>
       <c r="C12" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D12" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E12" t="n">
         <v>31.93</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I12" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J12" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K12" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L12" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M12" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N12" t="n">
         <v>32.03</v>
       </c>
       <c r="O12" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,74 +1522,82 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C13" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D13" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J13" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K13" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L13" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M13" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N13" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O13" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,12 +1610,12 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
@@ -1618,69 +1623,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C14" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E14" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I14" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J14" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K14" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L14" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M14" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N14" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O14" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,8 +1687,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1701,10 +1702,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1714,55 +1713,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C15" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D15" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E15" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H15" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I15" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J15" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K15" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L15" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N15" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O15" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1770,20 +1773,16 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1805,47 +1804,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C16" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D16" t="n">
         <v>32.04</v>
       </c>
       <c r="E16" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H16" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J16" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K16" t="n">
         <v>32.02</v>
       </c>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M16" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N16" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O16" t="n">
         <v>32.41</v>
@@ -1859,9 +1858,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1880,57 +1879,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>32.1</v>
       </c>
       <c r="C17" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D17" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E17" t="n">
         <v>32.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
         <v>0.14</v>
       </c>
       <c r="I17" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J17" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K17" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L17" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M17" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N17" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O17" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,8 +1945,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1962,42 +1963,42 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C18" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D18" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E18" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I18" t="n">
         <v>31.9</v>
       </c>
       <c r="J18" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K18" t="n">
         <v>32.03</v>
@@ -2012,7 +2013,7 @@
         <v>32.23</v>
       </c>
       <c r="O18" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,14 +2024,14 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2044,59 +2045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C19" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D19" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E19" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I19" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J19" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K19" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L19" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M19" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N19" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O19" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,15 +2104,13 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2128,55 +2123,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C20" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D20" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E20" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J20" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K20" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L20" t="n">
         <v>32.15</v>
       </c>
       <c r="M20" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N20" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O20" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2187,16 +2186,20 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2206,59 +2209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C21" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D21" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E21" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H21" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J21" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K21" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L21" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M21" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N21" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O21" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2297,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C22" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D22" t="n">
         <v>32.26</v>
       </c>
-      <c r="C22" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D22" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E22" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F22" t="n">
         <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H22" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I22" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J22" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K22" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L22" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M22" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N22" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O22" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,12 +2352,12 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -2379,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C23" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D23" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E23" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I23" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J23" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K23" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L23" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M23" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N23" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O23" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,23 +2429,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2456,34 +2453,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D24" t="n">
         <v>32.28</v>
       </c>
-      <c r="C24" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D24" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E24" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I24" t="n">
         <v>32.09</v>
@@ -2492,19 +2493,19 @@
         <v>32.12</v>
       </c>
       <c r="K24" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L24" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M24" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N24" t="n">
         <v>32.4</v>
       </c>
-      <c r="N24" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O24" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2512,21 +2513,23 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2536,59 +2539,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C25" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D25" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E25" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F25" t="n">
         <v>0.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J25" t="n">
         <v>32.09</v>
       </c>
-      <c r="J25" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K25" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L25" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M25" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N25" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O25" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2601,18 +2600,14 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2622,55 +2617,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C26" t="n">
         <v>32.38</v>
       </c>
       <c r="D26" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E26" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H26" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I26" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J26" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K26" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L26" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M26" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N26" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O26" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2678,12 +2677,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2702,57 +2703,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C27" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D27" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E27" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I27" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J27" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K27" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L27" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M27" t="n">
         <v>32.34</v>
       </c>
-      <c r="M27" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N27" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O27" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,21 +2761,23 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2793,50 +2796,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C28" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D28" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E28" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I28" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J28" t="n">
         <v>32.19</v>
       </c>
       <c r="K28" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L28" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M28" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N28" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O28" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2847,9 +2850,9 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2857,10 +2860,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2879,50 +2880,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C29" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D29" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E29" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H29" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I29" t="n">
         <v>32.16</v>
       </c>
       <c r="J29" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K29" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L29" t="n">
         <v>32.33</v>
       </c>
       <c r="M29" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N29" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O29" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2933,18 +2934,20 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2954,59 +2957,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C30" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D30" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E30" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H30" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I30" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J30" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K30" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L30" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M30" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N30" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O30" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3017,14 +3016,14 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -3040,55 +3039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C31" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D31" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E31" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H31" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J31" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K31" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L31" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M31" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N31" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O31" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3096,12 +3099,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3109,10 +3114,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3131,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C32" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D32" t="n">
         <v>32.21</v>
       </c>
       <c r="E32" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H32" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I32" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J32" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K32" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L32" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M32" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N32" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O32" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,18 +3187,16 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3210,57 +3211,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C33" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D33" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E33" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H33" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I33" t="n">
         <v>31.93</v>
       </c>
       <c r="J33" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K33" t="n">
         <v>32.15</v>
       </c>
-      <c r="K33" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L33" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M33" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N33" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O33" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3268,18 +3269,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3301,69 +3302,73 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>32.4</v>
       </c>
       <c r="C34" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D34" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E34" t="n">
         <v>32.4</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I34" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J34" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K34" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L34" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M34" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N34" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O34" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3378,62 +3383,60 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C35" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D35" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E35" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F35" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H35" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I35" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J35" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K35" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L35" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M35" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N35" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O35" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
@@ -3442,12 +3445,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3466,57 +3469,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C36" t="n">
         <v>32.31</v>
       </c>
       <c r="D36" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E36" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H36" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I36" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J36" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K36" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L36" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M36" t="n">
         <v>32.33</v>
       </c>
-      <c r="M36" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N36" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O36" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3559,67 +3562,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C37" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D37" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E37" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H37" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J37" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K37" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L37" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M37" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N37" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O37" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3638,57 +3637,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C38" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D38" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E38" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H38" t="n">
         <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J38" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K38" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L38" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M38" t="n">
         <v>32.29</v>
       </c>
       <c r="N38" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O38" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,13 +3698,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3727,35 +3728,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C39" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D39" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E39" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I39" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J39" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K39" t="n">
         <v>32.18</v>
@@ -3764,13 +3765,13 @@
         <v>32.23</v>
       </c>
       <c r="M39" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N39" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O39" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3778,18 +3779,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3804,63 +3805,67 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C40" t="n">
         <v>32.21</v>
       </c>
-      <c r="C40" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D40" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E40" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H40" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I40" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J40" t="n">
         <v>32.12</v>
       </c>
       <c r="K40" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L40" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M40" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N40" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O40" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3895,50 +3900,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C41" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D41" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E41" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H41" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J41" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K41" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L41" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M41" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N41" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O41" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -3952,12 +3957,12 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3983,64 +3988,62 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C42" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D42" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E42" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H42" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I42" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J42" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K42" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L42" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M42" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N42" t="n">
         <v>32.38</v>
       </c>
       <c r="O42" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4071,64 +4074,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C43" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D43" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E43" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H43" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I43" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J43" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K43" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L43" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M43" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N43" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O43" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4150,78 +4153,76 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C44" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D44" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E44" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H44" t="n">
         <v>0.17</v>
       </c>
       <c r="I44" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J44" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K44" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L44" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M44" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N44" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O44" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4234,59 +4235,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C45" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D45" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E45" t="n">
         <v>31.82</v>
       </c>
-      <c r="E45" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F45" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H45" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I45" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J45" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K45" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L45" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M45" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N45" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O45" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4294,18 +4291,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4318,55 +4315,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C46" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D46" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E46" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I46" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J46" t="n">
         <v>31.65</v>
       </c>
-      <c r="J46" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K46" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L46" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M46" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N46" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O46" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4374,18 +4375,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4400,57 +4401,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C47" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D47" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E47" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H47" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I47" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J47" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K47" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L47" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M47" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N47" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O47" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4458,18 +4459,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4484,57 +4485,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C48" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D48" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E48" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H48" t="n">
         <v>0.1</v>
       </c>
       <c r="I48" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J48" t="n">
         <v>31.72</v>
       </c>
       <c r="K48" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L48" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M48" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N48" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O48" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4542,18 +4543,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4568,57 +4569,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C49" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D49" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E49" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I49" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J49" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K49" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L49" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M49" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N49" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O49" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4629,9 +4630,9 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4652,76 +4653,80 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C50" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D50" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E50" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J50" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K50" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L50" t="n">
         <v>31.84</v>
       </c>
-      <c r="C50" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D50" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E50" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K50" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L50" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M50" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N50" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O50" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4736,71 +4741,69 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C51" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D51" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E51" t="n">
         <v>31.66</v>
       </c>
-      <c r="E51" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F51" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H51" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I51" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J51" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K51" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L51" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M51" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N51" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O51" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4817,85 +4820,79 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C52" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D52" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E52" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H52" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I52" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J52" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K52" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L52" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M52" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N52" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O52" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4908,55 +4905,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C53" t="n">
         <v>31.73</v>
       </c>
       <c r="D53" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E53" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H53" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I53" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J53" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K53" t="n">
         <v>31.57</v>
       </c>
-      <c r="K53" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L53" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M53" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N53" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O53" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4967,18 +4968,20 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4990,57 +4993,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C54" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D54" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E54" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H54" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I54" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J54" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K54" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L54" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M54" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N54" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O54" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5053,18 +5056,16 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5076,57 +5077,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C55" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D55" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E55" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H55" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I55" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J55" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K55" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L55" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M55" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N55" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O55" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5139,12 +5140,12 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5160,76 +5161,78 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C56" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D56" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E56" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I56" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J56" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K56" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L56" t="n">
         <v>31.72</v>
       </c>
-      <c r="C56" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E56" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I56" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J56" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K56" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L56" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M56" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N56" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O56" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5242,59 +5245,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C57" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D57" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E57" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H57" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I57" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J57" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K57" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L57" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M57" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N57" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O57" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,12 +5305,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5333,62 +5332,62 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C58" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D58" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E58" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I58" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J58" t="n">
         <v>31.49</v>
       </c>
-      <c r="E58" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I58" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J58" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K58" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L58" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M58" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N58" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O58" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5415,67 +5414,65 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>31.5</v>
       </c>
       <c r="C59" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D59" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E59" t="n">
         <v>31.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H59" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I59" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J59" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K59" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L59" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M59" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N59" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O59" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5497,50 +5494,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C60" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D60" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E60" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H60" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I60" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J60" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K60" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L60" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M60" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N60" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O60" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5550,77 +5547,87 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C61" t="n">
         <v>31.69</v>
       </c>
       <c r="D61" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E61" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H61" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I61" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J61" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K61" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L61" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M61" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N61" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O61" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,30 +5635,26 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
@@ -5667,50 +5670,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C62" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D62" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E62" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I62" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J62" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K62" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L62" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M62" t="n">
         <v>31.69</v>
       </c>
-      <c r="D62" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E62" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I62" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J62" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K62" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L62" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M62" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N62" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O62" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5728,16 +5731,18 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
@@ -5746,27 +5751,27 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C63" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D63" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E63" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F63" t="n">
         <v>0.04</v>
@@ -5775,28 +5780,28 @@
         <v>0.0013</v>
       </c>
       <c r="H63" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I63" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J63" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K63" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L63" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M63" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N63" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O63" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5809,12 +5814,12 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U63" s="8" t="inlineStr">
@@ -5822,10 +5827,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
@@ -5841,47 +5844,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C64" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D64" t="n">
         <v>31.72</v>
       </c>
-      <c r="C64" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D64" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E64" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H64" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I64" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J64" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K64" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L64" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M64" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N64" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O64" t="n">
         <v>32.13</v>
@@ -5920,122 +5923,122 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.76</v>
+        <v>31.83</v>
       </c>
       <c r="C65" t="n">
         <v>31.9</v>
       </c>
       <c r="D65" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E65" t="n">
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v/>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I65" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K65" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="L65" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="M65" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="N65" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="O65" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>明日預測</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="n">
         <v>31.77</v>
       </c>
-      <c r="F65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I65" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J65" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="K65" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L65" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="M65" t="n">
-        <v>31.83</v>
-      </c>
-      <c r="N65" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="O65" t="n">
-        <v>32.13</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="L66" s="13" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>31.93</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>32.08</v>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>31.96</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5934,25 +5931,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="C65" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D65" t="n">
         <v>31.83</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.86</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>0.09</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>0.0027</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="I65" t="n">
         <v>31.55</v>
@@ -5975,29 +5972,29 @@
       <c r="O65" t="n">
         <v>32.08</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -6009,36 +6006,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
+      <c r="I66" s="13" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="N66" s="13" t="n">
         <v>31.96</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>32.05</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,69 +637,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="C2" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="D2" t="n">
         <v>31.58</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I2" t="n">
-        <v>31.46</v>
+        <v>31.47</v>
       </c>
       <c r="J2" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="K2" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="L2" t="n">
-        <v>31.64</v>
+        <v>31.67</v>
       </c>
       <c r="M2" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N2" t="n">
-        <v>31.75</v>
+        <v>31.85</v>
       </c>
       <c r="O2" t="n">
-        <v>31.81</v>
+        <v>31.82</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,76 +714,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C3" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D3" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E3" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J3" t="n">
         <v>31.61</v>
       </c>
       <c r="K3" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L3" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M3" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N3" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O3" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,59 +798,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L4" t="n">
         <v>31.7</v>
       </c>
-      <c r="C4" t="n">
+      <c r="M4" t="n">
         <v>31.77</v>
       </c>
-      <c r="D4" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E4" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I4" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L4" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M4" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N4" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O4" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -868,11 +864,13 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -887,50 +885,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C5" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D5" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E5" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F5" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H5" t="n">
         <v>0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J5" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K5" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L5" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M5" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N5" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O5" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -948,13 +946,11 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -969,50 +965,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C6" t="n">
         <v>31.91</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E6" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J6" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K6" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L6" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M6" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N6" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O6" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,15 +1019,13 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1044,37 +1038,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C7" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D7" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E7" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J7" t="n">
         <v>31.75</v>
@@ -1086,13 +1084,13 @@
         <v>31.85</v>
       </c>
       <c r="M7" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N7" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O7" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,16 +1098,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1124,57 +1126,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C8" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D8" t="n">
         <v>31.79</v>
       </c>
       <c r="E8" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J8" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K8" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L8" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M8" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N8" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O8" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,12 +1186,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1217,50 +1219,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C9" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D9" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E9" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H9" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I9" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J9" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K9" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L9" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M9" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N9" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O9" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,21 +1270,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1294,59 +1294,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C10" t="n">
         <v>31.96</v>
       </c>
       <c r="D10" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E10" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L10" t="n">
         <v>31.89</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J10" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K10" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L10" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M10" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N10" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O10" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1383,50 +1379,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>31.93</v>
       </c>
       <c r="C11" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D11" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E11" t="n">
         <v>31.93</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I11" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J11" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K11" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L11" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M11" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N11" t="n">
         <v>32.03</v>
       </c>
       <c r="O11" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,74 +1435,82 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C12" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D12" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J12" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K12" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L12" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M12" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N12" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O12" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,12 +1523,12 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -1532,69 +1536,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C13" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E13" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F13" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I13" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J13" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K13" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L13" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M13" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N13" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O13" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,8 +1600,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1615,10 +1615,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1628,55 +1626,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C14" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D14" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E14" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H14" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I14" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J14" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K14" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L14" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M14" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N14" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O14" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,20 +1686,16 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1719,47 +1717,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C15" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D15" t="n">
         <v>32.04</v>
       </c>
       <c r="E15" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H15" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J15" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K15" t="n">
         <v>32.02</v>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M15" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N15" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O15" t="n">
         <v>32.41</v>
@@ -1773,9 +1771,9 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1794,57 +1792,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>32.1</v>
       </c>
       <c r="C16" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D16" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E16" t="n">
         <v>32.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H16" t="n">
         <v>0.14</v>
       </c>
       <c r="I16" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J16" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K16" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L16" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N16" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O16" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,8 +1858,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1876,42 +1876,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D17" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E17" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
         <v>31.9</v>
       </c>
       <c r="J17" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K17" t="n">
         <v>32.03</v>
@@ -1926,7 +1926,7 @@
         <v>32.23</v>
       </c>
       <c r="O17" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,14 +1937,14 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1958,59 +1958,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C18" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D18" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E18" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I18" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J18" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K18" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L18" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M18" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N18" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O18" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2021,15 +2017,13 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2042,55 +2036,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C19" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D19" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E19" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J19" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K19" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L19" t="n">
         <v>32.15</v>
       </c>
       <c r="M19" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N19" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O19" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,16 +2099,20 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2120,59 +2122,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D20" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E20" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I20" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J20" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K20" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L20" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M20" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N20" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O20" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2211,50 +2209,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D21" t="n">
         <v>32.26</v>
       </c>
-      <c r="C21" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D21" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E21" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F21" t="n">
         <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H21" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I21" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J21" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K21" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L21" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M21" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N21" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O21" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2267,12 +2265,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -2293,50 +2291,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C22" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D22" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E22" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H22" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J22" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K22" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L22" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M22" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N22" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O22" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2344,23 +2342,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2370,34 +2366,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C23" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D23" t="n">
         <v>32.28</v>
       </c>
-      <c r="C23" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D23" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E23" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H23" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I23" t="n">
         <v>32.09</v>
@@ -2406,19 +2406,19 @@
         <v>32.12</v>
       </c>
       <c r="K23" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L23" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M23" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N23" t="n">
         <v>32.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O23" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2426,21 +2426,23 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2450,59 +2452,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C24" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D24" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E24" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F24" t="n">
         <v>0.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I24" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J24" t="n">
         <v>32.09</v>
       </c>
-      <c r="J24" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K24" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L24" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M24" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N24" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O24" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,18 +2513,14 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2536,55 +2530,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C25" t="n">
         <v>32.38</v>
       </c>
       <c r="D25" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E25" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I25" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J25" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K25" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L25" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M25" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N25" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O25" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2592,12 +2590,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2616,57 +2616,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C26" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D26" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E26" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I26" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J26" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K26" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L26" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M26" t="n">
         <v>32.34</v>
       </c>
-      <c r="M26" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N26" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O26" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2674,21 +2674,23 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2707,50 +2709,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C27" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D27" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E27" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I27" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J27" t="n">
         <v>32.19</v>
       </c>
       <c r="K27" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L27" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M27" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N27" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O27" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2761,9 +2763,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2771,10 +2773,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2793,50 +2793,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C28" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D28" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E28" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H28" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I28" t="n">
         <v>32.16</v>
       </c>
       <c r="J28" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K28" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L28" t="n">
         <v>32.33</v>
       </c>
       <c r="M28" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N28" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O28" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2847,18 +2847,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2868,59 +2870,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C29" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D29" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E29" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H29" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I29" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J29" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K29" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L29" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M29" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N29" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O29" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2931,14 +2929,14 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="inlineStr">
@@ -2954,55 +2952,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C30" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D30" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E30" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H30" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I30" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J30" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K30" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L30" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M30" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N30" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O30" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3010,12 +3012,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3023,10 +3027,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3045,50 +3047,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C31" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D31" t="n">
         <v>32.21</v>
       </c>
       <c r="E31" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I31" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J31" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K31" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L31" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M31" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N31" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O31" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3098,18 +3100,16 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3124,57 +3124,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C32" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D32" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E32" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H32" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I32" t="n">
         <v>31.93</v>
       </c>
       <c r="J32" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K32" t="n">
         <v>32.15</v>
       </c>
-      <c r="K32" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L32" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M32" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N32" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O32" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,18 +3182,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3215,69 +3215,73 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>32.4</v>
       </c>
       <c r="C33" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D33" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E33" t="n">
         <v>32.4</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I33" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J33" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K33" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L33" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M33" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N33" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O33" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3292,62 +3296,60 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C34" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D34" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E34" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F34" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H34" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I34" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J34" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K34" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L34" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M34" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N34" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O34" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
@@ -3356,12 +3358,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3380,57 +3382,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C35" t="n">
         <v>32.31</v>
       </c>
       <c r="D35" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E35" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H35" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I35" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J35" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K35" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L35" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M35" t="n">
         <v>32.33</v>
       </c>
-      <c r="M35" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N35" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O35" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3473,67 +3475,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C36" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D36" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E36" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J36" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K36" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L36" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M36" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N36" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O36" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3552,57 +3550,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C37" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D37" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E37" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F37" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H37" t="n">
         <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J37" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K37" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L37" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M37" t="n">
         <v>32.29</v>
       </c>
       <c r="N37" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O37" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,13 +3611,15 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3641,35 +3641,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C38" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D38" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E38" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I38" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J38" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K38" t="n">
         <v>32.18</v>
@@ -3678,13 +3678,13 @@
         <v>32.23</v>
       </c>
       <c r="M38" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N38" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O38" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3692,18 +3692,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3718,63 +3718,67 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C39" t="n">
         <v>32.21</v>
       </c>
-      <c r="C39" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D39" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E39" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I39" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J39" t="n">
         <v>32.12</v>
       </c>
       <c r="K39" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L39" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M39" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N39" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O39" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3809,50 +3813,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C40" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D40" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E40" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H40" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I40" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J40" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K40" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L40" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M40" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N40" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O40" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -3866,12 +3870,12 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3897,64 +3901,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C41" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D41" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E41" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I41" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J41" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K41" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L41" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M41" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N41" t="n">
         <v>32.38</v>
       </c>
       <c r="O41" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3985,64 +3987,64 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C42" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D42" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E42" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H42" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I42" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J42" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K42" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L42" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M42" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N42" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O42" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4064,78 +4066,76 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C43" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D43" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E43" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
         <v>0.17</v>
       </c>
       <c r="I43" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J43" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K43" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L43" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M43" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N43" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O43" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4148,59 +4148,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C44" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D44" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E44" t="n">
         <v>31.82</v>
       </c>
-      <c r="E44" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F44" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H44" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I44" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J44" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K44" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L44" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M44" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N44" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O44" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4208,18 +4204,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4232,55 +4228,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C45" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D45" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E45" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I45" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J45" t="n">
         <v>31.65</v>
       </c>
-      <c r="J45" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K45" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L45" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M45" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N45" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O45" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4288,18 +4288,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4314,57 +4314,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C46" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D46" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E46" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H46" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I46" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J46" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K46" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L46" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M46" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N46" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O46" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,18 +4372,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4398,57 +4398,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C47" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D47" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E47" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H47" t="n">
         <v>0.1</v>
       </c>
       <c r="I47" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J47" t="n">
         <v>31.72</v>
       </c>
       <c r="K47" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L47" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M47" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N47" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O47" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,18 +4456,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4482,57 +4482,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C48" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D48" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E48" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I48" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J48" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K48" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L48" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M48" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N48" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O48" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4543,9 +4543,9 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4566,76 +4566,80 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C49" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D49" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E49" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J49" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K49" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L49" t="n">
         <v>31.84</v>
       </c>
-      <c r="C49" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D49" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E49" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J49" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K49" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L49" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M49" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N49" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O49" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4650,71 +4654,69 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C50" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D50" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E50" t="n">
         <v>31.66</v>
       </c>
-      <c r="E50" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F50" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H50" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I50" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J50" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K50" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L50" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M50" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N50" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O50" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4731,85 +4733,79 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C51" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D51" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E51" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H51" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I51" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J51" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K51" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L51" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M51" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N51" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O51" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4822,55 +4818,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C52" t="n">
         <v>31.73</v>
       </c>
       <c r="D52" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E52" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I52" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J52" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K52" t="n">
         <v>31.57</v>
       </c>
-      <c r="K52" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L52" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M52" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N52" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O52" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,18 +4881,20 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4904,57 +4906,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C53" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D53" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E53" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H53" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I53" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J53" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K53" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L53" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M53" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N53" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O53" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4967,18 +4969,16 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4990,57 +4990,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C54" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D54" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E54" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H54" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I54" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J54" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K54" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L54" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M54" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N54" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O54" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5074,76 +5074,78 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C55" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E55" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J55" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K55" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L55" t="n">
         <v>31.72</v>
       </c>
-      <c r="C55" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D55" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E55" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I55" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J55" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K55" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L55" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M55" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N55" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O55" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5156,59 +5158,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C56" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D56" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E56" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H56" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I56" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J56" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K56" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L56" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M56" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N56" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O56" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,12 +5218,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5247,62 +5245,62 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C57" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D57" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E57" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I57" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J57" t="n">
         <v>31.49</v>
       </c>
-      <c r="E57" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I57" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J57" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K57" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L57" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M57" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N57" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O57" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
@@ -5329,67 +5327,65 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>31.5</v>
       </c>
       <c r="C58" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D58" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E58" t="n">
         <v>31.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I58" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J58" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K58" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L58" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M58" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N58" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O58" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5411,50 +5407,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C59" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D59" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E59" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I59" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J59" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K59" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L59" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M59" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N59" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O59" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5464,77 +5460,87 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C60" t="n">
         <v>31.69</v>
       </c>
       <c r="D60" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E60" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H60" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I60" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J60" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K60" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L60" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M60" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N60" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O60" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5542,30 +5548,26 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
@@ -5581,50 +5583,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C61" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D61" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J61" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K61" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L61" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M61" t="n">
         <v>31.69</v>
       </c>
-      <c r="D61" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E61" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I61" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J61" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K61" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L61" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M61" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N61" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O61" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5642,16 +5644,18 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
@@ -5660,27 +5664,27 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C62" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D62" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E62" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F62" t="n">
         <v>0.04</v>
@@ -5689,28 +5693,28 @@
         <v>0.0013</v>
       </c>
       <c r="H62" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I62" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J62" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K62" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L62" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M62" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N62" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O62" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5723,12 +5727,12 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U62" s="8" t="inlineStr">
@@ -5736,10 +5740,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
@@ -5755,47 +5757,47 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C63" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D63" t="n">
         <v>31.72</v>
       </c>
-      <c r="C63" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D63" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E63" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H63" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I63" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J63" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K63" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L63" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M63" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N63" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O63" t="n">
         <v>32.13</v>
@@ -5834,57 +5836,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C64" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D64" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E64" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F64" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H64" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I64" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J64" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K64" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L64" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M64" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N64" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O64" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5897,12 +5899,12 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -5920,60 +5922,62 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B65" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="C65" t="n">
         <v>31.86</v>
       </c>
-      <c r="C65" t="n">
-        <v>31.94</v>
-      </c>
       <c r="D65" t="n">
-        <v>31.83</v>
+        <v>31.84</v>
       </c>
       <c r="E65" t="n">
-        <v>31.86</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>0.09</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0027</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I65" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J65" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K65" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L65" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M65" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N65" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O65" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+        <v>32.05</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5981,20 +5985,16 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -6006,36 +6006,8 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>31.74</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="L66" s="13" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>32.05</v>
+          <t>弱警訊</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5936,22 +5933,22 @@
         <v>31.85</v>
       </c>
       <c r="C65" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="D65" t="n">
-        <v>31.84</v>
+        <v>31.76</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.85</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>-0.01</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>-0.0003</v>
       </c>
       <c r="H65" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I65" t="n">
         <v>31.72</v>
@@ -5974,20 +5971,20 @@
       <c r="O65" t="n">
         <v>32.05</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P65" s="6" t="n">
+        <v/>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -6004,11 +6001,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -634,71 +634,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="C2" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="D2" t="n">
-        <v>31.58</v>
+        <v>31.64</v>
       </c>
       <c r="E2" t="n">
-        <v>31.69</v>
+        <v>31.7</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I2" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J2" t="n">
         <v>31.61</v>
       </c>
       <c r="K2" t="n">
-        <v>31.64</v>
+        <v>31.63</v>
       </c>
       <c r="L2" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="M2" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N2" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="O2" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E3" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L3" t="n">
         <v>31.7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="M3" t="n">
         <v>31.77</v>
       </c>
-      <c r="D3" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I3" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K3" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L3" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M3" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N3" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O3" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -781,11 +775,13 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C4" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D4" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E4" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F4" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H4" t="n">
         <v>0.11</v>
       </c>
       <c r="I4" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J4" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K4" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L4" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M4" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N4" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O4" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,13 +857,11 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -882,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C5" t="n">
         <v>31.91</v>
       </c>
       <c r="D5" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E5" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I5" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J5" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K5" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L5" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M5" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N5" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O5" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,15 +930,13 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -957,37 +949,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C6" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D6" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E6" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J6" t="n">
         <v>31.75</v>
@@ -999,13 +995,13 @@
         <v>31.85</v>
       </c>
       <c r="M6" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N6" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O6" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,16 +1009,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1037,57 +1037,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C7" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D7" t="n">
         <v>31.79</v>
       </c>
       <c r="E7" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I7" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J7" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K7" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L7" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M7" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N7" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O7" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1130,50 +1130,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C8" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E8" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H8" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I8" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J8" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K8" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L8" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M8" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N8" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O8" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1181,21 +1181,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,59 +1205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C9" t="n">
         <v>31.96</v>
       </c>
       <c r="D9" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E9" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L9" t="n">
         <v>31.89</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I9" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J9" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K9" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L9" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M9" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N9" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O9" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1296,50 +1290,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>31.93</v>
       </c>
       <c r="C10" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D10" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E10" t="n">
         <v>31.93</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I10" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J10" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K10" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L10" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M10" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N10" t="n">
         <v>32.03</v>
       </c>
       <c r="O10" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,74 +1346,82 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C11" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D11" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H11" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J11" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K11" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L11" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M11" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N11" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O11" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,12 +1434,12 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -1445,69 +1447,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C12" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E12" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I12" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J12" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K12" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L12" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M12" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N12" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O12" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,8 +1511,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1528,10 +1526,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1541,55 +1537,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C13" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D13" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E13" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H13" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I13" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J13" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K13" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L13" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N13" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O13" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,20 +1597,16 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1632,47 +1628,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C14" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D14" t="n">
         <v>32.04</v>
       </c>
       <c r="E14" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H14" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J14" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K14" t="n">
         <v>32.02</v>
       </c>
       <c r="L14" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M14" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N14" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O14" t="n">
         <v>32.41</v>
@@ -1686,9 +1682,9 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,57 +1703,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>32.1</v>
       </c>
       <c r="C15" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D15" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E15" t="n">
         <v>32.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H15" t="n">
         <v>0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J15" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K15" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L15" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N15" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O15" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,8 +1769,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1789,42 +1787,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C16" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D16" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E16" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
         <v>31.9</v>
       </c>
       <c r="J16" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K16" t="n">
         <v>32.03</v>
@@ -1839,7 +1837,7 @@
         <v>32.23</v>
       </c>
       <c r="O16" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1850,14 +1848,14 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1871,59 +1869,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C17" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D17" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E17" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H17" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I17" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J17" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K17" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L17" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M17" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N17" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O17" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1934,15 +1928,13 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1955,55 +1947,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C18" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D18" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E18" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I18" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J18" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K18" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L18" t="n">
         <v>32.15</v>
       </c>
       <c r="M18" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N18" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O18" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,16 +2010,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2033,59 +2033,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C19" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D19" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E19" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I19" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J19" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K19" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L19" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M19" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N19" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O19" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2124,50 +2120,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D20" t="n">
         <v>32.26</v>
       </c>
-      <c r="C20" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D20" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E20" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F20" t="n">
         <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I20" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J20" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K20" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L20" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M20" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N20" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O20" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2180,12 +2176,12 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -2206,50 +2202,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C21" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D21" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E21" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I21" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J21" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K21" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L21" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M21" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N21" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O21" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2257,23 +2253,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2283,34 +2277,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C22" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D22" t="n">
         <v>32.28</v>
       </c>
-      <c r="C22" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D22" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E22" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I22" t="n">
         <v>32.09</v>
@@ -2319,19 +2317,19 @@
         <v>32.12</v>
       </c>
       <c r="K22" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L22" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M22" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N22" t="n">
         <v>32.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O22" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,21 +2337,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2363,59 +2363,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C23" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D23" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E23" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F23" t="n">
         <v>0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I23" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J23" t="n">
         <v>32.09</v>
       </c>
-      <c r="J23" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K23" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L23" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M23" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N23" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O23" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2428,18 +2424,14 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2449,55 +2441,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C24" t="n">
         <v>32.38</v>
       </c>
       <c r="D24" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E24" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I24" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J24" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K24" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L24" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M24" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N24" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O24" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2505,12 +2501,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2529,57 +2527,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C25" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D25" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E25" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I25" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J25" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K25" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L25" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M25" t="n">
         <v>32.34</v>
       </c>
-      <c r="M25" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N25" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O25" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2587,21 +2585,23 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2620,50 +2620,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C26" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D26" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E26" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J26" t="n">
         <v>32.19</v>
       </c>
       <c r="K26" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L26" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M26" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N26" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O26" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2674,9 +2674,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2684,10 +2684,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2706,50 +2704,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C27" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D27" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E27" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H27" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I27" t="n">
         <v>32.16</v>
       </c>
       <c r="J27" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K27" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L27" t="n">
         <v>32.33</v>
       </c>
       <c r="M27" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N27" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O27" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,18 +2758,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2781,59 +2781,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C28" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D28" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E28" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H28" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I28" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J28" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K28" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L28" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M28" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N28" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O28" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2844,14 +2840,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -2867,55 +2863,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C29" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D29" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E29" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H29" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J29" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K29" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L29" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M29" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N29" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O29" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2923,12 +2923,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2936,10 +2938,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2958,50 +2958,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C30" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D30" t="n">
         <v>32.21</v>
       </c>
       <c r="E30" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H30" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I30" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J30" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K30" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L30" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M30" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N30" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O30" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3011,18 +3011,16 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3037,57 +3035,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C31" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D31" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E31" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H31" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I31" t="n">
         <v>31.93</v>
       </c>
       <c r="J31" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K31" t="n">
         <v>32.15</v>
       </c>
-      <c r="K31" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L31" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M31" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N31" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O31" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3095,18 +3093,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3128,69 +3126,73 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>32.4</v>
       </c>
       <c r="C32" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D32" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E32" t="n">
         <v>32.4</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I32" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J32" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K32" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L32" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M32" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N32" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O32" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3205,62 +3207,60 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C33" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D33" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E33" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F33" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H33" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I33" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J33" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K33" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L33" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M33" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N33" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O33" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3293,57 +3293,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C34" t="n">
         <v>32.31</v>
       </c>
       <c r="D34" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E34" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H34" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I34" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J34" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K34" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L34" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M34" t="n">
         <v>32.33</v>
       </c>
-      <c r="M34" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N34" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O34" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3386,67 +3386,63 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C35" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D35" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E35" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H35" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J35" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K35" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L35" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M35" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N35" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O35" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3465,57 +3461,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C36" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D36" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E36" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H36" t="n">
         <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J36" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K36" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L36" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M36" t="n">
         <v>32.29</v>
       </c>
       <c r="N36" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O36" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,13 +3522,15 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3554,35 +3552,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C37" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D37" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E37" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I37" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J37" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K37" t="n">
         <v>32.18</v>
@@ -3591,13 +3589,13 @@
         <v>32.23</v>
       </c>
       <c r="M37" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N37" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O37" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,18 +3603,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3631,63 +3629,67 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C38" t="n">
         <v>32.21</v>
       </c>
-      <c r="C38" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D38" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E38" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H38" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I38" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J38" t="n">
         <v>32.12</v>
       </c>
       <c r="K38" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L38" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M38" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N38" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O38" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3722,50 +3724,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C39" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D39" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E39" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H39" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I39" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J39" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K39" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L39" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M39" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N39" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O39" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -3779,12 +3781,12 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3810,64 +3812,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C40" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D40" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E40" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H40" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I40" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J40" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K40" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L40" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M40" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N40" t="n">
         <v>32.38</v>
       </c>
       <c r="O40" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3898,64 +3898,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C41" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D41" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E41" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H41" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I41" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J41" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K41" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L41" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M41" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N41" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O41" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3977,78 +3977,76 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C42" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D42" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E42" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H42" t="n">
         <v>0.17</v>
       </c>
       <c r="I42" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J42" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K42" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L42" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M42" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N42" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O42" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4061,59 +4059,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C43" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D43" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E43" t="n">
         <v>31.82</v>
       </c>
-      <c r="E43" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F43" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H43" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J43" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K43" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L43" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M43" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N43" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O43" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4121,18 +4115,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4145,55 +4139,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C44" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D44" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E44" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I44" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J44" t="n">
         <v>31.65</v>
       </c>
-      <c r="J44" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K44" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L44" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M44" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N44" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O44" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4201,18 +4199,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4227,57 +4225,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C45" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D45" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E45" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H45" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J45" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K45" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L45" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M45" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N45" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O45" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4285,18 +4283,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4311,57 +4309,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C46" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D46" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E46" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H46" t="n">
         <v>0.1</v>
       </c>
       <c r="I46" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J46" t="n">
         <v>31.72</v>
       </c>
       <c r="K46" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L46" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M46" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N46" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O46" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4369,18 +4367,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4395,57 +4393,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C47" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D47" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E47" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I47" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J47" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K47" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L47" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M47" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N47" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O47" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,9 +4454,9 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4479,76 +4477,80 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C48" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D48" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E48" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J48" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K48" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L48" t="n">
         <v>31.84</v>
       </c>
-      <c r="C48" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D48" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E48" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I48" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K48" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L48" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M48" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N48" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O48" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4563,71 +4565,69 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C49" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D49" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E49" t="n">
         <v>31.66</v>
       </c>
-      <c r="E49" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F49" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H49" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I49" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J49" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K49" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L49" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M49" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N49" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4644,85 +4644,79 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C50" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D50" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E50" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I50" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J50" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K50" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L50" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M50" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N50" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O50" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4735,55 +4729,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C51" t="n">
         <v>31.73</v>
       </c>
       <c r="D51" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E51" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I51" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J51" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K51" t="n">
         <v>31.57</v>
       </c>
-      <c r="K51" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L51" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M51" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N51" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O51" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4794,18 +4792,20 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4817,57 +4817,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C52" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D52" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E52" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H52" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I52" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J52" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K52" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L52" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M52" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N52" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O52" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,18 +4880,16 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4903,57 +4901,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C53" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D53" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E53" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H53" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I53" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J53" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K53" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L53" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M53" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N53" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O53" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4966,12 +4964,12 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4987,76 +4985,78 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C54" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D54" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E54" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I54" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J54" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K54" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L54" t="n">
         <v>31.72</v>
       </c>
-      <c r="C54" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D54" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E54" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I54" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J54" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K54" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L54" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M54" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N54" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O54" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5069,59 +5069,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C55" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D55" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E55" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H55" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I55" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J55" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K55" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L55" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M55" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N55" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O55" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5133,12 +5129,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5160,62 +5156,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C56" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D56" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E56" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I56" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J56" t="n">
         <v>31.49</v>
       </c>
-      <c r="E56" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I56" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J56" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K56" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L56" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M56" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N56" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O56" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5242,67 +5238,65 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>31.5</v>
       </c>
       <c r="C57" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D57" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E57" t="n">
         <v>31.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H57" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I57" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J57" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K57" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L57" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M57" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N57" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O57" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5324,50 +5318,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C58" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D58" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E58" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I58" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J58" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K58" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L58" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M58" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N58" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O58" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5377,77 +5371,87 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C59" t="n">
         <v>31.69</v>
       </c>
       <c r="D59" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E59" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H59" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I59" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J59" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K59" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L59" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M59" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N59" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O59" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5455,30 +5459,26 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
@@ -5494,50 +5494,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C60" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E60" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I60" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J60" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K60" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L60" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M60" t="n">
         <v>31.69</v>
       </c>
-      <c r="D60" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E60" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I60" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K60" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L60" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M60" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N60" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O60" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5555,16 +5555,18 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
@@ -5573,27 +5575,27 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C61" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D61" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E61" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F61" t="n">
         <v>0.04</v>
@@ -5602,28 +5604,28 @@
         <v>0.0013</v>
       </c>
       <c r="H61" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I61" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J61" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K61" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L61" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M61" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N61" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O61" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5636,12 +5638,12 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U61" s="8" t="inlineStr">
@@ -5649,10 +5651,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
@@ -5668,47 +5668,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C62" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D62" t="n">
         <v>31.72</v>
       </c>
-      <c r="C62" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D62" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E62" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H62" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I62" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J62" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K62" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L62" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M62" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N62" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O62" t="n">
         <v>32.13</v>
@@ -5747,57 +5747,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C63" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D63" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E63" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F63" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H63" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I63" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J63" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K63" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L63" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M63" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N63" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O63" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U63" s="8" t="inlineStr">
@@ -5833,57 +5833,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C64" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D64" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E64" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F64" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.09</v>
       </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I64" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J64" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K64" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L64" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M64" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N64" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O64" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5891,23 +5891,21 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5917,74 +5915,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C65" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D65" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E65" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H65" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I65" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J65" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K65" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L65" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M65" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N65" t="n">
         <v>31.96</v>
       </c>
       <c r="O65" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -6001,7 +5997,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="K2" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="L2" t="n">
         <v>31.7</v>
       </c>
-      <c r="C2" t="n">
+      <c r="M2" t="n">
         <v>31.77</v>
       </c>
-      <c r="D2" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="K2" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="L2" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="M2" t="n">
-        <v>31.74</v>
-      </c>
       <c r="N2" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="O2" t="n">
-        <v>31.79</v>
+        <v>31.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +698,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,50 +719,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C3" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D3" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E3" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F3" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H3" t="n">
         <v>0.11</v>
       </c>
       <c r="I3" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J3" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K3" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L3" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M3" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N3" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O3" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,13 +780,11 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -796,50 +799,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C4" t="n">
         <v>31.91</v>
       </c>
       <c r="D4" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E4" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I4" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J4" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K4" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L4" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M4" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N4" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O4" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -850,15 +853,13 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -871,37 +872,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C5" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D5" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E5" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J5" t="n">
         <v>31.75</v>
@@ -913,13 +918,13 @@
         <v>31.85</v>
       </c>
       <c r="M5" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N5" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O5" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -927,16 +932,20 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -951,57 +960,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C6" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D6" t="n">
         <v>31.79</v>
       </c>
       <c r="E6" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J6" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K6" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L6" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M6" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N6" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O6" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1011,12 +1020,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1044,50 +1053,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C7" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E7" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I7" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J7" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K7" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L7" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M7" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N7" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O7" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1095,21 +1104,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1121,59 +1128,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C8" t="n">
         <v>31.96</v>
       </c>
       <c r="D8" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E8" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L8" t="n">
         <v>31.89</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K8" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L8" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M8" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N8" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O8" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1210,50 +1213,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>31.93</v>
       </c>
       <c r="C9" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D9" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E9" t="n">
         <v>31.93</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I9" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J9" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K9" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L9" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M9" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N9" t="n">
         <v>32.03</v>
       </c>
       <c r="O9" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,74 +1269,82 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C10" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D10" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H10" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J10" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K10" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L10" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M10" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N10" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O10" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1346,12 +1357,12 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -1359,69 +1370,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E11" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I11" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J11" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K11" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L11" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M11" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N11" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O11" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,8 +1434,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1442,10 +1449,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1455,55 +1460,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D12" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E12" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I12" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J12" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K12" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L12" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M12" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N12" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O12" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1511,20 +1520,16 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1546,47 +1551,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C13" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D13" t="n">
         <v>32.04</v>
       </c>
       <c r="E13" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H13" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J13" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K13" t="n">
         <v>32.02</v>
       </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M13" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N13" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O13" t="n">
         <v>32.41</v>
@@ -1600,9 +1605,9 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1621,57 +1626,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>32.1</v>
       </c>
       <c r="C14" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D14" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E14" t="n">
         <v>32.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
         <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J14" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K14" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L14" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M14" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N14" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O14" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,8 +1692,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,42 +1710,42 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C15" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D15" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E15" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H15" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
         <v>31.9</v>
       </c>
       <c r="J15" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K15" t="n">
         <v>32.03</v>
@@ -1753,7 +1760,7 @@
         <v>32.23</v>
       </c>
       <c r="O15" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,14 +1771,14 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1785,59 +1792,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C16" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D16" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E16" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H16" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I16" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J16" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K16" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M16" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N16" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O16" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,15 +1851,13 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1869,55 +1870,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C17" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D17" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E17" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J17" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K17" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L17" t="n">
         <v>32.15</v>
       </c>
       <c r="M17" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N17" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O17" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1928,16 +1933,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1947,59 +1956,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C18" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D18" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E18" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I18" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J18" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K18" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L18" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M18" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N18" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O18" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2038,50 +2043,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D19" t="n">
         <v>32.26</v>
       </c>
-      <c r="C19" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E19" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F19" t="n">
         <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H19" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I19" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J19" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K19" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L19" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M19" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N19" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O19" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2094,12 +2099,12 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -2120,50 +2125,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C20" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D20" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E20" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J20" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K20" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L20" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M20" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N20" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O20" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2171,23 +2176,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2197,34 +2200,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D21" t="n">
         <v>32.28</v>
       </c>
-      <c r="C21" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D21" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E21" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I21" t="n">
         <v>32.09</v>
@@ -2233,19 +2240,19 @@
         <v>32.12</v>
       </c>
       <c r="K21" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L21" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M21" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N21" t="n">
         <v>32.4</v>
       </c>
-      <c r="N21" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O21" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2253,21 +2260,23 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2277,59 +2286,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C22" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D22" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E22" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F22" t="n">
         <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J22" t="n">
         <v>32.09</v>
       </c>
-      <c r="J22" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K22" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L22" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M22" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N22" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O22" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2342,18 +2347,14 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2363,55 +2364,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C23" t="n">
         <v>32.38</v>
       </c>
       <c r="D23" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E23" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H23" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I23" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J23" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K23" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L23" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M23" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N23" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O23" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2419,12 +2424,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2443,57 +2450,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C24" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D24" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E24" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I24" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J24" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K24" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L24" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M24" t="n">
         <v>32.34</v>
       </c>
-      <c r="M24" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N24" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O24" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2501,21 +2508,23 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2534,50 +2543,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C25" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D25" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E25" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J25" t="n">
         <v>32.19</v>
       </c>
       <c r="K25" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L25" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M25" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N25" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O25" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2588,9 +2597,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2598,10 +2607,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2620,50 +2627,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C26" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D26" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E26" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H26" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I26" t="n">
         <v>32.16</v>
       </c>
       <c r="J26" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K26" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L26" t="n">
         <v>32.33</v>
       </c>
       <c r="M26" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N26" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O26" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2674,18 +2681,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2695,59 +2704,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C27" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D27" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E27" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H27" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I27" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J27" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K27" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L27" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M27" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N27" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O27" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2758,14 +2763,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
@@ -2781,55 +2786,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C28" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D28" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E28" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H28" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I28" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J28" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K28" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L28" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M28" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N28" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O28" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2837,12 +2846,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2850,10 +2861,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2872,50 +2881,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C29" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D29" t="n">
         <v>32.21</v>
       </c>
       <c r="E29" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J29" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K29" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L29" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M29" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N29" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O29" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2925,18 +2934,16 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2951,57 +2958,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C30" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D30" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E30" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H30" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I30" t="n">
         <v>31.93</v>
       </c>
       <c r="J30" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K30" t="n">
         <v>32.15</v>
       </c>
-      <c r="K30" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L30" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M30" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N30" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O30" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3009,18 +3016,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3042,69 +3049,73 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>32.4</v>
       </c>
       <c r="C31" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D31" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E31" t="n">
         <v>32.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J31" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K31" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L31" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M31" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N31" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O31" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3119,62 +3130,60 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C32" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D32" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E32" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F32" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H32" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J32" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K32" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L32" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M32" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N32" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O32" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
@@ -3183,12 +3192,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3207,57 +3216,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C33" t="n">
         <v>32.31</v>
       </c>
       <c r="D33" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E33" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I33" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J33" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K33" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L33" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M33" t="n">
         <v>32.33</v>
       </c>
-      <c r="M33" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N33" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O33" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3300,67 +3309,63 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C34" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D34" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E34" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H34" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I34" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J34" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K34" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L34" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M34" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N34" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O34" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3379,57 +3384,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C35" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D35" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E35" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H35" t="n">
         <v>0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J35" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K35" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L35" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M35" t="n">
         <v>32.29</v>
       </c>
       <c r="N35" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O35" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3440,13 +3445,15 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3468,35 +3475,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C36" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D36" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E36" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J36" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K36" t="n">
         <v>32.18</v>
@@ -3505,13 +3512,13 @@
         <v>32.23</v>
       </c>
       <c r="M36" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N36" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O36" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3519,18 +3526,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3545,63 +3552,67 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C37" t="n">
         <v>32.21</v>
       </c>
-      <c r="C37" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D37" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E37" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I37" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J37" t="n">
         <v>32.12</v>
       </c>
       <c r="K37" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L37" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M37" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N37" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O37" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3636,50 +3647,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C38" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D38" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E38" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H38" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I38" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J38" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K38" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L38" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M38" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N38" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O38" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -3693,12 +3704,12 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3724,64 +3735,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C39" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D39" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E39" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H39" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I39" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J39" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K39" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L39" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M39" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N39" t="n">
         <v>32.38</v>
       </c>
       <c r="O39" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3812,64 +3821,64 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C40" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D40" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E40" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H40" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I40" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J40" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K40" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L40" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M40" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N40" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O40" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3891,78 +3900,76 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C41" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D41" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E41" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H41" t="n">
         <v>0.17</v>
       </c>
       <c r="I41" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J41" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K41" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L41" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M41" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N41" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O41" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3975,59 +3982,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C42" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D42" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E42" t="n">
         <v>31.82</v>
       </c>
-      <c r="E42" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F42" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H42" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J42" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K42" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L42" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M42" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N42" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O42" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,18 +4038,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4059,55 +4062,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C43" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E43" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I43" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J43" t="n">
         <v>31.65</v>
       </c>
-      <c r="J43" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K43" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L43" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M43" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N43" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O43" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,18 +4122,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4141,57 +4148,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C44" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D44" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E44" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H44" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J44" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K44" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L44" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M44" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N44" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O44" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,18 +4206,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4225,57 +4232,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C45" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D45" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E45" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H45" t="n">
         <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J45" t="n">
         <v>31.72</v>
       </c>
       <c r="K45" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L45" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M45" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N45" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O45" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4283,18 +4290,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4309,57 +4316,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C46" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D46" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E46" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I46" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J46" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K46" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L46" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M46" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N46" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O46" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,9 +4377,9 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4393,76 +4400,80 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C47" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D47" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E47" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J47" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K47" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L47" t="n">
         <v>31.84</v>
       </c>
-      <c r="C47" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D47" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E47" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I47" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K47" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L47" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M47" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N47" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O47" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4477,71 +4488,69 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C48" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D48" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E48" t="n">
         <v>31.66</v>
       </c>
-      <c r="E48" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F48" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H48" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I48" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J48" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K48" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L48" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M48" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N48" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4558,85 +4567,79 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C49" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D49" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E49" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I49" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J49" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K49" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L49" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M49" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N49" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O49" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4649,55 +4652,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C50" t="n">
         <v>31.73</v>
       </c>
       <c r="D50" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E50" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I50" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J50" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K50" t="n">
         <v>31.57</v>
       </c>
-      <c r="K50" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L50" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M50" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N50" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O50" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4708,18 +4715,20 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4731,57 +4740,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C51" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D51" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E51" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H51" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I51" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J51" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K51" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L51" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M51" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N51" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O51" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4794,18 +4803,16 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4817,57 +4824,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C52" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D52" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E52" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H52" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I52" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J52" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K52" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L52" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M52" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N52" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O52" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,12 +4887,12 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4901,76 +4908,78 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I53" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J53" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K53" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L53" t="n">
         <v>31.72</v>
       </c>
-      <c r="C53" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D53" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E53" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I53" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J53" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K53" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L53" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M53" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N53" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O53" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4983,59 +4992,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C54" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D54" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E54" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H54" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I54" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J54" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K54" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L54" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M54" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N54" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O54" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5047,12 +5052,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5074,62 +5079,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C55" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D55" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E55" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I55" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J55" t="n">
         <v>31.49</v>
       </c>
-      <c r="E55" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I55" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J55" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K55" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L55" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M55" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N55" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O55" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5156,67 +5161,65 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>31.5</v>
       </c>
       <c r="C56" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D56" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E56" t="n">
         <v>31.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H56" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I56" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J56" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K56" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L56" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M56" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N56" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O56" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5238,50 +5241,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C57" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D57" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E57" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I57" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J57" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K57" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L57" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M57" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N57" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O57" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5291,77 +5294,87 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C58" t="n">
         <v>31.69</v>
       </c>
       <c r="D58" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E58" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H58" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I58" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J58" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K58" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L58" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M58" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N58" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O58" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5369,30 +5382,26 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
@@ -5408,50 +5417,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C59" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D59" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E59" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J59" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K59" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L59" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M59" t="n">
         <v>31.69</v>
       </c>
-      <c r="D59" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E59" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I59" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J59" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K59" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L59" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M59" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N59" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O59" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5469,16 +5478,18 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
@@ -5487,27 +5498,27 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C60" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D60" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E60" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F60" t="n">
         <v>0.04</v>
@@ -5516,28 +5527,28 @@
         <v>0.0013</v>
       </c>
       <c r="H60" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I60" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J60" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K60" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L60" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M60" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N60" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O60" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5550,12 +5561,12 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U60" s="8" t="inlineStr">
@@ -5563,10 +5574,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
@@ -5582,47 +5591,47 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C61" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D61" t="n">
         <v>31.72</v>
       </c>
-      <c r="C61" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D61" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E61" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F61" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H61" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I61" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J61" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K61" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L61" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M61" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N61" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O61" t="n">
         <v>32.13</v>
@@ -5661,57 +5670,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C62" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D62" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E62" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H62" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I62" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J62" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K62" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L62" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M62" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N62" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O62" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5724,12 +5733,12 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U62" s="8" t="inlineStr">
@@ -5747,57 +5756,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C63" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D63" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E63" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F63" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H63" t="n">
         <v>0.09</v>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I63" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J63" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K63" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L63" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M63" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N63" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O63" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5805,23 +5814,21 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5831,74 +5838,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C64" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D64" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E64" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H64" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I64" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J64" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K64" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L64" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M64" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N64" t="n">
         <v>31.96</v>
       </c>
       <c r="O64" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5915,58 +5920,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.81</v>
+        <v>31.72</v>
       </c>
       <c r="C65" t="n">
-        <v>31.86</v>
+        <v>31.75</v>
       </c>
       <c r="D65" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E65" t="n">
-        <v>31.81</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>-0.04</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0013</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I65" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J65" t="n">
         <v>31.67</v>
       </c>
-      <c r="J65" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K65" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L65" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M65" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N65" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O65" t="n">
-        <v>31.95</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+        <v>32.01</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
@@ -5975,12 +5986,12 @@
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5997,11 +6008,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5933,22 +5930,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.72</v>
+        <v>31.74</v>
       </c>
       <c r="C65" t="n">
-        <v>31.75</v>
+        <v>31.74</v>
       </c>
       <c r="D65" t="n">
         <v>31.6</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.74</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>-0.0022</v>
       </c>
       <c r="H65" t="n">
         <v>0.15</v>
@@ -5974,24 +5971,22 @@
       <c r="O65" t="n">
         <v>32.01</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="C2" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D2" t="n">
-        <v>31.77</v>
+        <v>31.79</v>
       </c>
       <c r="E2" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="F2" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="H2" t="n">
         <v>0.11</v>
       </c>
       <c r="I2" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="J2" t="n">
-        <v>31.57</v>
+        <v>31.7</v>
       </c>
       <c r="K2" t="n">
-        <v>31.64</v>
+        <v>31.76</v>
       </c>
       <c r="L2" t="n">
-        <v>31.7</v>
+        <v>31.81</v>
       </c>
       <c r="M2" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="N2" t="n">
-        <v>31.83</v>
+        <v>31.91</v>
       </c>
       <c r="O2" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,13 +698,11 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +717,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C3" t="n">
         <v>31.91</v>
       </c>
       <c r="D3" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E3" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J3" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K3" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L3" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M3" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N3" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O3" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,15 +771,13 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -791,37 +790,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C4" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D4" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E4" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J4" t="n">
         <v>31.75</v>
@@ -833,13 +836,13 @@
         <v>31.85</v>
       </c>
       <c r="M4" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N4" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O4" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,16 +850,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -871,57 +878,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C5" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D5" t="n">
         <v>31.79</v>
       </c>
       <c r="E5" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I5" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J5" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K5" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L5" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M5" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N5" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O5" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,12 +938,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -964,50 +971,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C6" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E6" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J6" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K6" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L6" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M6" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N6" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O6" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,21 +1022,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1041,59 +1046,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C7" t="n">
         <v>31.96</v>
       </c>
       <c r="D7" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E7" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I7" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L7" t="n">
         <v>31.89</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I7" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K7" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L7" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M7" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N7" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O7" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1130,50 +1131,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>31.93</v>
       </c>
       <c r="C8" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E8" t="n">
         <v>31.93</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I8" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J8" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K8" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L8" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M8" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N8" t="n">
         <v>32.03</v>
       </c>
       <c r="O8" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,74 +1187,82 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C9" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D9" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H9" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J9" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K9" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L9" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M9" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N9" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O9" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,12 +1275,12 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -1279,69 +1288,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C10" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E10" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F10" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I10" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J10" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K10" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L10" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M10" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N10" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O10" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,8 +1352,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1362,10 +1367,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1375,55 +1378,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C11" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D11" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E11" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H11" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I11" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J11" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K11" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L11" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M11" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N11" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O11" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,20 +1438,16 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1466,47 +1469,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C12" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D12" t="n">
         <v>32.04</v>
       </c>
       <c r="E12" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J12" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K12" t="n">
         <v>32.02</v>
       </c>
       <c r="L12" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M12" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N12" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O12" t="n">
         <v>32.41</v>
@@ -1520,9 +1523,9 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1541,57 +1544,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>32.1</v>
       </c>
       <c r="C13" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D13" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E13" t="n">
         <v>32.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H13" t="n">
         <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J13" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K13" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L13" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N13" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O13" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,8 +1610,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1623,42 +1628,42 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C14" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D14" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E14" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
         <v>31.9</v>
       </c>
       <c r="J14" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K14" t="n">
         <v>32.03</v>
@@ -1673,7 +1678,7 @@
         <v>32.23</v>
       </c>
       <c r="O14" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,14 +1689,14 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1705,59 +1710,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C15" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D15" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E15" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H15" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I15" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J15" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K15" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M15" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N15" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O15" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,15 +1769,13 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1789,55 +1788,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C16" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D16" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E16" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J16" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K16" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L16" t="n">
         <v>32.15</v>
       </c>
       <c r="M16" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N16" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O16" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,16 +1851,20 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1867,59 +1874,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C17" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D17" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E17" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H17" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I17" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J17" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K17" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L17" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N17" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O17" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1958,50 +1961,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C18" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D18" t="n">
         <v>32.26</v>
       </c>
-      <c r="C18" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D18" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E18" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F18" t="n">
         <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I18" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J18" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K18" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L18" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N18" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O18" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,12 +2017,12 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -2040,50 +2043,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C19" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D19" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E19" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J19" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K19" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L19" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M19" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N19" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O19" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,23 +2094,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2117,34 +2118,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D20" t="n">
         <v>32.28</v>
       </c>
-      <c r="C20" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D20" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E20" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
         <v>32.09</v>
@@ -2153,19 +2158,19 @@
         <v>32.12</v>
       </c>
       <c r="K20" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L20" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M20" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N20" t="n">
         <v>32.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O20" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2173,21 +2178,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2197,59 +2204,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C21" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D21" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E21" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F21" t="n">
         <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I21" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J21" t="n">
         <v>32.09</v>
       </c>
-      <c r="J21" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K21" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L21" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M21" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N21" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O21" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2262,18 +2265,14 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2283,55 +2282,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C22" t="n">
         <v>32.38</v>
       </c>
       <c r="D22" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E22" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I22" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J22" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K22" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L22" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M22" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N22" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O22" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,12 +2342,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2363,57 +2368,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C23" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D23" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E23" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I23" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J23" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K23" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L23" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M23" t="n">
         <v>32.34</v>
       </c>
-      <c r="M23" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N23" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2421,21 +2426,23 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2454,50 +2461,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C24" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D24" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E24" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I24" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J24" t="n">
         <v>32.19</v>
       </c>
       <c r="K24" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L24" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M24" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N24" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O24" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2508,9 +2515,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2518,10 +2525,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2540,50 +2545,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C25" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D25" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E25" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I25" t="n">
         <v>32.16</v>
       </c>
       <c r="J25" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K25" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L25" t="n">
         <v>32.33</v>
       </c>
       <c r="M25" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N25" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O25" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2594,18 +2599,20 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2615,59 +2622,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C26" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D26" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E26" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H26" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I26" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J26" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K26" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L26" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M26" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N26" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O26" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2678,14 +2681,14 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -2701,55 +2704,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C27" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D27" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E27" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H27" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J27" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K27" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L27" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M27" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N27" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O27" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2757,12 +2764,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2770,10 +2779,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2792,50 +2799,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C28" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D28" t="n">
         <v>32.21</v>
       </c>
       <c r="E28" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H28" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I28" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J28" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K28" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L28" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M28" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N28" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O28" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2845,18 +2852,16 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2871,57 +2876,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C29" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D29" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E29" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H29" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I29" t="n">
         <v>31.93</v>
       </c>
       <c r="J29" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K29" t="n">
         <v>32.15</v>
       </c>
-      <c r="K29" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L29" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M29" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N29" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O29" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2929,18 +2934,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2962,69 +2967,73 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>32.4</v>
       </c>
       <c r="C30" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D30" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E30" t="n">
         <v>32.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I30" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J30" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K30" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L30" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M30" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N30" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O30" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3039,62 +3048,60 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C31" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D31" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E31" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F31" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I31" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J31" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K31" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L31" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M31" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N31" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O31" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
@@ -3103,12 +3110,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3127,57 +3134,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C32" t="n">
         <v>32.31</v>
       </c>
       <c r="D32" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E32" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I32" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J32" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K32" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L32" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M32" t="n">
         <v>32.33</v>
       </c>
-      <c r="M32" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N32" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O32" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,67 +3227,63 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C33" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D33" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E33" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H33" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J33" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K33" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L33" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M33" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N33" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O33" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3299,57 +3302,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C34" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D34" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E34" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H34" t="n">
         <v>0.1</v>
       </c>
       <c r="I34" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J34" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K34" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L34" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M34" t="n">
         <v>32.29</v>
       </c>
       <c r="N34" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O34" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3360,13 +3363,15 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3388,35 +3393,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C35" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D35" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E35" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J35" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K35" t="n">
         <v>32.18</v>
@@ -3425,13 +3430,13 @@
         <v>32.23</v>
       </c>
       <c r="M35" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N35" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O35" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,18 +3444,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3465,63 +3470,67 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C36" t="n">
         <v>32.21</v>
       </c>
-      <c r="C36" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D36" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E36" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I36" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J36" t="n">
         <v>32.12</v>
       </c>
       <c r="K36" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L36" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M36" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N36" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O36" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3556,50 +3565,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C37" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D37" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E37" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H37" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I37" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J37" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K37" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L37" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M37" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N37" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O37" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -3613,12 +3622,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3644,64 +3653,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C38" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D38" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E38" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H38" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I38" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J38" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K38" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L38" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M38" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N38" t="n">
         <v>32.38</v>
       </c>
       <c r="O38" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3732,64 +3739,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C39" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D39" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E39" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H39" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I39" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J39" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K39" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L39" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M39" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N39" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O39" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3811,78 +3818,76 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C40" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D40" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E40" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H40" t="n">
         <v>0.17</v>
       </c>
       <c r="I40" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J40" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K40" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L40" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M40" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N40" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O40" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3895,59 +3900,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C41" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D41" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E41" t="n">
         <v>31.82</v>
       </c>
-      <c r="E41" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F41" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H41" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I41" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J41" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K41" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L41" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M41" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N41" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O41" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,18 +3956,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3979,55 +3980,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C42" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D42" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E42" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I42" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J42" t="n">
         <v>31.65</v>
       </c>
-      <c r="J42" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K42" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L42" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M42" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N42" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O42" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,18 +4040,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4061,57 +4066,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C43" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D43" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E43" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H43" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J43" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K43" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L43" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M43" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N43" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O43" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4119,18 +4124,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4145,57 +4150,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C44" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D44" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E44" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H44" t="n">
         <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J44" t="n">
         <v>31.72</v>
       </c>
       <c r="K44" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L44" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M44" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N44" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O44" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4203,18 +4208,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4229,57 +4234,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C45" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D45" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E45" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I45" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J45" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K45" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L45" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M45" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N45" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O45" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4290,9 +4295,9 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4313,76 +4318,80 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C46" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E46" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L46" t="n">
         <v>31.84</v>
       </c>
-      <c r="C46" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D46" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E46" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I46" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K46" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L46" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M46" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N46" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O46" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4397,71 +4406,69 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C47" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D47" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E47" t="n">
         <v>31.66</v>
       </c>
-      <c r="E47" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F47" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H47" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I47" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J47" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K47" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L47" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M47" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N47" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4478,85 +4485,79 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C48" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D48" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E48" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H48" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I48" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J48" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K48" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L48" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M48" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N48" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O48" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4569,55 +4570,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C49" t="n">
         <v>31.73</v>
       </c>
       <c r="D49" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E49" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I49" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J49" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K49" t="n">
         <v>31.57</v>
       </c>
-      <c r="K49" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L49" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M49" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N49" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O49" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4628,18 +4633,20 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4651,57 +4658,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C50" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D50" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E50" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H50" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I50" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J50" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K50" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L50" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M50" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N50" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O50" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4714,18 +4721,16 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4737,57 +4742,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C51" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D51" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E51" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H51" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I51" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J51" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K51" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L51" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M51" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N51" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O51" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4800,12 +4805,12 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4821,76 +4826,78 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C52" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D52" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I52" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J52" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K52" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L52" t="n">
         <v>31.72</v>
       </c>
-      <c r="C52" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D52" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E52" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I52" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J52" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K52" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L52" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M52" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N52" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O52" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4903,59 +4910,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C53" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D53" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E53" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H53" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I53" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J53" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K53" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L53" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M53" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N53" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O53" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4967,12 +4970,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4994,62 +4997,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C54" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D54" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E54" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J54" t="n">
         <v>31.49</v>
       </c>
-      <c r="E54" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I54" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J54" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K54" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L54" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M54" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N54" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O54" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5076,67 +5079,65 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>31.5</v>
       </c>
       <c r="C55" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D55" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E55" t="n">
         <v>31.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H55" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I55" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J55" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K55" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L55" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M55" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N55" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O55" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5158,50 +5159,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C56" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D56" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E56" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H56" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I56" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J56" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K56" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L56" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M56" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N56" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O56" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,77 +5212,87 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C57" t="n">
         <v>31.69</v>
       </c>
       <c r="D57" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E57" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H57" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I57" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J57" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K57" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L57" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M57" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N57" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O57" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5289,30 +5300,26 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
@@ -5328,50 +5335,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C58" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D58" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E58" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I58" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J58" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K58" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L58" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M58" t="n">
         <v>31.69</v>
       </c>
-      <c r="D58" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E58" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I58" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J58" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K58" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L58" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M58" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N58" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O58" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5389,16 +5396,18 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
@@ -5407,27 +5416,27 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C59" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D59" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E59" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F59" t="n">
         <v>0.04</v>
@@ -5436,28 +5445,28 @@
         <v>0.0013</v>
       </c>
       <c r="H59" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I59" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J59" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K59" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L59" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M59" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N59" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O59" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5470,12 +5479,12 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U59" s="8" t="inlineStr">
@@ -5483,10 +5492,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
@@ -5502,47 +5509,47 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C60" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D60" t="n">
         <v>31.72</v>
       </c>
-      <c r="C60" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D60" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E60" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F60" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H60" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I60" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J60" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K60" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L60" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M60" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N60" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O60" t="n">
         <v>32.13</v>
@@ -5581,57 +5588,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C61" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D61" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E61" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H61" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I61" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J61" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K61" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L61" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M61" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N61" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O61" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5644,12 +5651,12 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="inlineStr">
@@ -5667,57 +5674,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C62" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D62" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E62" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F62" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H62" t="n">
         <v>0.09</v>
       </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I62" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J62" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K62" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L62" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M62" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N62" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O62" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5725,23 +5732,21 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5751,74 +5756,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C63" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D63" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E63" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H63" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I63" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J63" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K63" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L63" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M63" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N63" t="n">
         <v>31.96</v>
       </c>
       <c r="O63" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5835,55 +5838,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C64" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D64" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E64" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H64" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I64" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J64" t="n">
         <v>31.67</v>
       </c>
-      <c r="J64" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K64" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L64" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M64" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N64" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O64" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5917,76 +5924,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.74</v>
+        <v>31.66</v>
       </c>
       <c r="C65" t="n">
-        <v>31.74</v>
+        <v>31.7</v>
       </c>
       <c r="D65" t="n">
-        <v>31.6</v>
+        <v>31.63</v>
       </c>
       <c r="E65" t="n">
-        <v>31.74</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>-0.07000000000000001</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0022</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J65" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K65" t="n">
         <v>31.67</v>
       </c>
-      <c r="K65" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L65" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M65" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N65" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O65" t="n">
         <v>31.89</v>
       </c>
-      <c r="N65" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O65" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -6003,7 +6006,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5951,7 +5951,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I65" t="n">
         <v>31.45</v>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5936,7 +5936,7 @@
         <v>31.66</v>
       </c>
       <c r="C65" t="n">
-        <v>31.7</v>
+        <v>31.71</v>
       </c>
       <c r="D65" t="n">
         <v>31.63</v>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5936,7 +5936,7 @@
         <v>31.66</v>
       </c>
       <c r="C65" t="n">
-        <v>31.71</v>
+        <v>31.73</v>
       </c>
       <c r="D65" t="n">
         <v>31.63</v>
@@ -5951,7 +5951,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I65" t="n">
         <v>31.45</v>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -5936,7 +5936,7 @@
         <v>31.66</v>
       </c>
       <c r="C65" t="n">
-        <v>31.73</v>
+        <v>31.76</v>
       </c>
       <c r="D65" t="n">
         <v>31.63</v>
@@ -5951,7 +5951,7 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I65" t="n">
         <v>31.45</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5933,25 +5930,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="C65" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="D65" t="n">
-        <v>31.63</v>
+        <v>31.64</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>31.68</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>-0.06</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>-0.0019</v>
       </c>
       <c r="H65" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I65" t="n">
         <v>31.45</v>
@@ -5974,22 +5971,20 @@
       <c r="O65" t="n">
         <v>31.89</v>
       </c>
-      <c r="P65" s="6" t="inlineStr">
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="C2" t="n">
         <v>31.91</v>
       </c>
       <c r="D2" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I2" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="J2" t="n">
-        <v>31.7</v>
+        <v>31.75</v>
       </c>
       <c r="K2" t="n">
-        <v>31.76</v>
+        <v>31.8</v>
       </c>
       <c r="L2" t="n">
-        <v>31.81</v>
+        <v>31.85</v>
       </c>
       <c r="M2" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="N2" t="n">
-        <v>31.91</v>
+        <v>31.98</v>
       </c>
       <c r="O2" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,13 +690,11 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,37 +707,41 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C3" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D3" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E3" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J3" t="n">
         <v>31.75</v>
@@ -751,13 +753,13 @@
         <v>31.85</v>
       </c>
       <c r="M3" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N3" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O3" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C4" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D4" t="n">
         <v>31.79</v>
       </c>
       <c r="E4" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J4" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K4" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L4" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M4" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N4" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O4" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,12 +855,12 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -882,50 +888,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C5" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D5" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E5" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H5" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I5" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J5" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K5" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L5" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M5" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N5" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O5" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,21 +939,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,59 +963,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C6" t="n">
         <v>31.96</v>
       </c>
       <c r="D6" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E6" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L6" t="n">
         <v>31.89</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I6" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K6" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M6" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N6" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O6" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,7 +1022,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1048,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>31.93</v>
       </c>
       <c r="C7" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D7" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E7" t="n">
         <v>31.93</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I7" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J7" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K7" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L7" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M7" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N7" t="n">
         <v>32.03</v>
       </c>
       <c r="O7" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,76 +1102,84 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C8" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D8" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H8" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J8" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K8" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L8" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M8" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N8" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O8" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,14 +1190,14 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
@@ -1197,69 +1205,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C9" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E9" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F9" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J9" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K9" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L9" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M9" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N9" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O9" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,10 +1269,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1280,10 +1284,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1293,55 +1295,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C10" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D10" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E10" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I10" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J10" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K10" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L10" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M10" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N10" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O10" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,20 +1355,16 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1384,47 +1386,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C11" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D11" t="n">
         <v>32.04</v>
       </c>
       <c r="E11" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J11" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K11" t="n">
         <v>32.02</v>
       </c>
       <c r="L11" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M11" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N11" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O11" t="n">
         <v>32.41</v>
@@ -1440,7 +1442,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1459,57 +1461,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>32.1</v>
       </c>
       <c r="C12" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D12" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E12" t="n">
         <v>32.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H12" t="n">
         <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J12" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K12" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L12" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M12" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N12" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O12" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,13 +1522,15 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,42 +1545,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C13" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D13" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E13" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
         <v>31.9</v>
       </c>
       <c r="J13" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K13" t="n">
         <v>32.03</v>
@@ -1591,7 +1595,7 @@
         <v>32.23</v>
       </c>
       <c r="O13" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,12 +1608,12 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1623,59 +1627,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D14" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E14" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H14" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I14" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J14" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K14" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L14" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M14" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N14" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O14" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,13 +1688,11 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1707,55 +1705,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C15" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D15" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E15" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H15" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J15" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K15" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L15" t="n">
         <v>32.15</v>
       </c>
       <c r="M15" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N15" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O15" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,14 +1770,18 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1785,59 +1791,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C16" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D16" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E16" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I16" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J16" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K16" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L16" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M16" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N16" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O16" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,7 +1850,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1876,50 +1878,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C17" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D17" t="n">
         <v>32.26</v>
       </c>
-      <c r="C17" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D17" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E17" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F17" t="n">
         <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I17" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J17" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K17" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M17" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N17" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O17" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1930,14 +1932,14 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -1958,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C18" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D18" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E18" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J18" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K18" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L18" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M18" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N18" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O18" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2009,23 +2011,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2035,34 +2035,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D19" t="n">
         <v>32.28</v>
       </c>
-      <c r="C19" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E19" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I19" t="n">
         <v>32.09</v>
@@ -2071,19 +2075,19 @@
         <v>32.12</v>
       </c>
       <c r="K19" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L19" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M19" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N19" t="n">
         <v>32.4</v>
       </c>
-      <c r="N19" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O19" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,21 +2095,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2115,59 +2121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C20" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D20" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E20" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F20" t="n">
         <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J20" t="n">
         <v>32.09</v>
       </c>
-      <c r="J20" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K20" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L20" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M20" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N20" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O20" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2178,20 +2180,16 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2201,55 +2199,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C21" t="n">
         <v>32.38</v>
       </c>
       <c r="D21" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E21" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J21" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K21" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L21" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M21" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N21" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O21" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2257,12 +2259,14 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2281,57 +2285,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C22" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D22" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E22" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I22" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J22" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K22" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L22" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M22" t="n">
         <v>32.34</v>
       </c>
-      <c r="M22" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N22" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O22" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,21 +2343,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2372,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C23" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D23" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E23" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I23" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J23" t="n">
         <v>32.19</v>
       </c>
       <c r="K23" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L23" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M23" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N23" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O23" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2428,7 +2434,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2436,10 +2442,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2458,50 +2462,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C24" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D24" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E24" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I24" t="n">
         <v>32.16</v>
       </c>
       <c r="J24" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K24" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L24" t="n">
         <v>32.33</v>
       </c>
       <c r="M24" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N24" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O24" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2514,16 +2518,18 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2533,59 +2539,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C25" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D25" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E25" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H25" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I25" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J25" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K25" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L25" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M25" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N25" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O25" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2598,12 +2600,12 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
@@ -2619,55 +2621,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C26" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D26" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E26" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H26" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I26" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J26" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K26" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L26" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M26" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N26" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O26" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2675,12 +2681,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2688,10 +2696,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2710,50 +2716,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C27" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D27" t="n">
         <v>32.21</v>
       </c>
       <c r="E27" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I27" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J27" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K27" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L27" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M27" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N27" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O27" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2763,18 +2769,16 @@
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2789,57 +2793,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C28" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D28" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E28" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I28" t="n">
         <v>31.93</v>
       </c>
       <c r="J28" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K28" t="n">
         <v>32.15</v>
       </c>
-      <c r="K28" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L28" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M28" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N28" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O28" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2847,18 +2851,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2880,69 +2884,73 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>32.4</v>
       </c>
       <c r="C29" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D29" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E29" t="n">
         <v>32.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I29" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J29" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K29" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L29" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M29" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N29" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O29" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>32.57</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2957,62 +2965,60 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C30" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D30" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E30" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F30" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H30" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I30" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J30" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K30" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L30" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M30" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N30" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O30" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
@@ -3021,12 +3027,12 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3045,57 +3051,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C31" t="n">
         <v>32.31</v>
       </c>
       <c r="D31" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E31" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H31" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I31" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J31" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K31" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L31" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M31" t="n">
         <v>32.33</v>
       </c>
-      <c r="M31" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N31" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O31" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,7 +3116,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3138,67 +3144,63 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C32" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D32" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E32" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H32" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I32" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J32" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K32" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L32" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M32" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N32" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O32" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3217,57 +3219,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C33" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D33" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E33" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H33" t="n">
         <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J33" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K33" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L33" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M33" t="n">
         <v>32.29</v>
       </c>
       <c r="N33" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O33" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,11 +3282,13 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3306,35 +3310,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C34" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D34" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E34" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I34" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J34" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K34" t="n">
         <v>32.18</v>
@@ -3343,13 +3347,13 @@
         <v>32.23</v>
       </c>
       <c r="M34" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N34" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O34" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,18 +3361,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,70 +3387,74 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C35" t="n">
         <v>32.21</v>
       </c>
-      <c r="C35" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D35" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E35" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I35" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J35" t="n">
         <v>32.12</v>
       </c>
       <c r="K35" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L35" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M35" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N35" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O35" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3474,50 +3482,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C36" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D36" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E36" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H36" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I36" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J36" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K36" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L36" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M36" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N36" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O36" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -3531,12 +3539,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3562,67 +3570,65 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C37" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D37" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E37" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H37" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I37" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J37" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K37" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L37" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M37" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N37" t="n">
         <v>32.38</v>
       </c>
       <c r="O37" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3650,65 +3656,65 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C38" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D38" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E38" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H38" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I38" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J38" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K38" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L38" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M38" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N38" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O38" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3729,78 +3735,76 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C39" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D39" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E39" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H39" t="n">
         <v>0.17</v>
       </c>
       <c r="I39" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J39" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K39" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L39" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M39" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N39" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O39" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3813,59 +3817,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C40" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D40" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E40" t="n">
         <v>31.82</v>
       </c>
-      <c r="E40" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F40" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H40" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I40" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J40" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K40" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L40" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M40" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N40" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O40" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,18 +3873,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3897,55 +3897,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C41" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D41" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E41" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I41" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J41" t="n">
         <v>31.65</v>
       </c>
-      <c r="J41" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K41" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L41" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M41" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N41" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O41" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3953,18 +3957,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3979,57 +3983,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C42" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D42" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E42" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H42" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J42" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K42" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L42" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M42" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N42" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O42" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4037,18 +4041,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4063,57 +4067,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C43" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D43" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E43" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H43" t="n">
         <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J43" t="n">
         <v>31.72</v>
       </c>
       <c r="K43" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L43" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M43" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N43" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O43" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4121,18 +4125,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4147,57 +4151,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C44" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D44" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E44" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I44" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J44" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K44" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L44" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M44" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N44" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O44" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4210,7 +4214,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4231,76 +4235,80 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C45" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D45" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E45" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J45" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K45" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L45" t="n">
         <v>31.84</v>
       </c>
-      <c r="C45" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D45" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E45" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I45" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J45" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K45" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L45" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M45" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N45" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O45" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>31.99</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4315,74 +4323,72 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C46" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D46" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E46" t="n">
         <v>31.66</v>
       </c>
-      <c r="E46" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F46" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H46" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I46" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J46" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K46" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L46" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M46" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N46" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O46" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4396,85 +4402,79 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C47" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D47" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E47" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H47" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I47" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J47" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K47" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L47" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M47" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N47" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O47" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4487,55 +4487,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C48" t="n">
         <v>31.73</v>
       </c>
       <c r="D48" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E48" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I48" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J48" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K48" t="n">
         <v>31.57</v>
       </c>
-      <c r="K48" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L48" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M48" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N48" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O48" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4548,16 +4552,18 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4569,57 +4575,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C49" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D49" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E49" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H49" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I49" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J49" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K49" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L49" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M49" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N49" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O49" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4630,20 +4636,18 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4655,57 +4659,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C50" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D50" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E50" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I50" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J50" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K50" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L50" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M50" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N50" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O50" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4716,14 +4720,14 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4739,76 +4743,78 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C51" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J51" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K51" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L51" t="n">
         <v>31.72</v>
       </c>
-      <c r="C51" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D51" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E51" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I51" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J51" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K51" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L51" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M51" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N51" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O51" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4821,59 +4827,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C52" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D52" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E52" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H52" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I52" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J52" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K52" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L52" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M52" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N52" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O52" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4885,12 +4887,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4912,65 +4914,65 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C53" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D53" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I53" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J53" t="n">
         <v>31.49</v>
       </c>
-      <c r="E53" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I53" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J53" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K53" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L53" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M53" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N53" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O53" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4994,58 +4996,56 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>31.5</v>
       </c>
       <c r="C54" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D54" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E54" t="n">
         <v>31.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H54" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I54" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J54" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K54" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L54" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M54" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N54" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O54" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5076,50 +5076,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C55" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D55" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E55" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H55" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I55" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J55" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K55" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L55" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M55" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N55" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O55" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5129,77 +5129,87 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C56" t="n">
         <v>31.69</v>
       </c>
       <c r="D56" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E56" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H56" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I56" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J56" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K56" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L56" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M56" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N56" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O56" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5207,30 +5217,26 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
@@ -5246,50 +5252,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C57" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D57" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E57" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I57" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J57" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K57" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L57" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M57" t="n">
         <v>31.69</v>
       </c>
-      <c r="D57" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E57" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I57" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J57" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K57" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L57" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M57" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N57" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O57" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5300,23 +5306,25 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
@@ -5325,27 +5333,27 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C58" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D58" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E58" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F58" t="n">
         <v>0.04</v>
@@ -5354,28 +5362,28 @@
         <v>0.0013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I58" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J58" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K58" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L58" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M58" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N58" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O58" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5386,14 +5394,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
@@ -5401,10 +5409,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
@@ -5420,47 +5426,47 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C59" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D59" t="n">
         <v>31.72</v>
       </c>
-      <c r="C59" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D59" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E59" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H59" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I59" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J59" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K59" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L59" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M59" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N59" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O59" t="n">
         <v>32.13</v>
@@ -5474,7 +5480,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5499,57 +5505,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C60" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D60" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E60" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F60" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H60" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I60" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J60" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K60" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L60" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M60" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N60" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O60" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5560,14 +5566,14 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U60" s="8" t="inlineStr">
@@ -5585,57 +5591,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C61" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D61" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E61" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F61" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H61" t="n">
         <v>0.09</v>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I61" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J61" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K61" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L61" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M61" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N61" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O61" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5643,23 +5649,21 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5669,74 +5673,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C62" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D62" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E62" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H62" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I62" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J62" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K62" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L62" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M62" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N62" t="n">
         <v>31.96</v>
       </c>
       <c r="O62" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5753,55 +5755,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C63" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D63" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E63" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H63" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I63" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J63" t="n">
         <v>31.67</v>
       </c>
-      <c r="J63" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K63" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L63" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M63" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N63" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O63" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5816,7 +5822,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5835,74 +5841,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C64" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D64" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E64" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H64" t="n">
         <v>0.15</v>
       </c>
       <c r="I64" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J64" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K64" t="n">
         <v>31.67</v>
       </c>
-      <c r="K64" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L64" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M64" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N64" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O64" t="n">
         <v>31.89</v>
       </c>
-      <c r="N64" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O64" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q64" s="6" t="n">
+        <v/>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5921,55 +5921,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C65" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D65" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E65" t="n">
         <v>31.79</v>
       </c>
-      <c r="D65" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E65" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F65" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H65" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I65" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J65" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K65" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L65" t="n">
         <v>31.7</v>
       </c>
       <c r="M65" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N65" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O65" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5977,22 +5981,24 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
       <c r="V65" s="8" t="n">
         <v/>
       </c>
@@ -6003,7 +6009,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,32 +634,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="C2" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D2" t="n">
-        <v>31.82</v>
+        <v>31.79</v>
       </c>
       <c r="E2" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="J2" t="n">
         <v>31.75</v>
@@ -671,13 +671,13 @@
         <v>31.85</v>
       </c>
       <c r="M2" t="n">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N2" t="n">
-        <v>31.98</v>
+        <v>31.93</v>
       </c>
       <c r="O2" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,57 +713,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C3" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D3" t="n">
         <v>31.79</v>
       </c>
       <c r="E3" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I3" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J3" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K3" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L3" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M3" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N3" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O3" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,12 +773,12 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -802,50 +806,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C4" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D4" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E4" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J4" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K4" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L4" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M4" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N4" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,21 +857,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -879,59 +881,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C5" t="n">
         <v>31.96</v>
       </c>
       <c r="D5" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E5" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L5" t="n">
         <v>31.89</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I5" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J5" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K5" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L5" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M5" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N5" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O5" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +940,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -968,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>31.93</v>
       </c>
       <c r="C6" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E6" t="n">
         <v>31.93</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J6" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K6" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L6" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M6" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N6" t="n">
         <v>32.03</v>
       </c>
       <c r="O6" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,76 +1020,84 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C7" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D7" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H7" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J7" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K7" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L7" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M7" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N7" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O7" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,14 +1108,14 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
@@ -1117,69 +1123,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C8" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E8" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F8" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I8" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J8" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K8" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L8" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M8" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N8" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O8" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,10 +1187,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1200,10 +1202,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1213,55 +1213,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C9" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D9" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E9" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H9" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I9" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J9" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K9" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L9" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M9" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N9" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O9" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1269,20 +1273,16 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1304,47 +1304,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C10" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D10" t="n">
         <v>32.04</v>
       </c>
       <c r="E10" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J10" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K10" t="n">
         <v>32.02</v>
       </c>
       <c r="L10" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M10" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N10" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O10" t="n">
         <v>32.41</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1379,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>32.1</v>
       </c>
       <c r="C11" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D11" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E11" t="n">
         <v>32.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H11" t="n">
         <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J11" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K11" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L11" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M11" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N11" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O11" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,13 +1440,15 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1461,42 +1463,42 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C12" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D12" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E12" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
         <v>31.9</v>
       </c>
       <c r="J12" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K12" t="n">
         <v>32.03</v>
@@ -1511,7 +1513,7 @@
         <v>32.23</v>
       </c>
       <c r="O12" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,12 +1526,12 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1543,59 +1545,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C13" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D13" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E13" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I13" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J13" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K13" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M13" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N13" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O13" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,13 +1606,11 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1627,55 +1623,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C14" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D14" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E14" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H14" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J14" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K14" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L14" t="n">
         <v>32.15</v>
       </c>
       <c r="M14" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N14" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O14" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,14 +1688,18 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1705,59 +1709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C15" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D15" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E15" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H15" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I15" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J15" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K15" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L15" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M15" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N15" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O15" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,7 +1768,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1796,50 +1796,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C16" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D16" t="n">
         <v>32.26</v>
       </c>
-      <c r="C16" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D16" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E16" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F16" t="n">
         <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H16" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I16" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J16" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K16" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N16" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O16" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1850,14 +1850,14 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -1878,50 +1878,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C17" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D17" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E17" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I17" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J17" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K17" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L17" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M17" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N17" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O17" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,23 +1929,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1955,34 +1953,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C18" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D18" t="n">
         <v>32.28</v>
       </c>
-      <c r="C18" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D18" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E18" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I18" t="n">
         <v>32.09</v>
@@ -1991,19 +1993,19 @@
         <v>32.12</v>
       </c>
       <c r="K18" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L18" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M18" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N18" t="n">
         <v>32.4</v>
       </c>
-      <c r="N18" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O18" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2011,21 +2013,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2035,59 +2039,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C19" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D19" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E19" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F19" t="n">
         <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J19" t="n">
         <v>32.09</v>
       </c>
-      <c r="J19" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K19" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L19" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M19" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N19" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O19" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2098,20 +2098,16 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2121,55 +2117,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C20" t="n">
         <v>32.38</v>
       </c>
       <c r="D20" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E20" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I20" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J20" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K20" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L20" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M20" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N20" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O20" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,12 +2177,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2201,57 +2203,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C21" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D21" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E21" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I21" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J21" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K21" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L21" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M21" t="n">
         <v>32.34</v>
       </c>
-      <c r="M21" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N21" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O21" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2259,21 +2261,23 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2292,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C22" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D22" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E22" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J22" t="n">
         <v>32.19</v>
       </c>
       <c r="K22" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L22" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M22" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N22" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O22" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,7 +2352,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2356,10 +2360,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2378,50 +2380,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C23" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D23" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E23" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H23" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I23" t="n">
         <v>32.16</v>
       </c>
       <c r="J23" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K23" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L23" t="n">
         <v>32.33</v>
       </c>
       <c r="M23" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N23" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O23" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,16 +2436,18 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2453,59 +2457,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C24" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D24" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E24" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H24" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I24" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J24" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K24" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L24" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M24" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N24" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O24" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -2539,55 +2539,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C25" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D25" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E25" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H25" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I25" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J25" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K25" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L25" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M25" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N25" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O25" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2595,12 +2599,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2608,10 +2614,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2630,50 +2634,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C26" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D26" t="n">
         <v>32.21</v>
       </c>
       <c r="E26" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H26" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I26" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J26" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K26" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L26" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M26" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N26" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O26" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,18 +2687,16 @@
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2709,57 +2711,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C27" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D27" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E27" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H27" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I27" t="n">
         <v>31.93</v>
       </c>
       <c r="J27" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K27" t="n">
         <v>32.15</v>
       </c>
-      <c r="K27" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L27" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M27" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N27" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O27" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,18 +2769,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2800,69 +2802,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>32.4</v>
       </c>
       <c r="C28" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D28" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E28" t="n">
         <v>32.4</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I28" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J28" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K28" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L28" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M28" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N28" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O28" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>32.57</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2877,62 +2883,60 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C29" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D29" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E29" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F29" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H29" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I29" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J29" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K29" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L29" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M29" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N29" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O29" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
@@ -2941,12 +2945,12 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2965,57 +2969,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C30" t="n">
         <v>32.31</v>
       </c>
       <c r="D30" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E30" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H30" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I30" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J30" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K30" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L30" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M30" t="n">
         <v>32.33</v>
       </c>
-      <c r="M30" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N30" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O30" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3030,7 +3034,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3058,67 +3062,63 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C31" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D31" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E31" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H31" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J31" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K31" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L31" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M31" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N31" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O31" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3137,57 +3137,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C32" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D32" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E32" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H32" t="n">
         <v>0.1</v>
       </c>
       <c r="I32" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J32" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K32" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L32" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M32" t="n">
         <v>32.29</v>
       </c>
       <c r="N32" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O32" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3200,11 +3200,13 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3226,35 +3228,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C33" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D33" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E33" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I33" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J33" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K33" t="n">
         <v>32.18</v>
@@ -3263,13 +3265,13 @@
         <v>32.23</v>
       </c>
       <c r="M33" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N33" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O33" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,18 +3279,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3303,70 +3305,74 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C34" t="n">
         <v>32.21</v>
       </c>
-      <c r="C34" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D34" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E34" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I34" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J34" t="n">
         <v>32.12</v>
       </c>
       <c r="K34" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L34" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M34" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N34" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O34" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3394,50 +3400,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C35" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D35" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E35" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I35" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J35" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K35" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L35" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M35" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N35" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O35" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -3451,12 +3457,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3482,67 +3488,65 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C36" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D36" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E36" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H36" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I36" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J36" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K36" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L36" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M36" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N36" t="n">
         <v>32.38</v>
       </c>
       <c r="O36" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3570,65 +3574,65 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C37" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D37" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E37" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H37" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I37" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J37" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K37" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L37" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M37" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N37" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O37" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3649,78 +3653,76 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C38" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D38" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E38" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H38" t="n">
         <v>0.17</v>
       </c>
       <c r="I38" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J38" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K38" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L38" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M38" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N38" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O38" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3733,59 +3735,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C39" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D39" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" t="n">
         <v>31.82</v>
       </c>
-      <c r="E39" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F39" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H39" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I39" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J39" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K39" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L39" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M39" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N39" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O39" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3793,18 +3791,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3817,55 +3815,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C40" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D40" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E40" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I40" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J40" t="n">
         <v>31.65</v>
       </c>
-      <c r="J40" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K40" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L40" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M40" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N40" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O40" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,18 +3875,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3899,57 +3901,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C41" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D41" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E41" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H41" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J41" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K41" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L41" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M41" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N41" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O41" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3957,18 +3959,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3983,57 +3985,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C42" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D42" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E42" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H42" t="n">
         <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J42" t="n">
         <v>31.72</v>
       </c>
       <c r="K42" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L42" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M42" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N42" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O42" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4041,18 +4043,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4067,57 +4069,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C43" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D43" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E43" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I43" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J43" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K43" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L43" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M43" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N43" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O43" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4130,7 +4132,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4151,76 +4153,80 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C44" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D44" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E44" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I44" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J44" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K44" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L44" t="n">
         <v>31.84</v>
       </c>
-      <c r="C44" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D44" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E44" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I44" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J44" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K44" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L44" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M44" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N44" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O44" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>31.99</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4235,74 +4241,72 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C45" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D45" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E45" t="n">
         <v>31.66</v>
       </c>
-      <c r="E45" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F45" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H45" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I45" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J45" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K45" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L45" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M45" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N45" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O45" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4316,85 +4320,79 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C46" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D46" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E46" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H46" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I46" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J46" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K46" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L46" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M46" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O46" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4407,55 +4405,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C47" t="n">
         <v>31.73</v>
       </c>
       <c r="D47" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E47" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I47" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J47" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K47" t="n">
         <v>31.57</v>
       </c>
-      <c r="K47" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L47" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M47" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N47" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O47" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4468,16 +4470,18 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4489,57 +4493,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C48" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D48" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E48" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F48" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I48" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J48" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K48" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L48" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M48" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N48" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O48" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4550,20 +4554,18 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4575,57 +4577,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C49" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D49" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E49" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H49" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I49" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J49" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K49" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L49" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M49" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N49" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O49" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4636,14 +4638,14 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4659,76 +4661,78 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C50" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D50" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E50" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J50" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K50" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L50" t="n">
         <v>31.72</v>
       </c>
-      <c r="C50" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D50" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E50" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J50" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K50" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L50" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M50" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N50" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O50" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4741,59 +4745,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C51" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D51" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E51" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H51" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I51" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J51" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K51" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L51" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M51" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N51" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O51" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4805,12 +4805,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4832,65 +4832,65 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C52" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D52" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I52" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J52" t="n">
         <v>31.49</v>
       </c>
-      <c r="E52" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I52" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J52" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K52" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L52" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M52" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N52" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O52" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4914,58 +4914,56 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>31.5</v>
       </c>
       <c r="C53" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D53" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E53" t="n">
         <v>31.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H53" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I53" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J53" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K53" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L53" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M53" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N53" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O53" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4974,7 +4972,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4996,50 +4994,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C54" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D54" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E54" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H54" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I54" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J54" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K54" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L54" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M54" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N54" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O54" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,77 +5047,87 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C55" t="n">
         <v>31.69</v>
       </c>
       <c r="D55" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E55" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H55" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I55" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J55" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K55" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L55" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M55" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N55" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O55" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,30 +5135,26 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5166,50 +5170,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C56" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D56" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E56" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I56" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J56" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K56" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L56" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M56" t="n">
         <v>31.69</v>
       </c>
-      <c r="D56" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E56" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I56" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J56" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K56" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L56" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M56" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N56" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O56" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,23 +5224,25 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
@@ -5245,27 +5251,27 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C57" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D57" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E57" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F57" t="n">
         <v>0.04</v>
@@ -5274,28 +5280,28 @@
         <v>0.0013</v>
       </c>
       <c r="H57" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I57" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J57" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K57" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L57" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M57" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N57" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O57" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,14 +5312,14 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="inlineStr">
@@ -5321,10 +5327,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
@@ -5340,47 +5344,47 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C58" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D58" t="n">
         <v>31.72</v>
       </c>
-      <c r="C58" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D58" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E58" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H58" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I58" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J58" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K58" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L58" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M58" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N58" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O58" t="n">
         <v>32.13</v>
@@ -5394,7 +5398,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5419,57 +5423,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C59" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D59" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E59" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H59" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I59" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J59" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K59" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L59" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M59" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N59" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O59" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5480,14 +5484,14 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U59" s="8" t="inlineStr">
@@ -5505,57 +5509,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C60" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D60" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E60" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H60" t="n">
         <v>0.09</v>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I60" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J60" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K60" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L60" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M60" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N60" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O60" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5563,23 +5567,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5589,74 +5591,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C61" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D61" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E61" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I61" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J61" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K61" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L61" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M61" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N61" t="n">
         <v>31.96</v>
       </c>
       <c r="O61" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5673,55 +5673,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C62" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D62" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E62" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H62" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I62" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J62" t="n">
         <v>31.67</v>
       </c>
-      <c r="J62" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K62" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L62" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M62" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N62" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O62" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5736,7 +5740,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5755,74 +5759,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C63" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D63" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E63" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H63" t="n">
         <v>0.15</v>
       </c>
       <c r="I63" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J63" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K63" t="n">
         <v>31.67</v>
       </c>
-      <c r="K63" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L63" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M63" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O63" t="n">
         <v>31.89</v>
       </c>
-      <c r="N63" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O63" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q63" s="6" t="n">
+        <v/>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5841,55 +5839,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C64" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D64" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E64" t="n">
         <v>31.79</v>
       </c>
-      <c r="D64" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E64" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F64" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H64" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I64" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J64" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K64" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L64" t="n">
         <v>31.7</v>
       </c>
       <c r="M64" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N64" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O64" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5897,22 +5899,24 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
@@ -5923,57 +5927,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B65" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C65" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D65" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E65" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I65" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K65" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L65" t="n">
         <v>31.79</v>
       </c>
-      <c r="C65" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D65" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E65" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I65" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J65" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K65" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L65" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M65" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N65" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O65" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5981,23 +5985,21 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -6009,7 +6011,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="C2" t="n">
-        <v>31.9</v>
+        <v>31.95</v>
       </c>
       <c r="D2" t="n">
         <v>31.79</v>
       </c>
       <c r="E2" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="I2" t="n">
-        <v>31.73</v>
+        <v>31.69</v>
       </c>
       <c r="J2" t="n">
-        <v>31.75</v>
+        <v>31.77</v>
       </c>
       <c r="K2" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L2" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="M2" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="N2" t="n">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="O2" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,12 +687,12 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -720,50 +720,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C3" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D3" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E3" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I3" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J3" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K3" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L3" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M3" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N3" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,21 +771,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -797,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C4" t="n">
         <v>31.96</v>
       </c>
       <c r="D4" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E4" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I4" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L4" t="n">
         <v>31.89</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I4" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L4" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M4" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N4" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O4" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,7 +854,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -886,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>31.93</v>
       </c>
       <c r="C5" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D5" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E5" t="n">
         <v>31.93</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I5" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J5" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K5" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L5" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M5" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N5" t="n">
         <v>32.03</v>
       </c>
       <c r="O5" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,76 +934,84 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C6" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D6" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J6" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K6" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L6" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M6" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N6" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O6" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,14 +1022,14 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
@@ -1035,69 +1037,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C7" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E7" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I7" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J7" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K7" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L7" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M7" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N7" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O7" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,10 +1101,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1118,10 +1116,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1131,55 +1127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C8" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E8" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H8" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I8" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J8" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K8" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L8" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M8" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N8" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O8" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,20 +1187,16 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1222,47 +1218,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C9" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D9" t="n">
         <v>32.04</v>
       </c>
       <c r="E9" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H9" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J9" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K9" t="n">
         <v>32.02</v>
       </c>
       <c r="L9" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M9" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N9" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O9" t="n">
         <v>32.41</v>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1297,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>32.1</v>
       </c>
       <c r="C10" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D10" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E10" t="n">
         <v>32.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H10" t="n">
         <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J10" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K10" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L10" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M10" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N10" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O10" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,13 +1354,15 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,42 +1377,42 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C11" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D11" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E11" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
         <v>31.9</v>
       </c>
       <c r="J11" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K11" t="n">
         <v>32.03</v>
@@ -1429,7 +1427,7 @@
         <v>32.23</v>
       </c>
       <c r="O11" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,12 +1440,12 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1461,59 +1459,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C12" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D12" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E12" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I12" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J12" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K12" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L12" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M12" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N12" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O12" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,13 +1520,11 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1545,55 +1537,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C13" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D13" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E13" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H13" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J13" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K13" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L13" t="n">
         <v>32.15</v>
       </c>
       <c r="M13" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N13" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O13" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,14 +1602,18 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1623,59 +1623,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C14" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D14" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E14" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H14" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I14" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J14" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K14" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L14" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M14" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N14" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O14" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,7 +1682,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1714,50 +1710,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D15" t="n">
         <v>32.26</v>
       </c>
-      <c r="C15" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E15" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F15" t="n">
         <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I15" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J15" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K15" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M15" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N15" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O15" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,14 +1764,14 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -1796,50 +1792,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C16" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D16" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E16" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J16" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K16" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L16" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M16" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N16" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O16" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1847,23 +1843,21 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1873,34 +1867,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C17" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D17" t="n">
         <v>32.28</v>
       </c>
-      <c r="C17" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D17" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E17" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="n">
         <v>32.09</v>
@@ -1909,19 +1907,19 @@
         <v>32.12</v>
       </c>
       <c r="K17" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L17" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M17" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N17" t="n">
         <v>32.4</v>
       </c>
-      <c r="N17" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O17" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,21 +1927,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1953,59 +1953,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C18" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D18" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E18" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F18" t="n">
         <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J18" t="n">
         <v>32.09</v>
       </c>
-      <c r="J18" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K18" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L18" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M18" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N18" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O18" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,20 +2012,16 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2039,55 +2031,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C19" t="n">
         <v>32.38</v>
       </c>
       <c r="D19" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E19" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I19" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J19" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K19" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L19" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M19" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N19" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O19" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2095,12 +2091,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2119,57 +2117,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C20" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D20" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E20" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I20" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J20" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K20" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L20" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M20" t="n">
         <v>32.34</v>
       </c>
-      <c r="M20" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N20" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O20" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,21 +2175,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2210,50 +2210,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C21" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D21" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E21" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I21" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J21" t="n">
         <v>32.19</v>
       </c>
       <c r="K21" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L21" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M21" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N21" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O21" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2274,10 +2274,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2296,50 +2294,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C22" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D22" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E22" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
         <v>32.16</v>
       </c>
       <c r="J22" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K22" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L22" t="n">
         <v>32.33</v>
       </c>
       <c r="M22" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N22" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O22" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,16 +2350,18 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2371,59 +2371,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C23" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D23" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E23" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H23" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I23" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J23" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K23" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L23" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M23" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N23" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O23" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,12 +2432,12 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -2457,55 +2453,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C24" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D24" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E24" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H24" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J24" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K24" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L24" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M24" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N24" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O24" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2513,12 +2513,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2526,10 +2528,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2548,50 +2548,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C25" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D25" t="n">
         <v>32.21</v>
       </c>
       <c r="E25" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H25" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I25" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J25" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K25" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L25" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M25" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N25" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O25" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2601,18 +2601,16 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2627,57 +2625,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C26" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D26" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E26" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H26" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I26" t="n">
         <v>31.93</v>
       </c>
       <c r="J26" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K26" t="n">
         <v>32.15</v>
       </c>
-      <c r="K26" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L26" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M26" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N26" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O26" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,18 +2683,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2718,69 +2716,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>32.4</v>
       </c>
       <c r="C27" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D27" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E27" t="n">
         <v>32.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I27" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J27" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K27" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L27" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M27" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N27" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O27" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>32.57</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2795,62 +2797,60 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C28" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D28" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E28" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F28" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H28" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I28" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J28" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K28" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L28" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M28" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N28" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O28" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2883,57 +2883,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C29" t="n">
         <v>32.31</v>
       </c>
       <c r="D29" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E29" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H29" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I29" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J29" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K29" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L29" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M29" t="n">
         <v>32.33</v>
       </c>
-      <c r="M29" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N29" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O29" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2948,7 +2948,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2976,67 +2976,63 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C30" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D30" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E30" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H30" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J30" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K30" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L30" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M30" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N30" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O30" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3055,57 +3051,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C31" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D31" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E31" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H31" t="n">
         <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J31" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K31" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L31" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M31" t="n">
         <v>32.29</v>
       </c>
       <c r="N31" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O31" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3118,11 +3114,13 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3144,35 +3142,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C32" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D32" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E32" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I32" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J32" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K32" t="n">
         <v>32.18</v>
@@ -3181,13 +3179,13 @@
         <v>32.23</v>
       </c>
       <c r="M32" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N32" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O32" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,18 +3193,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3221,70 +3219,74 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C33" t="n">
         <v>32.21</v>
       </c>
-      <c r="C33" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D33" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E33" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I33" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J33" t="n">
         <v>32.12</v>
       </c>
       <c r="K33" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L33" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M33" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N33" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O33" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3312,50 +3314,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C34" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D34" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E34" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I34" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J34" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K34" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L34" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M34" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N34" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O34" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -3369,12 +3371,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3400,67 +3402,65 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C35" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D35" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E35" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H35" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I35" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J35" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K35" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L35" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M35" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N35" t="n">
         <v>32.38</v>
       </c>
       <c r="O35" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3488,65 +3488,65 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C36" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D36" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E36" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H36" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I36" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J36" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K36" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L36" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M36" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N36" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O36" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3567,78 +3567,76 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C37" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D37" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E37" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="n">
         <v>0.17</v>
       </c>
       <c r="I37" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J37" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K37" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L37" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M37" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N37" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O37" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3651,59 +3649,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C38" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D38" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E38" t="n">
         <v>31.82</v>
       </c>
-      <c r="E38" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F38" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H38" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I38" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J38" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K38" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L38" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M38" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N38" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O38" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,18 +3705,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3735,55 +3729,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C39" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D39" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E39" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I39" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J39" t="n">
         <v>31.65</v>
       </c>
-      <c r="J39" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K39" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L39" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M39" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N39" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O39" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,18 +3789,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3817,57 +3815,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C40" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D40" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E40" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H40" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J40" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K40" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L40" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M40" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N40" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O40" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3875,18 +3873,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3901,57 +3899,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C41" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D41" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E41" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H41" t="n">
         <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J41" t="n">
         <v>31.72</v>
       </c>
       <c r="K41" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L41" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M41" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N41" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O41" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3959,18 +3957,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3985,57 +3983,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C42" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D42" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E42" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I42" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J42" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K42" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L42" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M42" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N42" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O42" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4048,7 +4046,7 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4069,76 +4067,80 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D43" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I43" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J43" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K43" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L43" t="n">
         <v>31.84</v>
       </c>
-      <c r="C43" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D43" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E43" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I43" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J43" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K43" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L43" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M43" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N43" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O43" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>31.99</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4153,74 +4155,72 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C44" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D44" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E44" t="n">
         <v>31.66</v>
       </c>
-      <c r="E44" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F44" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H44" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I44" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J44" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K44" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L44" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M44" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N44" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O44" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4234,85 +4234,79 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C45" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D45" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E45" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H45" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I45" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J45" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K45" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L45" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M45" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N45" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O45" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4325,55 +4319,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C46" t="n">
         <v>31.73</v>
       </c>
       <c r="D46" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E46" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H46" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I46" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J46" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K46" t="n">
         <v>31.57</v>
       </c>
-      <c r="K46" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L46" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M46" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N46" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O46" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4386,16 +4384,18 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4407,57 +4407,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C47" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D47" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E47" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F47" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I47" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J47" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K47" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L47" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M47" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N47" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O47" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4468,20 +4468,18 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4493,57 +4491,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C48" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D48" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E48" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H48" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I48" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J48" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K48" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L48" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M48" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N48" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O48" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4554,14 +4552,14 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4577,76 +4575,78 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C49" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D49" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E49" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J49" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K49" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L49" t="n">
         <v>31.72</v>
       </c>
-      <c r="C49" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D49" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E49" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J49" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K49" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L49" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M49" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N49" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O49" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4659,59 +4659,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C50" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D50" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E50" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H50" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I50" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J50" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K50" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L50" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M50" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N50" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O50" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4723,12 +4719,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4750,65 +4746,65 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C51" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D51" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J51" t="n">
         <v>31.49</v>
       </c>
-      <c r="E51" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I51" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J51" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K51" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L51" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M51" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N51" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O51" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4832,58 +4828,56 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>31.5</v>
       </c>
       <c r="C52" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D52" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E52" t="n">
         <v>31.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H52" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I52" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J52" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K52" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L52" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M52" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N52" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O52" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4892,7 +4886,7 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4914,50 +4908,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C53" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D53" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E53" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H53" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I53" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J53" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K53" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L53" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M53" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N53" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O53" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4967,77 +4961,87 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C54" t="n">
         <v>31.69</v>
       </c>
       <c r="D54" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E54" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H54" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I54" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J54" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K54" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L54" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M54" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N54" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O54" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5045,30 +5049,26 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5084,50 +5084,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C55" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E55" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I55" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J55" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K55" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L55" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M55" t="n">
         <v>31.69</v>
       </c>
-      <c r="D55" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E55" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I55" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J55" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K55" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L55" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M55" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N55" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O55" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,23 +5138,25 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5163,27 +5165,27 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C56" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D56" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E56" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F56" t="n">
         <v>0.04</v>
@@ -5192,28 +5194,28 @@
         <v>0.0013</v>
       </c>
       <c r="H56" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I56" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J56" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K56" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L56" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M56" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N56" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O56" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5224,14 +5226,14 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
@@ -5239,10 +5241,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
@@ -5258,47 +5258,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C57" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D57" t="n">
         <v>31.72</v>
       </c>
-      <c r="C57" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E57" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F57" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H57" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I57" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J57" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K57" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L57" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M57" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N57" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O57" t="n">
         <v>32.13</v>
@@ -5312,7 +5312,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5337,57 +5337,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C58" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D58" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E58" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H58" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I58" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J58" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K58" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L58" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M58" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N58" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O58" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5398,14 +5398,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
@@ -5423,57 +5423,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C59" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D59" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E59" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F59" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H59" t="n">
         <v>0.09</v>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I59" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J59" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K59" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L59" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M59" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N59" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O59" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5481,23 +5481,21 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5507,74 +5505,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C60" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D60" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E60" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H60" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I60" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J60" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K60" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L60" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M60" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N60" t="n">
         <v>31.96</v>
       </c>
       <c r="O60" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5591,55 +5587,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C61" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D61" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E61" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H61" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I61" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J61" t="n">
         <v>31.67</v>
       </c>
-      <c r="J61" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K61" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L61" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M61" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N61" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O61" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5654,7 +5654,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5673,74 +5673,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C62" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D62" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E62" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H62" t="n">
         <v>0.15</v>
       </c>
       <c r="I62" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J62" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K62" t="n">
         <v>31.67</v>
       </c>
-      <c r="K62" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L62" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M62" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N62" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O62" t="n">
         <v>31.89</v>
       </c>
-      <c r="N62" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O62" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q62" s="6" t="n">
+        <v/>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5759,55 +5753,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C63" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D63" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E63" t="n">
         <v>31.79</v>
       </c>
-      <c r="D63" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F63" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H63" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I63" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J63" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K63" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L63" t="n">
         <v>31.7</v>
       </c>
       <c r="M63" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N63" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O63" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5815,22 +5813,24 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
@@ -5841,57 +5841,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C64" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D64" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E64" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I64" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J64" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K64" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L64" t="n">
         <v>31.79</v>
       </c>
-      <c r="C64" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D64" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E64" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I64" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J64" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K64" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L64" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M64" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N64" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O64" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5899,23 +5899,21 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5927,57 +5925,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C65" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="D65" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E65" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I65" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J65" t="n">
         <v>31.71</v>
       </c>
-      <c r="E65" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I65" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J65" t="n">
-        <v>31.65</v>
-      </c>
       <c r="K65" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="L65" t="n">
         <v>31.79</v>
       </c>
       <c r="M65" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="N65" t="n">
-        <v>31.92</v>
+        <v>31.95</v>
       </c>
       <c r="O65" t="n">
-        <v>32</v>
+        <v>31.95</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5992,7 +5990,7 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.83</v>
+        <v>31.9</v>
       </c>
       <c r="C2" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D2" t="n">
-        <v>31.79</v>
+        <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>31.83</v>
+        <v>31.89</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="I2" t="n">
-        <v>31.69</v>
+        <v>31.64</v>
       </c>
       <c r="J2" t="n">
-        <v>31.77</v>
+        <v>31.66</v>
       </c>
       <c r="K2" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L2" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="M2" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="N2" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,21 +685,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C3" t="n">
         <v>31.96</v>
       </c>
       <c r="D3" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E3" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L3" t="n">
         <v>31.89</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I3" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K3" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L3" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M3" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N3" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O3" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -800,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>31.93</v>
       </c>
       <c r="C4" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D4" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E4" t="n">
         <v>31.93</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I4" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J4" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K4" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L4" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M4" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N4" t="n">
         <v>32.03</v>
       </c>
       <c r="O4" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,76 +848,84 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C5" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D5" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H5" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J5" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K5" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L5" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M5" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N5" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O5" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -934,14 +936,14 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
@@ -949,69 +951,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C6" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E6" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F6" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H6" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I6" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J6" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K6" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L6" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M6" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N6" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O6" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,10 +1015,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1032,10 +1030,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1045,55 +1041,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C7" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D7" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E7" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I7" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J7" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K7" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L7" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M7" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N7" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O7" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,20 +1101,16 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1136,47 +1132,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C8" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D8" t="n">
         <v>32.04</v>
       </c>
       <c r="E8" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H8" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J8" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K8" t="n">
         <v>32.02</v>
       </c>
       <c r="L8" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M8" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N8" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O8" t="n">
         <v>32.41</v>
@@ -1192,7 +1188,7 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1211,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>32.1</v>
       </c>
       <c r="C9" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D9" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E9" t="n">
         <v>32.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H9" t="n">
         <v>0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J9" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K9" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L9" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M9" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N9" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O9" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,13 +1268,15 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,42 +1291,42 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D10" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E10" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
         <v>31.9</v>
       </c>
       <c r="J10" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K10" t="n">
         <v>32.03</v>
@@ -1343,7 +1341,7 @@
         <v>32.23</v>
       </c>
       <c r="O10" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,12 +1354,12 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1375,59 +1373,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C11" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D11" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E11" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J11" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K11" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L11" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M11" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N11" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O11" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,13 +1434,11 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,55 +1451,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C12" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E12" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J12" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K12" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L12" t="n">
         <v>32.15</v>
       </c>
       <c r="M12" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N12" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O12" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,14 +1516,18 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1537,59 +1537,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C13" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D13" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E13" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I13" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J13" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K13" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L13" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M13" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N13" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O13" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,7 +1596,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,50 +1624,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C14" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D14" t="n">
         <v>32.26</v>
       </c>
-      <c r="C14" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D14" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E14" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F14" t="n">
         <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H14" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I14" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J14" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K14" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L14" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M14" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N14" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O14" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,14 +1678,14 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -1710,50 +1706,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C15" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D15" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E15" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J15" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K15" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L15" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M15" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N15" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O15" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1761,23 +1757,21 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1787,34 +1781,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C16" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D16" t="n">
         <v>32.28</v>
       </c>
-      <c r="C16" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D16" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E16" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
         <v>32.09</v>
@@ -1823,19 +1821,19 @@
         <v>32.12</v>
       </c>
       <c r="K16" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L16" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M16" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N16" t="n">
         <v>32.4</v>
       </c>
-      <c r="N16" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O16" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,21 +1841,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1867,59 +1867,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C17" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D17" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E17" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F17" t="n">
         <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I17" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J17" t="n">
         <v>32.09</v>
       </c>
-      <c r="J17" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K17" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L17" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M17" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N17" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O17" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1930,20 +1926,16 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1953,55 +1945,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C18" t="n">
         <v>32.38</v>
       </c>
       <c r="D18" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E18" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I18" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J18" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K18" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L18" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M18" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N18" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O18" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2009,12 +2005,14 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2033,57 +2031,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C19" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D19" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E19" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I19" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J19" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K19" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L19" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M19" t="n">
         <v>32.34</v>
       </c>
-      <c r="M19" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N19" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O19" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,21 +2089,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2124,50 +2124,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C20" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D20" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E20" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J20" t="n">
         <v>32.19</v>
       </c>
       <c r="K20" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L20" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M20" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N20" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O20" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2188,10 +2188,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2210,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C21" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D21" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E21" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I21" t="n">
         <v>32.16</v>
       </c>
       <c r="J21" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K21" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L21" t="n">
         <v>32.33</v>
       </c>
       <c r="M21" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N21" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O21" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,16 +2264,18 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2285,59 +2285,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C22" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D22" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E22" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I22" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J22" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K22" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L22" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M22" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N22" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O22" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,12 +2346,12 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -2371,55 +2367,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C23" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D23" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E23" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H23" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J23" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K23" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L23" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M23" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N23" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O23" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2427,12 +2427,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2440,10 +2442,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2462,50 +2462,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C24" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D24" t="n">
         <v>32.21</v>
       </c>
       <c r="E24" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H24" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I24" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J24" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K24" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L24" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M24" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N24" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O24" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,18 +2515,16 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2541,57 +2539,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C25" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D25" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E25" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H25" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I25" t="n">
         <v>31.93</v>
       </c>
       <c r="J25" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K25" t="n">
         <v>32.15</v>
       </c>
-      <c r="K25" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L25" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M25" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N25" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O25" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2599,18 +2597,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2632,69 +2630,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>32.4</v>
       </c>
       <c r="C26" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D26" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E26" t="n">
         <v>32.4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I26" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J26" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K26" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L26" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M26" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N26" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O26" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>32.57</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2709,62 +2711,60 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C27" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D27" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E27" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J27" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K27" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L27" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M27" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N27" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O27" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2797,57 +2797,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C28" t="n">
         <v>32.31</v>
       </c>
       <c r="D28" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E28" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H28" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I28" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J28" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K28" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L28" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M28" t="n">
         <v>32.33</v>
       </c>
-      <c r="M28" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N28" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O28" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2862,7 +2862,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2890,67 +2890,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C29" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D29" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E29" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H29" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J29" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K29" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L29" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M29" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N29" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O29" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2969,57 +2965,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C30" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D30" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E30" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H30" t="n">
         <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J30" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K30" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L30" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M30" t="n">
         <v>32.29</v>
       </c>
       <c r="N30" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O30" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3032,11 +3028,13 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3058,35 +3056,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C31" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D31" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E31" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I31" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J31" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K31" t="n">
         <v>32.18</v>
@@ -3095,13 +3093,13 @@
         <v>32.23</v>
       </c>
       <c r="M31" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N31" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O31" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3109,18 +3107,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3135,70 +3133,74 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C32" t="n">
         <v>32.21</v>
       </c>
-      <c r="C32" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D32" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E32" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I32" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J32" t="n">
         <v>32.12</v>
       </c>
       <c r="K32" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L32" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M32" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N32" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O32" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3226,50 +3228,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C33" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D33" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E33" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H33" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I33" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J33" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K33" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L33" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M33" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N33" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O33" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -3283,12 +3285,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3314,67 +3316,65 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C34" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D34" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E34" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H34" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I34" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J34" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K34" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L34" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M34" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N34" t="n">
         <v>32.38</v>
       </c>
       <c r="O34" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3402,65 +3402,65 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C35" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D35" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E35" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H35" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I35" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J35" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K35" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L35" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M35" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N35" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O35" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3481,78 +3481,76 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C36" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D36" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E36" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="n">
         <v>0.17</v>
       </c>
       <c r="I36" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J36" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K36" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L36" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M36" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N36" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O36" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3565,59 +3563,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C37" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D37" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E37" t="n">
         <v>31.82</v>
       </c>
-      <c r="E37" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F37" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H37" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I37" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J37" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K37" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L37" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M37" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N37" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O37" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3625,18 +3619,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3649,55 +3643,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C38" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D38" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E38" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I38" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J38" t="n">
         <v>31.65</v>
       </c>
-      <c r="J38" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K38" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L38" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M38" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N38" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O38" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,18 +3703,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3731,57 +3729,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C39" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D39" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E39" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H39" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J39" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K39" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L39" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M39" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N39" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O39" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,18 +3787,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3815,57 +3813,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C40" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D40" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E40" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H40" t="n">
         <v>0.1</v>
       </c>
       <c r="I40" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J40" t="n">
         <v>31.72</v>
       </c>
       <c r="K40" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L40" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M40" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N40" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O40" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,18 +3871,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3899,57 +3897,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C41" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D41" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E41" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I41" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J41" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K41" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L41" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M41" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N41" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O41" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,7 +3960,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3983,76 +3981,80 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C42" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D42" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K42" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L42" t="n">
         <v>31.84</v>
       </c>
-      <c r="C42" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D42" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E42" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I42" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J42" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K42" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L42" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M42" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N42" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O42" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>31.99</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4067,74 +4069,72 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C43" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D43" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E43" t="n">
         <v>31.66</v>
       </c>
-      <c r="E43" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F43" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H43" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I43" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J43" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K43" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L43" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M43" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N43" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O43" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4148,85 +4148,79 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C44" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D44" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E44" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H44" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I44" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J44" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K44" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L44" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M44" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N44" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O44" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4239,55 +4233,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C45" t="n">
         <v>31.73</v>
       </c>
       <c r="D45" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E45" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I45" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J45" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K45" t="n">
         <v>31.57</v>
       </c>
-      <c r="K45" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L45" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M45" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N45" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O45" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4300,16 +4298,18 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C46" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D46" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E46" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H46" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I46" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J46" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K46" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L46" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M46" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N46" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O46" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4382,20 +4382,18 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4407,57 +4405,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C47" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D47" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E47" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I47" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J47" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K47" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L47" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M47" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N47" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O47" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4468,14 +4466,14 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4491,76 +4489,78 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C48" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D48" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E48" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I48" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J48" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K48" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L48" t="n">
         <v>31.72</v>
       </c>
-      <c r="C48" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D48" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E48" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I48" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J48" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K48" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L48" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M48" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N48" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O48" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4573,59 +4573,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C49" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D49" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E49" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H49" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I49" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J49" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K49" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L49" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M49" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N49" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O49" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4637,12 +4633,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4664,65 +4660,65 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C50" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D50" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E50" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J50" t="n">
         <v>31.49</v>
       </c>
-      <c r="E50" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J50" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K50" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L50" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M50" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N50" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O50" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4746,58 +4742,56 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>31.5</v>
       </c>
       <c r="C51" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D51" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E51" t="n">
         <v>31.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H51" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I51" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J51" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K51" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L51" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M51" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N51" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O51" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4806,7 +4800,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4828,50 +4822,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C52" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D52" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E52" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I52" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J52" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K52" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L52" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M52" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N52" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O52" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,77 +4875,87 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C53" t="n">
         <v>31.69</v>
       </c>
       <c r="D53" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E53" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H53" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I53" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J53" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K53" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L53" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M53" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N53" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O53" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,30 +4963,26 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
@@ -4998,50 +4998,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C54" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D54" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E54" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I54" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J54" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K54" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L54" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M54" t="n">
         <v>31.69</v>
       </c>
-      <c r="D54" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E54" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I54" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J54" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K54" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L54" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M54" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N54" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O54" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5052,23 +5052,25 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5077,27 +5079,27 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C55" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D55" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E55" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F55" t="n">
         <v>0.04</v>
@@ -5106,28 +5108,28 @@
         <v>0.0013</v>
       </c>
       <c r="H55" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I55" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J55" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K55" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L55" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M55" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N55" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O55" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,14 +5140,14 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U55" s="8" t="inlineStr">
@@ -5153,10 +5155,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5172,47 +5172,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C56" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D56" t="n">
         <v>31.72</v>
       </c>
-      <c r="C56" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E56" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F56" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H56" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I56" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J56" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K56" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L56" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M56" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N56" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O56" t="n">
         <v>32.13</v>
@@ -5226,7 +5226,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5251,57 +5251,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C57" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D57" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E57" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H57" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I57" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J57" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K57" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L57" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M57" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N57" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O57" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5312,14 +5312,14 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="inlineStr">
@@ -5337,57 +5337,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C58" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D58" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E58" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F58" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.09</v>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I58" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J58" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K58" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L58" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M58" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N58" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O58" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5395,23 +5395,21 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5421,74 +5419,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C59" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D59" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E59" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I59" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J59" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K59" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L59" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M59" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N59" t="n">
         <v>31.96</v>
       </c>
       <c r="O59" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5505,55 +5501,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C60" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D60" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E60" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H60" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I60" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J60" t="n">
         <v>31.67</v>
       </c>
-      <c r="J60" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K60" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L60" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M60" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N60" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O60" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5568,7 +5568,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5587,74 +5587,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C61" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D61" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E61" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H61" t="n">
         <v>0.15</v>
       </c>
       <c r="I61" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J61" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K61" t="n">
         <v>31.67</v>
       </c>
-      <c r="K61" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L61" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M61" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N61" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O61" t="n">
         <v>31.89</v>
       </c>
-      <c r="N61" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O61" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5673,55 +5667,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C62" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D62" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E62" t="n">
         <v>31.79</v>
       </c>
-      <c r="D62" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E62" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F62" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H62" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I62" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J62" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K62" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L62" t="n">
         <v>31.7</v>
       </c>
       <c r="M62" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N62" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O62" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5729,22 +5727,24 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
@@ -5755,57 +5755,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C63" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D63" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I63" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K63" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L63" t="n">
         <v>31.79</v>
       </c>
-      <c r="C63" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D63" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I63" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J63" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K63" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L63" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M63" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N63" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O63" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5813,23 +5813,21 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5841,57 +5839,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C64" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="D64" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E64" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I64" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J64" t="n">
         <v>31.71</v>
       </c>
-      <c r="E64" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I64" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J64" t="n">
-        <v>31.65</v>
-      </c>
       <c r="K64" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="L64" t="n">
         <v>31.79</v>
       </c>
       <c r="M64" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="N64" t="n">
-        <v>31.92</v>
+        <v>31.95</v>
       </c>
       <c r="O64" t="n">
-        <v>32</v>
+        <v>31.95</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5906,7 +5904,7 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5932,50 +5930,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>31.78</v>
       </c>
       <c r="C65" t="n">
-        <v>31.82</v>
+        <v>31.9</v>
       </c>
       <c r="D65" t="n">
-        <v>31.73</v>
+        <v>31.77</v>
       </c>
       <c r="E65" t="n">
         <v>31.78</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0001</v>
       </c>
       <c r="H65" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I65" t="n">
-        <v>31.59</v>
+        <v>31.64</v>
       </c>
       <c r="J65" t="n">
-        <v>31.71</v>
+        <v>31.69</v>
       </c>
       <c r="K65" t="n">
-        <v>31.75</v>
+        <v>31.73</v>
       </c>
       <c r="L65" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="M65" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N65" t="n">
         <v>31.87</v>
       </c>
-      <c r="N65" t="n">
-        <v>31.95</v>
-      </c>
       <c r="O65" t="n">
-        <v>31.95</v>
+        <v>31.91</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5983,21 +5981,23 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R65" s="6" t="n">
+        <v/>
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.9</v>
+        <v>31.93</v>
       </c>
       <c r="C2" t="n">
         <v>31.96</v>
       </c>
       <c r="D2" t="n">
-        <v>31.82</v>
+        <v>31.87</v>
       </c>
       <c r="E2" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="K2" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="L2" t="n">
         <v>31.89</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K2" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L2" t="n">
-        <v>31.85</v>
-      </c>
       <c r="M2" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="N2" t="n">
-        <v>31.97</v>
+        <v>32.03</v>
       </c>
       <c r="O2" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>31.93</v>
       </c>
       <c r="C3" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D3" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E3" t="n">
         <v>31.93</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I3" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J3" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K3" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L3" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M3" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N3" t="n">
         <v>32.03</v>
       </c>
       <c r="O3" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,74 +770,82 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C4" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D4" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J4" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K4" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L4" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M4" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N4" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O4" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -850,12 +858,12 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
@@ -863,69 +871,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C5" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E5" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H5" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I5" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J5" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K5" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L5" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M5" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N5" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O5" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,8 +935,10 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
@@ -946,10 +950,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -959,55 +961,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C6" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D6" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E6" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I6" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J6" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K6" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L6" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M6" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N6" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O6" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,20 +1021,16 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1050,47 +1052,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C7" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D7" t="n">
         <v>32.04</v>
       </c>
       <c r="E7" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J7" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K7" t="n">
         <v>32.02</v>
       </c>
       <c r="L7" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M7" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N7" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O7" t="n">
         <v>32.41</v>
@@ -1104,9 +1106,9 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1125,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>32.1</v>
       </c>
       <c r="C8" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E8" t="n">
         <v>32.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H8" t="n">
         <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J8" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K8" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L8" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M8" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N8" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O8" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,8 +1193,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1207,42 +1211,42 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D9" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E9" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
         <v>31.9</v>
       </c>
       <c r="J9" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K9" t="n">
         <v>32.03</v>
@@ -1257,7 +1261,7 @@
         <v>32.23</v>
       </c>
       <c r="O9" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,14 +1272,14 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1289,59 +1293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C10" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D10" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E10" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I10" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J10" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K10" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L10" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M10" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N10" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O10" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,15 +1352,13 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,55 +1371,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C11" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D11" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E11" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H11" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J11" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K11" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L11" t="n">
         <v>32.15</v>
       </c>
       <c r="M11" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N11" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O11" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,16 +1434,20 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1451,59 +1457,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C12" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D12" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E12" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I12" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J12" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K12" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L12" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M12" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N12" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O12" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1542,50 +1544,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D13" t="n">
         <v>32.26</v>
       </c>
-      <c r="C13" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D13" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E13" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F13" t="n">
         <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I13" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J13" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K13" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L13" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M13" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N13" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O13" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1598,12 +1600,12 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
@@ -1624,50 +1626,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C14" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D14" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E14" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J14" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K14" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M14" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N14" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O14" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1675,23 +1677,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1701,34 +1701,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D15" t="n">
         <v>32.28</v>
       </c>
-      <c r="C15" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E15" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I15" t="n">
         <v>32.09</v>
@@ -1737,19 +1741,19 @@
         <v>32.12</v>
       </c>
       <c r="K15" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L15" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M15" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N15" t="n">
         <v>32.4</v>
       </c>
-      <c r="N15" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O15" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1757,21 +1761,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1781,59 +1787,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C16" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D16" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E16" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F16" t="n">
         <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J16" t="n">
         <v>32.09</v>
       </c>
-      <c r="J16" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K16" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L16" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M16" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N16" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O16" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1846,18 +1848,14 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1867,55 +1865,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C17" t="n">
         <v>32.38</v>
       </c>
       <c r="D17" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E17" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J17" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K17" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L17" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M17" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N17" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O17" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1923,12 +1925,14 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1947,57 +1951,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C18" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D18" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E18" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I18" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J18" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K18" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L18" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M18" t="n">
         <v>32.34</v>
       </c>
-      <c r="M18" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N18" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O18" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2005,21 +2009,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2038,50 +2044,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C19" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D19" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E19" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J19" t="n">
         <v>32.19</v>
       </c>
       <c r="K19" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L19" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M19" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N19" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O19" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2092,9 +2098,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2102,10 +2108,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2124,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C20" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D20" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E20" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="n">
         <v>32.16</v>
       </c>
       <c r="J20" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K20" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L20" t="n">
         <v>32.33</v>
       </c>
       <c r="M20" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N20" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O20" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2178,18 +2182,20 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2199,59 +2205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C21" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D21" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E21" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H21" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I21" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J21" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K21" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L21" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M21" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N21" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O21" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2262,14 +2264,14 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -2285,55 +2287,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C22" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D22" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E22" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H22" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I22" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J22" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K22" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L22" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M22" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N22" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O22" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2341,12 +2347,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2354,10 +2362,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2376,50 +2382,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C23" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D23" t="n">
         <v>32.21</v>
       </c>
       <c r="E23" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H23" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I23" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J23" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K23" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L23" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M23" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N23" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O23" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2429,18 +2435,16 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2455,57 +2459,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C24" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D24" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E24" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I24" t="n">
         <v>31.93</v>
       </c>
       <c r="J24" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K24" t="n">
         <v>32.15</v>
       </c>
-      <c r="K24" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L24" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M24" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N24" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O24" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2513,18 +2517,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2546,69 +2550,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>32.4</v>
       </c>
       <c r="C25" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D25" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E25" t="n">
         <v>32.4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I25" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J25" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K25" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L25" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M25" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N25" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O25" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2623,62 +2631,60 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C26" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D26" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E26" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F26" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H26" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I26" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J26" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K26" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L26" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M26" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N26" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O26" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
@@ -2687,12 +2693,12 @@
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2711,57 +2717,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C27" t="n">
         <v>32.31</v>
       </c>
       <c r="D27" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E27" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H27" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I27" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J27" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K27" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L27" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M27" t="n">
         <v>32.33</v>
       </c>
-      <c r="M27" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N27" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O27" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2804,67 +2810,63 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C28" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D28" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E28" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H28" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J28" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K28" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L28" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M28" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N28" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O28" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2883,57 +2885,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C29" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D29" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E29" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H29" t="n">
         <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J29" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K29" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L29" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M29" t="n">
         <v>32.29</v>
       </c>
       <c r="N29" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O29" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,13 +2946,15 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2972,35 +2976,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C30" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D30" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E30" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I30" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J30" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K30" t="n">
         <v>32.18</v>
@@ -3009,13 +3013,13 @@
         <v>32.23</v>
       </c>
       <c r="M30" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N30" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O30" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,18 +3027,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3049,63 +3053,67 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C31" t="n">
         <v>32.21</v>
       </c>
-      <c r="C31" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D31" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E31" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I31" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J31" t="n">
         <v>32.12</v>
       </c>
       <c r="K31" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L31" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M31" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N31" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O31" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3140,50 +3148,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C32" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D32" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E32" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H32" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I32" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J32" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K32" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L32" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M32" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N32" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O32" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -3197,12 +3205,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3228,64 +3236,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C33" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D33" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E33" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H33" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I33" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J33" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K33" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L33" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M33" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N33" t="n">
         <v>32.38</v>
       </c>
       <c r="O33" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -3316,64 +3322,64 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C34" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D34" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E34" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H34" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I34" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J34" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K34" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L34" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M34" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N34" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O34" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3395,78 +3401,76 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C35" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D35" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E35" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H35" t="n">
         <v>0.17</v>
       </c>
       <c r="I35" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J35" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K35" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L35" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M35" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N35" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O35" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3479,59 +3483,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C36" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D36" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E36" t="n">
         <v>31.82</v>
       </c>
-      <c r="E36" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F36" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H36" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I36" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J36" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K36" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L36" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M36" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N36" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O36" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,18 +3539,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3563,55 +3563,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C37" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D37" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E37" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H37" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I37" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J37" t="n">
         <v>31.65</v>
       </c>
-      <c r="J37" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K37" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L37" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M37" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N37" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O37" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3619,18 +3623,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3645,57 +3649,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C38" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D38" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E38" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H38" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J38" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K38" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L38" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M38" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N38" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O38" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3703,18 +3707,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3729,57 +3733,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C39" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D39" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E39" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H39" t="n">
         <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J39" t="n">
         <v>31.72</v>
       </c>
       <c r="K39" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L39" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M39" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N39" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O39" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3787,18 +3791,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3813,57 +3817,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C40" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D40" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E40" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I40" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J40" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K40" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L40" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M40" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N40" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O40" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3874,9 +3878,9 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3897,76 +3901,80 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C41" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D41" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E41" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J41" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K41" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L41" t="n">
         <v>31.84</v>
       </c>
-      <c r="C41" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D41" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E41" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I41" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K41" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L41" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M41" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N41" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O41" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3981,71 +3989,69 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C42" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D42" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E42" t="n">
         <v>31.66</v>
       </c>
-      <c r="E42" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F42" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H42" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I42" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J42" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K42" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L42" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M42" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N42" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O42" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4062,85 +4068,79 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C43" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D43" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E43" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H43" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I43" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J43" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K43" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L43" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M43" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N43" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O43" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4153,55 +4153,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C44" t="n">
         <v>31.73</v>
       </c>
       <c r="D44" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E44" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H44" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I44" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J44" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K44" t="n">
         <v>31.57</v>
       </c>
-      <c r="K44" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L44" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M44" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N44" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O44" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4212,18 +4216,20 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4235,57 +4241,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C45" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D45" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E45" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I45" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J45" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K45" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L45" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M45" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N45" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O45" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4298,18 +4304,16 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4321,57 +4325,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C46" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D46" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E46" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I46" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J46" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K46" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L46" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M46" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N46" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O46" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,12 +4388,12 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4405,76 +4409,78 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C47" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D47" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E47" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I47" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J47" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K47" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L47" t="n">
         <v>31.72</v>
       </c>
-      <c r="C47" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D47" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E47" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I47" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K47" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L47" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M47" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N47" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O47" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4487,59 +4493,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C48" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D48" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E48" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H48" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I48" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J48" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K48" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L48" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M48" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N48" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O48" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,12 +4553,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4578,62 +4580,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C49" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D49" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E49" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J49" t="n">
         <v>31.49</v>
       </c>
-      <c r="E49" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J49" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K49" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L49" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M49" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N49" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O49" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4660,67 +4662,65 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>31.5</v>
       </c>
       <c r="C50" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D50" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E50" t="n">
         <v>31.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H50" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I50" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J50" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K50" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L50" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M50" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N50" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O50" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4742,50 +4742,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C51" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D51" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E51" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I51" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J51" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K51" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L51" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M51" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N51" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O51" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4795,77 +4795,87 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C52" t="n">
         <v>31.69</v>
       </c>
       <c r="D52" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E52" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H52" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I52" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J52" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K52" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L52" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M52" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N52" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O52" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4873,30 +4883,26 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4912,50 +4918,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C53" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I53" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J53" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K53" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L53" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M53" t="n">
         <v>31.69</v>
       </c>
-      <c r="D53" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E53" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I53" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J53" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K53" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L53" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M53" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N53" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O53" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4973,16 +4979,18 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
@@ -4991,27 +4999,27 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C54" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D54" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E54" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F54" t="n">
         <v>0.04</v>
@@ -5020,28 +5028,28 @@
         <v>0.0013</v>
       </c>
       <c r="H54" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I54" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J54" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K54" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L54" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M54" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N54" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O54" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5054,12 +5062,12 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
@@ -5067,10 +5075,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5086,47 +5092,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C55" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D55" t="n">
         <v>31.72</v>
       </c>
-      <c r="C55" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D55" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E55" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F55" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H55" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I55" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J55" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K55" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L55" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M55" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N55" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O55" t="n">
         <v>32.13</v>
@@ -5165,57 +5171,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C56" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D56" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E56" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H56" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I56" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J56" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K56" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L56" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M56" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N56" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O56" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5228,12 +5234,12 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
@@ -5251,57 +5257,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C57" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D57" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E57" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F57" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.09</v>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I57" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J57" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K57" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L57" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M57" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N57" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O57" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5309,23 +5315,21 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5335,74 +5339,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C58" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D58" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I58" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J58" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K58" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L58" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M58" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N58" t="n">
         <v>31.96</v>
       </c>
       <c r="O58" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5419,55 +5421,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C59" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D59" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E59" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H59" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I59" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J59" t="n">
         <v>31.67</v>
       </c>
-      <c r="J59" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K59" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L59" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M59" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N59" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O59" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5501,67 +5507,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C60" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D60" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E60" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H60" t="n">
         <v>0.15</v>
       </c>
       <c r="I60" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J60" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K60" t="n">
         <v>31.67</v>
       </c>
-      <c r="K60" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L60" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M60" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N60" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O60" t="n">
         <v>31.89</v>
       </c>
-      <c r="N60" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O60" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5587,55 +5587,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C61" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D61" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E61" t="n">
         <v>31.79</v>
       </c>
-      <c r="D61" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E61" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F61" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H61" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I61" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J61" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K61" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L61" t="n">
         <v>31.7</v>
       </c>
       <c r="M61" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N61" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O61" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5643,22 +5647,24 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5669,57 +5675,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C62" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D62" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E62" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I62" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K62" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L62" t="n">
         <v>31.79</v>
       </c>
-      <c r="C62" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D62" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E62" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I62" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J62" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K62" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L62" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M62" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N62" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O62" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5727,23 +5733,21 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5755,57 +5759,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C63" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="D63" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I63" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J63" t="n">
         <v>31.71</v>
       </c>
-      <c r="E63" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I63" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J63" t="n">
-        <v>31.65</v>
-      </c>
       <c r="K63" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="L63" t="n">
         <v>31.79</v>
       </c>
       <c r="M63" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="N63" t="n">
-        <v>31.92</v>
+        <v>31.95</v>
       </c>
       <c r="O63" t="n">
-        <v>32</v>
+        <v>31.95</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5818,9 +5822,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5846,50 +5850,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>31.78</v>
       </c>
       <c r="C64" t="n">
-        <v>31.82</v>
+        <v>31.9</v>
       </c>
       <c r="D64" t="n">
-        <v>31.73</v>
+        <v>31.77</v>
       </c>
       <c r="E64" t="n">
         <v>31.78</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0001</v>
       </c>
       <c r="H64" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I64" t="n">
-        <v>31.59</v>
+        <v>31.64</v>
       </c>
       <c r="J64" t="n">
-        <v>31.71</v>
+        <v>31.69</v>
       </c>
       <c r="K64" t="n">
-        <v>31.75</v>
+        <v>31.73</v>
       </c>
       <c r="L64" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="M64" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N64" t="n">
         <v>31.87</v>
       </c>
-      <c r="N64" t="n">
-        <v>31.95</v>
-      </c>
       <c r="O64" t="n">
-        <v>31.95</v>
+        <v>31.91</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5897,21 +5901,23 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5923,57 +5929,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="C65" t="n">
         <v>31.9</v>
       </c>
       <c r="D65" t="n">
-        <v>31.77</v>
+        <v>31.82</v>
       </c>
       <c r="E65" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H65" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>31.64</v>
       </c>
       <c r="J65" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="K65" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="L65" t="n">
-        <v>31.78</v>
+        <v>31.81</v>
       </c>
       <c r="M65" t="n">
-        <v>31.82</v>
+        <v>31.85</v>
       </c>
       <c r="N65" t="n">
-        <v>31.87</v>
+        <v>31.89</v>
       </c>
       <c r="O65" t="n">
-        <v>31.91</v>
+        <v>32.04</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5986,12 +5992,12 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U65" s="8" t="inlineStr">
@@ -6009,7 +6015,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>31.93</v>
       </c>
       <c r="C2" t="n">
-        <v>31.96</v>
+        <v>32.13</v>
       </c>
       <c r="D2" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="E2" t="n">
         <v>31.93</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="I2" t="n">
-        <v>31.69</v>
+        <v>31.77</v>
       </c>
       <c r="J2" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="K2" t="n">
-        <v>31.83</v>
+        <v>31.88</v>
       </c>
       <c r="L2" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="M2" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="N2" t="n">
         <v>32.03</v>
       </c>
       <c r="O2" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,74 +690,82 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C3" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D3" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J3" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K3" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L3" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M3" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N3" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O3" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,12 +778,12 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -783,69 +791,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C4" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E4" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I4" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J4" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K4" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L4" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M4" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N4" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O4" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,8 +855,10 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
@@ -866,10 +870,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -879,55 +881,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C5" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D5" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E5" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H5" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I5" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J5" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K5" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L5" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M5" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N5" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O5" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,20 +941,16 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -970,47 +972,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C6" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D6" t="n">
         <v>32.04</v>
       </c>
       <c r="E6" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J6" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K6" t="n">
         <v>32.02</v>
       </c>
       <c r="L6" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M6" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N6" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O6" t="n">
         <v>32.41</v>
@@ -1024,9 +1026,9 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1045,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>32.1</v>
       </c>
       <c r="C7" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D7" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E7" t="n">
         <v>32.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H7" t="n">
         <v>0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J7" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K7" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L7" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M7" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N7" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O7" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,8 +1113,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,42 +1131,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C8" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D8" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E8" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
         <v>31.9</v>
       </c>
       <c r="J8" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K8" t="n">
         <v>32.03</v>
@@ -1177,7 +1181,7 @@
         <v>32.23</v>
       </c>
       <c r="O8" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,14 +1192,14 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1209,59 +1213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C9" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E9" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I9" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J9" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K9" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L9" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M9" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N9" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O9" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,15 +1272,13 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,55 +1291,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C10" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D10" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E10" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H10" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J10" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K10" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L10" t="n">
         <v>32.15</v>
       </c>
       <c r="M10" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N10" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O10" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,16 +1354,20 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1371,59 +1377,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C11" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D11" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E11" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I11" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J11" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K11" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L11" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M11" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N11" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O11" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1462,50 +1464,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C12" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D12" t="n">
         <v>32.26</v>
       </c>
-      <c r="C12" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D12" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E12" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F12" t="n">
         <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I12" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J12" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K12" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L12" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M12" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N12" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O12" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,12 +1520,12 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -1544,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C13" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E13" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J13" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K13" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L13" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M13" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N13" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O13" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,23 +1597,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1621,34 +1621,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C14" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D14" t="n">
         <v>32.28</v>
       </c>
-      <c r="C14" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E14" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
         <v>32.09</v>
@@ -1657,19 +1661,19 @@
         <v>32.12</v>
       </c>
       <c r="K14" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L14" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M14" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N14" t="n">
         <v>32.4</v>
       </c>
-      <c r="N14" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O14" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1677,21 +1681,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1701,59 +1707,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C15" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D15" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E15" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F15" t="n">
         <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I15" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J15" t="n">
         <v>32.09</v>
       </c>
-      <c r="J15" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K15" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L15" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M15" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N15" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O15" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,18 +1768,14 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1787,55 +1785,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C16" t="n">
         <v>32.38</v>
       </c>
       <c r="D16" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E16" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I16" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J16" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K16" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L16" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M16" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N16" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O16" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,12 +1845,14 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1867,57 +1871,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C17" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D17" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E17" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I17" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J17" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K17" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L17" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M17" t="n">
         <v>32.34</v>
       </c>
-      <c r="M17" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N17" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O17" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1925,21 +1929,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1958,50 +1964,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C18" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D18" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E18" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J18" t="n">
         <v>32.19</v>
       </c>
       <c r="K18" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L18" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M18" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N18" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O18" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2012,9 +2018,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2022,10 +2028,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2044,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C19" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D19" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E19" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
         <v>32.16</v>
       </c>
       <c r="J19" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K19" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L19" t="n">
         <v>32.33</v>
       </c>
       <c r="M19" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N19" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O19" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2098,18 +2102,20 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2119,59 +2125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C20" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D20" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E20" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H20" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I20" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J20" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K20" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L20" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M20" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N20" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O20" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2182,14 +2184,14 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -2205,55 +2207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C21" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D21" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E21" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H21" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I21" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J21" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K21" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L21" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M21" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N21" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O21" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2261,12 +2267,14 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2274,10 +2282,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2296,50 +2302,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C22" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D22" t="n">
         <v>32.21</v>
       </c>
       <c r="E22" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H22" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I22" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J22" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K22" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L22" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M22" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N22" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O22" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,18 +2355,16 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2375,57 +2379,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C23" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D23" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E23" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H23" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I23" t="n">
         <v>31.93</v>
       </c>
       <c r="J23" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K23" t="n">
         <v>32.15</v>
       </c>
-      <c r="K23" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L23" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M23" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N23" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O23" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2433,18 +2437,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2466,69 +2470,73 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>32.4</v>
       </c>
       <c r="C24" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D24" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E24" t="n">
         <v>32.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I24" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J24" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K24" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L24" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M24" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N24" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O24" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2543,62 +2551,60 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C25" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D25" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E25" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F25" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I25" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J25" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K25" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L25" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M25" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N25" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O25" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
@@ -2607,12 +2613,12 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2631,57 +2637,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C26" t="n">
         <v>32.31</v>
       </c>
       <c r="D26" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E26" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H26" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I26" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J26" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K26" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L26" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M26" t="n">
         <v>32.33</v>
       </c>
-      <c r="M26" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N26" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O26" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2724,67 +2730,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C27" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D27" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E27" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H27" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J27" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K27" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L27" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M27" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N27" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O27" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2803,57 +2805,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C28" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D28" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E28" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H28" t="n">
         <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J28" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K28" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L28" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M28" t="n">
         <v>32.29</v>
       </c>
       <c r="N28" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O28" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2864,13 +2866,15 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2892,35 +2896,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C29" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D29" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E29" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I29" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J29" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K29" t="n">
         <v>32.18</v>
@@ -2929,13 +2933,13 @@
         <v>32.23</v>
       </c>
       <c r="M29" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N29" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O29" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,18 +2947,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2969,63 +2973,67 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C30" t="n">
         <v>32.21</v>
       </c>
-      <c r="C30" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D30" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E30" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I30" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J30" t="n">
         <v>32.12</v>
       </c>
       <c r="K30" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L30" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M30" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N30" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O30" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3060,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C31" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D31" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E31" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H31" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J31" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K31" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L31" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M31" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N31" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O31" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -3117,12 +3125,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3148,64 +3156,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C32" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D32" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E32" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H32" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I32" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J32" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K32" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L32" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M32" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N32" t="n">
         <v>32.38</v>
       </c>
       <c r="O32" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
@@ -3236,64 +3242,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C33" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D33" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E33" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H33" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I33" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J33" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K33" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L33" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M33" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N33" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O33" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3315,78 +3321,76 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C34" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D34" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E34" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H34" t="n">
         <v>0.17</v>
       </c>
       <c r="I34" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J34" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K34" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L34" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M34" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N34" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O34" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3399,59 +3403,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C35" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D35" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E35" t="n">
         <v>31.82</v>
       </c>
-      <c r="E35" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F35" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H35" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I35" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J35" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K35" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L35" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M35" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N35" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O35" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3459,18 +3459,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3483,55 +3483,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C36" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D36" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E36" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H36" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I36" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J36" t="n">
         <v>31.65</v>
       </c>
-      <c r="J36" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K36" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L36" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M36" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N36" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O36" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,18 +3543,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3565,57 +3569,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C37" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D37" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E37" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H37" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J37" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K37" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L37" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M37" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N37" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O37" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,18 +3627,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3649,57 +3653,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C38" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D38" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E38" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H38" t="n">
         <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J38" t="n">
         <v>31.72</v>
       </c>
       <c r="K38" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L38" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M38" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N38" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O38" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,18 +3711,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3733,57 +3737,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C39" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D39" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E39" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I39" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J39" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K39" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L39" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M39" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N39" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O39" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3794,9 +3798,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3817,76 +3821,80 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C40" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D40" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J40" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K40" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L40" t="n">
         <v>31.84</v>
       </c>
-      <c r="C40" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D40" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E40" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I40" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K40" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L40" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M40" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N40" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O40" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3901,71 +3909,69 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C41" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D41" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E41" t="n">
         <v>31.66</v>
       </c>
-      <c r="E41" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F41" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H41" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I41" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J41" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K41" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L41" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M41" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N41" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O41" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3982,85 +3988,79 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C42" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D42" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E42" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H42" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I42" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J42" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K42" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L42" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M42" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N42" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O42" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4073,55 +4073,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C43" t="n">
         <v>31.73</v>
       </c>
       <c r="D43" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E43" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H43" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J43" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K43" t="n">
         <v>31.57</v>
       </c>
-      <c r="K43" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L43" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M43" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N43" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O43" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4132,18 +4136,20 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4155,57 +4161,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C44" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D44" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E44" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H44" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I44" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J44" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K44" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L44" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M44" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N44" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O44" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,18 +4224,16 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4241,57 +4245,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C45" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D45" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E45" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I45" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J45" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K45" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L45" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M45" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N45" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O45" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4304,12 +4308,12 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4325,76 +4329,78 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C46" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E46" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L46" t="n">
         <v>31.72</v>
       </c>
-      <c r="C46" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D46" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E46" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I46" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J46" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K46" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L46" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M46" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N46" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O46" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4407,59 +4413,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C47" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D47" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E47" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H47" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J47" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K47" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L47" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M47" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N47" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O47" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4471,12 +4473,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4498,62 +4500,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C48" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D48" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E48" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I48" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J48" t="n">
         <v>31.49</v>
       </c>
-      <c r="E48" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I48" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J48" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K48" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L48" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M48" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N48" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O48" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4580,67 +4582,65 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>31.5</v>
       </c>
       <c r="C49" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D49" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E49" t="n">
         <v>31.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H49" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I49" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J49" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K49" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L49" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M49" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N49" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O49" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4662,50 +4662,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C50" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D50" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E50" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I50" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J50" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K50" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L50" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M50" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N50" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O50" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,77 +4715,87 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C51" t="n">
         <v>31.69</v>
       </c>
       <c r="D51" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E51" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H51" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I51" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J51" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K51" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L51" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M51" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N51" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O51" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,30 +4803,26 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4832,50 +4838,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C52" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D52" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I52" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J52" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K52" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L52" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M52" t="n">
         <v>31.69</v>
       </c>
-      <c r="D52" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E52" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I52" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J52" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K52" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L52" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M52" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N52" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O52" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4893,16 +4899,18 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4911,27 +4919,27 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C53" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D53" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E53" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F53" t="n">
         <v>0.04</v>
@@ -4940,28 +4948,28 @@
         <v>0.0013</v>
       </c>
       <c r="H53" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I53" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J53" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K53" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L53" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M53" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N53" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O53" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4974,12 +4982,12 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="inlineStr">
@@ -4987,10 +4995,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
@@ -5006,47 +5012,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C54" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D54" t="n">
         <v>31.72</v>
       </c>
-      <c r="C54" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D54" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E54" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H54" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I54" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J54" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K54" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L54" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M54" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N54" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O54" t="n">
         <v>32.13</v>
@@ -5085,57 +5091,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C55" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D55" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E55" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H55" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I55" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J55" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K55" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L55" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M55" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N55" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O55" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5148,12 +5154,12 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="inlineStr">
@@ -5171,57 +5177,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C56" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D56" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E56" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H56" t="n">
         <v>0.09</v>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I56" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J56" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K56" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L56" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M56" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N56" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O56" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5229,23 +5235,21 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5255,74 +5259,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C57" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D57" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E57" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I57" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J57" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K57" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L57" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M57" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N57" t="n">
         <v>31.96</v>
       </c>
       <c r="O57" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5339,55 +5341,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C58" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D58" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E58" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H58" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I58" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J58" t="n">
         <v>31.67</v>
       </c>
-      <c r="J58" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K58" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L58" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M58" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N58" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O58" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5421,67 +5427,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C59" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D59" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E59" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H59" t="n">
         <v>0.15</v>
       </c>
       <c r="I59" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J59" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K59" t="n">
         <v>31.67</v>
       </c>
-      <c r="K59" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L59" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M59" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N59" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O59" t="n">
         <v>31.89</v>
       </c>
-      <c r="N59" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O59" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5507,55 +5507,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C60" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E60" t="n">
         <v>31.79</v>
       </c>
-      <c r="D60" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E60" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F60" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H60" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I60" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J60" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K60" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L60" t="n">
         <v>31.7</v>
       </c>
       <c r="M60" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N60" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O60" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5563,22 +5567,24 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
@@ -5589,57 +5595,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C61" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D61" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J61" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K61" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L61" t="n">
         <v>31.79</v>
       </c>
-      <c r="C61" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D61" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E61" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I61" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J61" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K61" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L61" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M61" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N61" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O61" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5647,23 +5653,21 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5675,57 +5679,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C62" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="D62" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E62" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I62" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J62" t="n">
         <v>31.71</v>
       </c>
-      <c r="E62" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I62" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>31.65</v>
-      </c>
       <c r="K62" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="L62" t="n">
         <v>31.79</v>
       </c>
       <c r="M62" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="N62" t="n">
-        <v>31.92</v>
+        <v>31.95</v>
       </c>
       <c r="O62" t="n">
-        <v>32</v>
+        <v>31.95</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5738,9 +5742,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5766,50 +5770,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>31.78</v>
       </c>
       <c r="C63" t="n">
-        <v>31.82</v>
+        <v>31.9</v>
       </c>
       <c r="D63" t="n">
-        <v>31.73</v>
+        <v>31.77</v>
       </c>
       <c r="E63" t="n">
         <v>31.78</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0001</v>
       </c>
       <c r="H63" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I63" t="n">
-        <v>31.59</v>
+        <v>31.64</v>
       </c>
       <c r="J63" t="n">
-        <v>31.71</v>
+        <v>31.69</v>
       </c>
       <c r="K63" t="n">
-        <v>31.75</v>
+        <v>31.73</v>
       </c>
       <c r="L63" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="M63" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N63" t="n">
         <v>31.87</v>
       </c>
-      <c r="N63" t="n">
-        <v>31.95</v>
-      </c>
       <c r="O63" t="n">
-        <v>31.95</v>
+        <v>31.91</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5817,21 +5821,23 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5843,57 +5849,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="C64" t="n">
         <v>31.9</v>
       </c>
       <c r="D64" t="n">
-        <v>31.77</v>
+        <v>31.82</v>
       </c>
       <c r="E64" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H64" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I64" t="n">
         <v>31.64</v>
       </c>
       <c r="J64" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="K64" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="L64" t="n">
-        <v>31.78</v>
+        <v>31.81</v>
       </c>
       <c r="M64" t="n">
-        <v>31.82</v>
+        <v>31.85</v>
       </c>
       <c r="N64" t="n">
-        <v>31.87</v>
+        <v>31.89</v>
       </c>
       <c r="O64" t="n">
-        <v>31.91</v>
+        <v>32.04</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5906,12 +5912,12 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -5929,57 +5935,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="C65" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D65" t="n">
         <v>31.85</v>
       </c>
-      <c r="C65" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="D65" t="n">
-        <v>31.82</v>
-      </c>
       <c r="E65" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I65" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="K65" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="L65" t="n">
         <v>31.85</v>
       </c>
-      <c r="F65" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I65" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J65" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="K65" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="L65" t="n">
-        <v>31.81</v>
-      </c>
       <c r="M65" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="N65" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="O65" t="n">
-        <v>32.04</v>
+        <v>31.97</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5992,12 +5998,12 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U65" s="8" t="inlineStr">
@@ -6005,8 +6011,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W65" s="11" t="inlineStr">
         <is>
@@ -6015,7 +6023,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="C2" t="n">
-        <v>32.13</v>
+        <v>32.16</v>
       </c>
       <c r="D2" t="n">
-        <v>31.92</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>31.93</v>
+        <v>32.05</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>31.77</v>
+        <v>31.71</v>
       </c>
       <c r="J2" t="n">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="K2" t="n">
-        <v>31.88</v>
+        <v>31.82</v>
       </c>
       <c r="L2" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="M2" t="n">
-        <v>31.98</v>
+        <v>32.03</v>
       </c>
       <c r="N2" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="O2" t="n">
-        <v>32.06</v>
+        <v>32.33</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,12 +690,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="inlineStr">
@@ -703,69 +703,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C3" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E3" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J3" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K3" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L3" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M3" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N3" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O3" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,8 +767,10 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -786,10 +782,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -799,55 +793,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C4" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D4" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E4" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I4" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J4" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K4" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L4" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M4" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N4" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O4" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,20 +853,16 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -890,47 +884,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C5" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D5" t="n">
         <v>32.04</v>
       </c>
       <c r="E5" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H5" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J5" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K5" t="n">
         <v>32.02</v>
       </c>
       <c r="L5" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M5" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N5" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O5" t="n">
         <v>32.41</v>
@@ -944,9 +938,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -965,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>32.1</v>
       </c>
       <c r="C6" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D6" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E6" t="n">
         <v>32.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H6" t="n">
         <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J6" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K6" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L6" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M6" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N6" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O6" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,8 +1025,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,42 +1043,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C7" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E7" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
         <v>31.9</v>
       </c>
       <c r="J7" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K7" t="n">
         <v>32.03</v>
@@ -1097,7 +1093,7 @@
         <v>32.23</v>
       </c>
       <c r="O7" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,14 +1104,14 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1129,59 +1125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C8" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D8" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E8" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J8" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K8" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L8" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M8" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N8" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O8" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,15 +1184,13 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,55 +1203,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C9" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D9" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E9" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H9" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J9" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K9" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L9" t="n">
         <v>32.15</v>
       </c>
       <c r="M9" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N9" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O9" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,16 +1266,20 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1291,59 +1289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C10" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D10" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E10" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I10" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J10" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K10" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L10" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M10" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N10" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O10" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1382,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C11" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D11" t="n">
         <v>32.26</v>
       </c>
-      <c r="C11" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D11" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E11" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F11" t="n">
         <v>0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I11" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J11" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K11" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L11" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M11" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N11" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O11" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,12 +1432,12 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -1464,50 +1458,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C12" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D12" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E12" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J12" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K12" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L12" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M12" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N12" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O12" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,23 +1509,21 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1541,34 +1533,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D13" t="n">
         <v>32.28</v>
       </c>
-      <c r="C13" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E13" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I13" t="n">
         <v>32.09</v>
@@ -1577,19 +1573,19 @@
         <v>32.12</v>
       </c>
       <c r="K13" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L13" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M13" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N13" t="n">
         <v>32.4</v>
       </c>
-      <c r="N13" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O13" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,21 +1593,23 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1621,59 +1619,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C14" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D14" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E14" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F14" t="n">
         <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J14" t="n">
         <v>32.09</v>
       </c>
-      <c r="J14" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K14" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L14" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M14" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N14" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O14" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,18 +1680,14 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1707,55 +1697,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C15" t="n">
         <v>32.38</v>
       </c>
       <c r="D15" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E15" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H15" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I15" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J15" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K15" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L15" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M15" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N15" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O15" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1763,12 +1757,14 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1787,57 +1783,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C16" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D16" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E16" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I16" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J16" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K16" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L16" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M16" t="n">
         <v>32.34</v>
       </c>
-      <c r="M16" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N16" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O16" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1845,21 +1841,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1878,50 +1876,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C17" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D17" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E17" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I17" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J17" t="n">
         <v>32.19</v>
       </c>
       <c r="K17" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L17" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M17" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N17" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O17" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1932,9 +1930,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1942,10 +1940,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1964,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C18" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D18" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E18" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I18" t="n">
         <v>32.16</v>
       </c>
       <c r="J18" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K18" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L18" t="n">
         <v>32.33</v>
       </c>
       <c r="M18" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N18" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O18" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,18 +2014,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2039,59 +2037,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C19" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D19" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E19" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I19" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J19" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K19" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L19" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M19" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N19" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O19" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,14 +2096,14 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -2125,55 +2119,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C20" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D20" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E20" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H20" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I20" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J20" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K20" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L20" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M20" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N20" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O20" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,12 +2179,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2194,10 +2194,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2216,50 +2214,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C21" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D21" t="n">
         <v>32.21</v>
       </c>
       <c r="E21" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H21" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I21" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J21" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K21" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L21" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M21" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N21" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O21" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,18 +2267,16 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2295,57 +2291,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C22" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D22" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E22" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H22" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I22" t="n">
         <v>31.93</v>
       </c>
       <c r="J22" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K22" t="n">
         <v>32.15</v>
       </c>
-      <c r="K22" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L22" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M22" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N22" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O22" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,18 +2349,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2386,69 +2382,73 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>32.4</v>
       </c>
       <c r="C23" t="n">
-        <v>32.45</v>
+        <v>32.4</v>
       </c>
       <c r="D23" t="n">
-        <v>32.33</v>
+        <v>32.12</v>
       </c>
       <c r="E23" t="n">
         <v>32.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>31.93</v>
+        <v>32.22</v>
       </c>
       <c r="J23" t="n">
-        <v>31.98</v>
+        <v>32.28</v>
       </c>
       <c r="K23" t="n">
-        <v>32.15</v>
+        <v>32.34</v>
       </c>
       <c r="L23" t="n">
-        <v>32.32</v>
+        <v>32.39</v>
       </c>
       <c r="M23" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N23" t="n">
-        <v>32.54</v>
+        <v>32.51</v>
       </c>
       <c r="O23" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>32.57</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2463,62 +2463,60 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="C24" t="n">
-        <v>32.4</v>
+        <v>32.31</v>
       </c>
       <c r="D24" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="E24" t="n">
-        <v>32.4</v>
+        <v>32.26</v>
       </c>
       <c r="F24" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0</v>
+        <v>-0.004</v>
       </c>
       <c r="H24" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="I24" t="n">
-        <v>32.22</v>
+        <v>31.85</v>
       </c>
       <c r="J24" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K24" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="L24" t="n">
-        <v>32.39</v>
+        <v>32.33</v>
       </c>
       <c r="M24" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="N24" t="n">
-        <v>32.51</v>
+        <v>32.74</v>
       </c>
       <c r="O24" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.67</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
@@ -2527,12 +2525,12 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2551,57 +2549,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="C25" t="n">
         <v>32.31</v>
       </c>
       <c r="D25" t="n">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="E25" t="n">
-        <v>32.26</v>
+        <v>32.21</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="H25" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="I25" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="J25" t="n">
-        <v>32.19</v>
+        <v>32.15</v>
       </c>
       <c r="K25" t="n">
-        <v>32.26</v>
+        <v>32.2</v>
       </c>
       <c r="L25" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="M25" t="n">
         <v>32.33</v>
       </c>
-      <c r="M25" t="n">
-        <v>32.53</v>
-      </c>
       <c r="N25" t="n">
-        <v>32.74</v>
+        <v>32.4</v>
       </c>
       <c r="O25" t="n">
-        <v>32.67</v>
+        <v>32.43</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2644,67 +2642,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="C26" t="n">
-        <v>32.31</v>
+        <v>32.27</v>
       </c>
       <c r="D26" t="n">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="E26" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="H26" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="J26" t="n">
-        <v>32.15</v>
+        <v>32.03</v>
       </c>
       <c r="K26" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="L26" t="n">
-        <v>32.25</v>
+        <v>32.22</v>
       </c>
       <c r="M26" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="N26" t="n">
-        <v>32.4</v>
+        <v>32.36</v>
       </c>
       <c r="O26" t="n">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2723,57 +2717,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="C27" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
       <c r="D27" t="n">
-        <v>32.17</v>
+        <v>32.19</v>
       </c>
       <c r="E27" t="n">
-        <v>32.24</v>
+        <v>32.23</v>
       </c>
       <c r="F27" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0002</v>
       </c>
       <c r="H27" t="n">
         <v>0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>31.98</v>
+        <v>32.07</v>
       </c>
       <c r="J27" t="n">
-        <v>32.03</v>
+        <v>32.14</v>
       </c>
       <c r="K27" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="L27" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="M27" t="n">
         <v>32.29</v>
       </c>
       <c r="N27" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="O27" t="n">
-        <v>32.47</v>
+        <v>32.37</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,13 +2778,15 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2812,35 +2808,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="C28" t="n">
-        <v>32.29</v>
+        <v>32.25</v>
       </c>
       <c r="D28" t="n">
-        <v>32.19</v>
+        <v>32.16</v>
       </c>
       <c r="E28" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I28" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="J28" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
       <c r="K28" t="n">
         <v>32.18</v>
@@ -2849,13 +2845,13 @@
         <v>32.23</v>
       </c>
       <c r="M28" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="N28" t="n">
-        <v>32.34</v>
+        <v>32.32</v>
       </c>
       <c r="O28" t="n">
-        <v>32.37</v>
+        <v>32.39</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,18 +2859,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2889,63 +2885,67 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C29" t="n">
         <v>32.21</v>
       </c>
-      <c r="C29" t="n">
-        <v>32.25</v>
-      </c>
       <c r="D29" t="n">
-        <v>32.16</v>
+        <v>32.06</v>
       </c>
       <c r="E29" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I29" t="n">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="J29" t="n">
         <v>32.12</v>
       </c>
       <c r="K29" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="L29" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="M29" t="n">
-        <v>32.28</v>
+        <v>32.26</v>
       </c>
       <c r="N29" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="O29" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>32.34</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2980,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="C30" t="n">
-        <v>32.21</v>
+        <v>32.13</v>
       </c>
       <c r="D30" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="E30" t="n">
-        <v>32.2</v>
+        <v>32.12</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="H30" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I30" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="J30" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="K30" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="L30" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="M30" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N30" t="n">
-        <v>32.3</v>
+        <v>32.38</v>
       </c>
       <c r="O30" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3068,64 +3068,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="C31" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="D31" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E31" t="n">
-        <v>32.12</v>
+        <v>31.99</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0042</v>
       </c>
       <c r="H31" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I31" t="n">
-        <v>31.92</v>
+        <v>31.71</v>
       </c>
       <c r="J31" t="n">
-        <v>32.1</v>
+        <v>31.96</v>
       </c>
       <c r="K31" t="n">
-        <v>32.13</v>
+        <v>32.02</v>
       </c>
       <c r="L31" t="n">
-        <v>32.17</v>
+        <v>32.08</v>
       </c>
       <c r="M31" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="N31" t="n">
         <v>32.38</v>
       </c>
       <c r="O31" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32.34</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
@@ -3156,64 +3154,64 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="C32" t="n">
-        <v>32.01</v>
+        <v>31.93</v>
       </c>
       <c r="D32" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="E32" t="n">
-        <v>31.99</v>
+        <v>31.85</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0044</v>
       </c>
       <c r="H32" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I32" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="J32" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="K32" t="n">
-        <v>32.02</v>
+        <v>31.86</v>
       </c>
       <c r="L32" t="n">
-        <v>32.08</v>
+        <v>31.94</v>
       </c>
       <c r="M32" t="n">
-        <v>32.23</v>
+        <v>32.12</v>
       </c>
       <c r="N32" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="O32" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3235,78 +3233,76 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="C33" t="n">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
       <c r="D33" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="E33" t="n">
-        <v>31.85</v>
+        <v>31.88</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.001</v>
       </c>
       <c r="H33" t="n">
         <v>0.17</v>
       </c>
       <c r="I33" t="n">
-        <v>31.5</v>
+        <v>31.59</v>
       </c>
       <c r="J33" t="n">
-        <v>31.79</v>
+        <v>31.68</v>
       </c>
       <c r="K33" t="n">
-        <v>31.86</v>
+        <v>31.77</v>
       </c>
       <c r="L33" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="M33" t="n">
-        <v>32.12</v>
+        <v>31.93</v>
       </c>
       <c r="N33" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O33" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3319,59 +3315,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.88</v>
+        <v>31.81</v>
       </c>
       <c r="C34" t="n">
-        <v>31.99</v>
+        <v>31.94</v>
       </c>
       <c r="D34" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E34" t="n">
         <v>31.82</v>
       </c>
-      <c r="E34" t="n">
-        <v>31.88</v>
-      </c>
       <c r="F34" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0021</v>
       </c>
       <c r="H34" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I34" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="J34" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K34" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="L34" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="M34" t="n">
-        <v>31.93</v>
+        <v>31.97</v>
       </c>
       <c r="N34" t="n">
-        <v>32.02</v>
+        <v>32.04</v>
       </c>
       <c r="O34" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3379,18 +3371,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3403,55 +3395,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C35" t="n">
-        <v>31.94</v>
+        <v>31.89</v>
       </c>
       <c r="D35" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="E35" t="n">
-        <v>31.82</v>
+        <v>31.84</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0007</v>
       </c>
       <c r="H35" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="I35" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J35" t="n">
         <v>31.65</v>
       </c>
-      <c r="J35" t="n">
-        <v>31.7</v>
-      </c>
       <c r="K35" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="L35" t="n">
-        <v>31.89</v>
+        <v>31.84</v>
       </c>
       <c r="M35" t="n">
-        <v>31.97</v>
+        <v>31.88</v>
       </c>
       <c r="N35" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="O35" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3459,18 +3455,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3485,57 +3481,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="C36" t="n">
-        <v>31.89</v>
+        <v>31.86</v>
       </c>
       <c r="D36" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="E36" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H36" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="J36" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="K36" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="L36" t="n">
-        <v>31.84</v>
+        <v>31.83</v>
       </c>
       <c r="M36" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="N36" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O36" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3543,18 +3539,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3569,57 +3565,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="C37" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="D37" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="E37" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="H37" t="n">
         <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>31.65</v>
+        <v>31.66</v>
       </c>
       <c r="J37" t="n">
         <v>31.72</v>
       </c>
       <c r="K37" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="L37" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="M37" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="N37" t="n">
-        <v>31.96</v>
+        <v>31.93</v>
       </c>
       <c r="O37" t="n">
-        <v>32.01</v>
+        <v>31.97</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,18 +3623,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3653,57 +3649,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="C38" t="n">
-        <v>31.91</v>
+        <v>31.88</v>
       </c>
       <c r="D38" t="n">
-        <v>31.81</v>
+        <v>31.77</v>
       </c>
       <c r="E38" t="n">
-        <v>31.81</v>
+        <v>31.84</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I38" t="n">
-        <v>31.66</v>
+        <v>31.7</v>
       </c>
       <c r="J38" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="K38" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="L38" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="M38" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="N38" t="n">
-        <v>31.93</v>
+        <v>31.89</v>
       </c>
       <c r="O38" t="n">
-        <v>31.97</v>
+        <v>32.01</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3714,9 +3710,9 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3737,76 +3733,80 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C39" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D39" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E39" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="J39" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="K39" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="L39" t="n">
         <v>31.84</v>
       </c>
-      <c r="C39" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="D39" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="E39" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I39" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J39" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="K39" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="L39" t="n">
-        <v>31.83</v>
-      </c>
       <c r="M39" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="N39" t="n">
-        <v>31.89</v>
+        <v>31.96</v>
       </c>
       <c r="O39" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.99</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3821,71 +3821,69 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.81</v>
+        <v>31.66</v>
       </c>
       <c r="C40" t="n">
-        <v>31.81</v>
+        <v>31.67</v>
       </c>
       <c r="D40" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="E40" t="n">
         <v>31.66</v>
       </c>
-      <c r="E40" t="n">
-        <v>31.81</v>
-      </c>
       <c r="F40" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0046</v>
       </c>
       <c r="H40" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="I40" t="n">
-        <v>31.66</v>
+        <v>31.5</v>
       </c>
       <c r="J40" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="K40" t="n">
-        <v>31.79</v>
+        <v>31.73</v>
       </c>
       <c r="L40" t="n">
-        <v>31.84</v>
+        <v>31.77</v>
       </c>
       <c r="M40" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="N40" t="n">
-        <v>31.96</v>
+        <v>32</v>
       </c>
       <c r="O40" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.97</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3902,85 +3900,79 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="C41" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="D41" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="E41" t="n">
-        <v>31.66</v>
+        <v>31.63</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="H41" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I41" t="n">
-        <v>31.5</v>
+        <v>31.44</v>
       </c>
       <c r="J41" t="n">
-        <v>31.69</v>
+        <v>31.57</v>
       </c>
       <c r="K41" t="n">
-        <v>31.73</v>
+        <v>31.6</v>
       </c>
       <c r="L41" t="n">
-        <v>31.77</v>
+        <v>31.64</v>
       </c>
       <c r="M41" t="n">
-        <v>31.88</v>
+        <v>31.72</v>
       </c>
       <c r="N41" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="O41" t="n">
-        <v>31.97</v>
+        <v>31.78</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3993,55 +3985,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.63</v>
+        <v>31.68</v>
       </c>
       <c r="C42" t="n">
         <v>31.73</v>
       </c>
       <c r="D42" t="n">
-        <v>31.61</v>
+        <v>31.59</v>
       </c>
       <c r="E42" t="n">
-        <v>31.63</v>
+        <v>31.69</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="H42" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>31.44</v>
+        <v>31.49</v>
       </c>
       <c r="J42" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K42" t="n">
         <v>31.57</v>
       </c>
-      <c r="K42" t="n">
-        <v>31.6</v>
-      </c>
       <c r="L42" t="n">
-        <v>31.64</v>
+        <v>31.65</v>
       </c>
       <c r="M42" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="N42" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="O42" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4052,18 +4048,20 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4075,57 +4073,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="C43" t="n">
-        <v>31.73</v>
+        <v>31.8</v>
       </c>
       <c r="D43" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="E43" t="n">
-        <v>31.69</v>
+        <v>31.67</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0004</v>
       </c>
       <c r="H43" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I43" t="n">
-        <v>31.49</v>
+        <v>31.45</v>
       </c>
       <c r="J43" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="K43" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L43" t="n">
-        <v>31.65</v>
+        <v>31.67</v>
       </c>
       <c r="M43" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="N43" t="n">
-        <v>31.73</v>
+        <v>31.84</v>
       </c>
       <c r="O43" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4138,18 +4136,16 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4161,57 +4157,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.67</v>
+        <v>31.72</v>
       </c>
       <c r="C44" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="D44" t="n">
-        <v>31.67</v>
+        <v>31.65</v>
       </c>
       <c r="E44" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I44" t="n">
-        <v>31.45</v>
+        <v>31.54</v>
       </c>
       <c r="J44" t="n">
-        <v>31.57</v>
+        <v>31.52</v>
       </c>
       <c r="K44" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="L44" t="n">
-        <v>31.67</v>
+        <v>31.7</v>
       </c>
       <c r="M44" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="N44" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
       <c r="O44" t="n">
-        <v>31.86</v>
+        <v>31.93</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4224,12 +4220,12 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4245,76 +4241,78 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="C45" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D45" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E45" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="J45" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="K45" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="L45" t="n">
         <v>31.72</v>
       </c>
-      <c r="C45" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="D45" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="E45" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I45" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="J45" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="K45" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="L45" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M45" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="N45" t="n">
-        <v>31.78</v>
+        <v>31.86</v>
       </c>
       <c r="O45" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4327,59 +4325,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="C46" t="n">
-        <v>31.74</v>
+        <v>31.64</v>
       </c>
       <c r="D46" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="E46" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0023</v>
       </c>
       <c r="H46" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I46" t="n">
-        <v>31.53</v>
+        <v>31.43</v>
       </c>
       <c r="J46" t="n">
-        <v>31.61</v>
+        <v>31.56</v>
       </c>
       <c r="K46" t="n">
-        <v>31.66</v>
+        <v>31.62</v>
       </c>
       <c r="L46" t="n">
-        <v>31.72</v>
+        <v>31.68</v>
       </c>
       <c r="M46" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="N46" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="O46" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4391,12 +4385,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4418,62 +4412,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="C47" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="D47" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="E47" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J47" t="n">
         <v>31.49</v>
       </c>
-      <c r="E47" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I47" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31.56</v>
-      </c>
       <c r="K47" t="n">
-        <v>31.62</v>
+        <v>31.54</v>
       </c>
       <c r="L47" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M47" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
       <c r="N47" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="O47" t="n">
-        <v>31.89</v>
+        <v>31.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4500,67 +4494,65 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>31.5</v>
       </c>
       <c r="C48" t="n">
-        <v>31.55</v>
+        <v>31.5</v>
       </c>
       <c r="D48" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="E48" t="n">
         <v>31.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0002</v>
       </c>
       <c r="H48" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I48" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="J48" t="n">
-        <v>31.49</v>
+        <v>31.39</v>
       </c>
       <c r="K48" t="n">
-        <v>31.54</v>
+        <v>31.44</v>
       </c>
       <c r="L48" t="n">
-        <v>31.59</v>
+        <v>31.5</v>
       </c>
       <c r="M48" t="n">
-        <v>31.7</v>
+        <v>31.56</v>
       </c>
       <c r="N48" t="n">
-        <v>31.8</v>
+        <v>31.63</v>
       </c>
       <c r="O48" t="n">
-        <v>31.8</v>
+        <v>31.67</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4582,50 +4574,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.5</v>
+        <v>31.47</v>
       </c>
       <c r="C49" t="n">
-        <v>31.5</v>
+        <v>31.69</v>
       </c>
       <c r="D49" t="n">
-        <v>31.42</v>
+        <v>31.45</v>
       </c>
       <c r="E49" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="I49" t="n">
-        <v>31.31</v>
+        <v>31.33</v>
       </c>
       <c r="J49" t="n">
-        <v>31.39</v>
+        <v>31.43</v>
       </c>
       <c r="K49" t="n">
-        <v>31.44</v>
+        <v>31.46</v>
       </c>
       <c r="L49" t="n">
-        <v>31.5</v>
+        <v>31.48</v>
       </c>
       <c r="M49" t="n">
-        <v>31.56</v>
+        <v>31.54</v>
       </c>
       <c r="N49" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="O49" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,77 +4627,87 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.47</v>
+        <v>31.64</v>
       </c>
       <c r="C50" t="n">
         <v>31.69</v>
       </c>
       <c r="D50" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="E50" t="n">
-        <v>31.46</v>
+        <v>31.64</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0054</v>
       </c>
       <c r="H50" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="I50" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="J50" t="n">
-        <v>31.43</v>
+        <v>31.17</v>
       </c>
       <c r="K50" t="n">
-        <v>31.46</v>
+        <v>31.34</v>
       </c>
       <c r="L50" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="M50" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="N50" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="O50" t="n">
-        <v>31.59</v>
+        <v>31.94</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,30 +4715,26 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
@@ -4752,50 +4750,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="C51" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="J51" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="K51" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="L51" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="M51" t="n">
         <v>31.69</v>
       </c>
-      <c r="D51" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="E51" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I51" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="J51" t="n">
-        <v>31.17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="L51" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="M51" t="n">
-        <v>31.58</v>
-      </c>
       <c r="N51" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="O51" t="n">
-        <v>31.94</v>
+        <v>31.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4813,16 +4811,18 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4831,27 +4831,27 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="C52" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D52" t="n">
-        <v>31.61</v>
+        <v>31.69</v>
       </c>
       <c r="E52" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F52" t="n">
         <v>0.04</v>
@@ -4860,28 +4860,28 @@
         <v>0.0013</v>
       </c>
       <c r="H52" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I52" t="n">
-        <v>31.46</v>
+        <v>31.35</v>
       </c>
       <c r="J52" t="n">
-        <v>31.52</v>
+        <v>31.38</v>
       </c>
       <c r="K52" t="n">
-        <v>31.58</v>
+        <v>31.55</v>
       </c>
       <c r="L52" t="n">
-        <v>31.63</v>
+        <v>31.71</v>
       </c>
       <c r="M52" t="n">
-        <v>31.69</v>
+        <v>31.81</v>
       </c>
       <c r="N52" t="n">
-        <v>31.75</v>
+        <v>31.9</v>
       </c>
       <c r="O52" t="n">
-        <v>31.8</v>
+        <v>32.13</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="inlineStr">
@@ -4907,10 +4907,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4926,47 +4924,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D53" t="n">
         <v>31.72</v>
       </c>
-      <c r="C53" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D53" t="n">
-        <v>31.69</v>
-      </c>
       <c r="E53" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F53" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="H53" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="I53" t="n">
-        <v>31.35</v>
+        <v>31.47</v>
       </c>
       <c r="J53" t="n">
-        <v>31.38</v>
+        <v>31.46</v>
       </c>
       <c r="K53" t="n">
-        <v>31.55</v>
+        <v>31.61</v>
       </c>
       <c r="L53" t="n">
-        <v>31.71</v>
+        <v>31.76</v>
       </c>
       <c r="M53" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="N53" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="O53" t="n">
         <v>32.13</v>
@@ -5005,57 +5003,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.76</v>
+        <v>31.86</v>
       </c>
       <c r="C54" t="n">
-        <v>31.9</v>
+        <v>31.94</v>
       </c>
       <c r="D54" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="E54" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="H54" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="I54" t="n">
-        <v>31.47</v>
+        <v>31.55</v>
       </c>
       <c r="J54" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="K54" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="L54" t="n">
-        <v>31.76</v>
+        <v>31.79</v>
       </c>
       <c r="M54" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="N54" t="n">
-        <v>31.89</v>
+        <v>31.93</v>
       </c>
       <c r="O54" t="n">
-        <v>32.13</v>
+        <v>32.08</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5068,12 +5066,12 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
@@ -5091,57 +5089,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="C55" t="n">
-        <v>31.94</v>
+        <v>31.85</v>
       </c>
       <c r="D55" t="n">
-        <v>31.83</v>
+        <v>31.76</v>
       </c>
       <c r="E55" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="F55" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H55" t="n">
         <v>0.09</v>
       </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.11</v>
-      </c>
       <c r="I55" t="n">
-        <v>31.55</v>
+        <v>31.72</v>
       </c>
       <c r="J55" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K55" t="n">
-        <v>31.68</v>
+        <v>31.8</v>
       </c>
       <c r="L55" t="n">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="M55" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="N55" t="n">
-        <v>31.93</v>
+        <v>31.96</v>
       </c>
       <c r="O55" t="n">
-        <v>32.08</v>
+        <v>32.05</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5149,23 +5147,21 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5175,74 +5171,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="C56" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="D56" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="E56" t="n">
-        <v>31.85</v>
+        <v>31.81</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H56" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="I56" t="n">
-        <v>31.72</v>
+        <v>31.67</v>
       </c>
       <c r="J56" t="n">
-        <v>31.74</v>
+        <v>31.78</v>
       </c>
       <c r="K56" t="n">
-        <v>31.8</v>
+        <v>31.81</v>
       </c>
       <c r="L56" t="n">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="M56" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="N56" t="n">
         <v>31.96</v>
       </c>
       <c r="O56" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5259,55 +5253,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="C57" t="n">
-        <v>31.86</v>
+        <v>31.74</v>
       </c>
       <c r="D57" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E57" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0022</v>
       </c>
       <c r="H57" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I57" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J57" t="n">
         <v>31.67</v>
       </c>
-      <c r="J57" t="n">
-        <v>31.78</v>
-      </c>
       <c r="K57" t="n">
-        <v>31.81</v>
+        <v>31.73</v>
       </c>
       <c r="L57" t="n">
-        <v>31.83</v>
+        <v>31.79</v>
       </c>
       <c r="M57" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="N57" t="n">
-        <v>31.96</v>
+        <v>31.98</v>
       </c>
       <c r="O57" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5341,67 +5339,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="C58" t="n">
-        <v>31.74</v>
+        <v>31.79</v>
       </c>
       <c r="D58" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="E58" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0019</v>
       </c>
       <c r="H58" t="n">
         <v>0.15</v>
       </c>
       <c r="I58" t="n">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="J58" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K58" t="n">
         <v>31.67</v>
       </c>
-      <c r="K58" t="n">
-        <v>31.73</v>
-      </c>
       <c r="L58" t="n">
-        <v>31.79</v>
+        <v>31.7</v>
       </c>
       <c r="M58" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="N58" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="O58" t="n">
         <v>31.89</v>
       </c>
-      <c r="N58" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="O58" t="n">
-        <v>32.01</v>
-      </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5427,55 +5419,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="C59" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="D59" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E59" t="n">
         <v>31.79</v>
       </c>
-      <c r="D59" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="E59" t="n">
-        <v>31.68</v>
-      </c>
       <c r="F59" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0035</v>
       </c>
       <c r="H59" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I59" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="J59" t="n">
-        <v>31.63</v>
+        <v>31.51</v>
       </c>
       <c r="K59" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="L59" t="n">
         <v>31.7</v>
       </c>
       <c r="M59" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="N59" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="O59" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5483,22 +5479,24 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5509,57 +5507,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C60" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="E60" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I60" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K60" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="L60" t="n">
         <v>31.79</v>
       </c>
-      <c r="C60" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D60" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="E60" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I60" t="n">
-        <v>31.48</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="K60" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L60" t="n">
-        <v>31.7</v>
-      </c>
       <c r="M60" t="n">
-        <v>31.76</v>
+        <v>31.85</v>
       </c>
       <c r="N60" t="n">
-        <v>31.82</v>
+        <v>31.92</v>
       </c>
       <c r="O60" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5567,23 +5565,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5595,57 +5591,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C61" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
       <c r="D61" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="J61" t="n">
         <v>31.71</v>
       </c>
-      <c r="E61" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I61" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J61" t="n">
-        <v>31.65</v>
-      </c>
       <c r="K61" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="L61" t="n">
         <v>31.79</v>
       </c>
       <c r="M61" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="N61" t="n">
-        <v>31.92</v>
+        <v>31.95</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>31.95</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5658,9 +5654,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5686,50 +5682,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>31.78</v>
       </c>
       <c r="C62" t="n">
-        <v>31.82</v>
+        <v>31.9</v>
       </c>
       <c r="D62" t="n">
-        <v>31.73</v>
+        <v>31.77</v>
       </c>
       <c r="E62" t="n">
         <v>31.78</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I62" t="n">
-        <v>31.59</v>
+        <v>31.64</v>
       </c>
       <c r="J62" t="n">
-        <v>31.71</v>
+        <v>31.69</v>
       </c>
       <c r="K62" t="n">
-        <v>31.75</v>
+        <v>31.73</v>
       </c>
       <c r="L62" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="M62" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N62" t="n">
         <v>31.87</v>
       </c>
-      <c r="N62" t="n">
-        <v>31.95</v>
-      </c>
       <c r="O62" t="n">
-        <v>31.95</v>
+        <v>31.91</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5737,21 +5733,23 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5763,57 +5761,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="C63" t="n">
         <v>31.9</v>
       </c>
       <c r="D63" t="n">
-        <v>31.77</v>
+        <v>31.82</v>
       </c>
       <c r="E63" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="H63" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>31.64</v>
       </c>
       <c r="J63" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="K63" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="L63" t="n">
-        <v>31.78</v>
+        <v>31.81</v>
       </c>
       <c r="M63" t="n">
-        <v>31.82</v>
+        <v>31.85</v>
       </c>
       <c r="N63" t="n">
-        <v>31.87</v>
+        <v>31.89</v>
       </c>
       <c r="O63" t="n">
-        <v>31.91</v>
+        <v>32.04</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5826,12 +5824,12 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U63" s="8" t="inlineStr">
@@ -5849,57 +5847,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="C64" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D64" t="n">
         <v>31.85</v>
       </c>
-      <c r="C64" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="D64" t="n">
-        <v>31.82</v>
-      </c>
       <c r="E64" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I64" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="J64" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="K64" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="L64" t="n">
         <v>31.85</v>
       </c>
-      <c r="F64" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="J64" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="K64" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="L64" t="n">
-        <v>31.81</v>
-      </c>
       <c r="M64" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="N64" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="O64" t="n">
-        <v>32.04</v>
+        <v>31.97</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5912,12 +5910,12 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -5925,8 +5923,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V64" s="8" t="n">
-        <v/>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W64" s="11" t="inlineStr">
         <is>
@@ -5935,27 +5935,27 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.87</v>
+        <v>31.88</v>
       </c>
       <c r="C65" t="n">
-        <v>32.07</v>
+        <v>31.95</v>
       </c>
       <c r="D65" t="n">
-        <v>31.85</v>
+        <v>31.76</v>
       </c>
       <c r="E65" t="n">
-        <v>31.87</v>
+        <v>31.89</v>
       </c>
       <c r="F65" t="n">
         <v>0.02</v>
@@ -5964,28 +5964,28 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I65" t="n">
-        <v>31.75</v>
+        <v>31.63</v>
       </c>
       <c r="J65" t="n">
-        <v>31.77</v>
+        <v>31.6</v>
       </c>
       <c r="K65" t="n">
-        <v>31.81</v>
+        <v>31.76</v>
       </c>
       <c r="L65" t="n">
-        <v>31.85</v>
+        <v>31.91</v>
       </c>
       <c r="M65" t="n">
-        <v>31.89</v>
+        <v>31.98</v>
       </c>
       <c r="N65" t="n">
-        <v>31.92</v>
+        <v>32.04</v>
       </c>
       <c r="O65" t="n">
-        <v>31.97</v>
+        <v>32.29</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5996,25 +5996,19 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="11" t="inlineStr">
         <is>
@@ -6023,7 +6017,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_daily.xlsx
+++ b/three_gate/analysis/USDTWD_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="C2" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="E2" t="n">
-        <v>32.05</v>
+        <v>32.14</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>31.71</v>
+        <v>31.85</v>
       </c>
       <c r="J2" t="n">
-        <v>31.67</v>
+        <v>31.89</v>
       </c>
       <c r="K2" t="n">
-        <v>31.82</v>
+        <v>31.98</v>
       </c>
       <c r="L2" t="n">
-        <v>31.97</v>
+        <v>32.07</v>
       </c>
       <c r="M2" t="n">
-        <v>32.03</v>
+        <v>32.13</v>
       </c>
       <c r="N2" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="O2" t="n">
-        <v>32.33</v>
+        <v>32.31</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -698,10 +700,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="C3" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="D3" t="n">
-        <v>31.96</v>
+        <v>32.04</v>
       </c>
       <c r="E3" t="n">
-        <v>32.14</v>
+        <v>32.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="I3" t="n">
-        <v>31.85</v>
+        <v>31.73</v>
       </c>
       <c r="J3" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="K3" t="n">
-        <v>31.98</v>
+        <v>32.02</v>
       </c>
       <c r="L3" t="n">
-        <v>32.07</v>
+        <v>32.1</v>
       </c>
       <c r="M3" t="n">
-        <v>32.13</v>
+        <v>32.25</v>
       </c>
       <c r="N3" t="n">
-        <v>32.19</v>
+        <v>32.39</v>
       </c>
       <c r="O3" t="n">
-        <v>32.31</v>
+        <v>32.41</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,20 +771,16 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -802,47 +802,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="C4" t="n">
-        <v>32.23</v>
+        <v>32.18</v>
       </c>
       <c r="D4" t="n">
         <v>32.04</v>
       </c>
       <c r="E4" t="n">
-        <v>32.11</v>
+        <v>32.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="I4" t="n">
-        <v>31.73</v>
+        <v>31.85</v>
       </c>
       <c r="J4" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="K4" t="n">
         <v>32.02</v>
       </c>
       <c r="L4" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="M4" t="n">
-        <v>32.25</v>
+        <v>32.2</v>
       </c>
       <c r="N4" t="n">
-        <v>32.39</v>
+        <v>32.28</v>
       </c>
       <c r="O4" t="n">
         <v>32.41</v>
@@ -856,9 +856,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -877,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>32.1</v>
       </c>
       <c r="C5" t="n">
-        <v>32.18</v>
+        <v>32.17</v>
       </c>
       <c r="D5" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="E5" t="n">
         <v>32.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H5" t="n">
         <v>0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="J5" t="n">
-        <v>31.91</v>
+        <v>31.95</v>
       </c>
       <c r="K5" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="L5" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="M5" t="n">
-        <v>32.2</v>
+        <v>32.17</v>
       </c>
       <c r="N5" t="n">
-        <v>32.28</v>
+        <v>32.23</v>
       </c>
       <c r="O5" t="n">
-        <v>32.41</v>
+        <v>32.32</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,8 +943,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -959,42 +961,42 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="C6" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
       <c r="D6" t="n">
-        <v>32.03</v>
+        <v>32.06</v>
       </c>
       <c r="E6" t="n">
-        <v>32.1</v>
+        <v>32.16</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
         <v>31.9</v>
       </c>
       <c r="J6" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="K6" t="n">
         <v>32.03</v>
@@ -1009,7 +1011,7 @@
         <v>32.23</v>
       </c>
       <c r="O6" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,14 +1022,14 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1041,59 +1043,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="C7" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
       <c r="D7" t="n">
-        <v>32.06</v>
+        <v>32.11</v>
       </c>
       <c r="E7" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I7" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="J7" t="n">
-        <v>31.96</v>
+        <v>32.02</v>
       </c>
       <c r="K7" t="n">
-        <v>32.03</v>
+        <v>32.08</v>
       </c>
       <c r="L7" t="n">
-        <v>32.1</v>
+        <v>32.15</v>
       </c>
       <c r="M7" t="n">
-        <v>32.17</v>
+        <v>32.24</v>
       </c>
       <c r="N7" t="n">
-        <v>32.23</v>
+        <v>32.33</v>
       </c>
       <c r="O7" t="n">
-        <v>32.31</v>
+        <v>32.37</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,15 +1102,13 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1125,55 +1121,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="C8" t="n">
-        <v>32.23</v>
+        <v>32.27</v>
       </c>
       <c r="D8" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
       <c r="E8" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0024</v>
       </c>
       <c r="H8" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>31.91</v>
+        <v>31.99</v>
       </c>
       <c r="J8" t="n">
-        <v>32.02</v>
+        <v>31.99</v>
       </c>
       <c r="K8" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="L8" t="n">
         <v>32.15</v>
       </c>
       <c r="M8" t="n">
-        <v>32.24</v>
+        <v>32.19</v>
       </c>
       <c r="N8" t="n">
-        <v>32.33</v>
+        <v>32.23</v>
       </c>
       <c r="O8" t="n">
-        <v>32.37</v>
+        <v>32.35</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,16 +1184,20 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1203,59 +1207,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="C9" t="n">
-        <v>32.27</v>
+        <v>32.42</v>
       </c>
       <c r="D9" t="n">
-        <v>32.12</v>
+        <v>32.23</v>
       </c>
       <c r="E9" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0017</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I9" t="n">
-        <v>31.99</v>
+        <v>31.97</v>
       </c>
       <c r="J9" t="n">
-        <v>31.99</v>
+        <v>32.07</v>
       </c>
       <c r="K9" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="L9" t="n">
-        <v>32.15</v>
+        <v>32.2</v>
       </c>
       <c r="M9" t="n">
-        <v>32.19</v>
+        <v>32.29</v>
       </c>
       <c r="N9" t="n">
-        <v>32.23</v>
+        <v>32.37</v>
       </c>
       <c r="O9" t="n">
-        <v>32.35</v>
+        <v>32.42</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1294,50 +1294,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D10" t="n">
         <v>32.26</v>
       </c>
-      <c r="C10" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D10" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E10" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="F10" t="n">
         <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I10" t="n">
-        <v>31.97</v>
+        <v>32.04</v>
       </c>
       <c r="J10" t="n">
-        <v>32.07</v>
+        <v>32.04</v>
       </c>
       <c r="K10" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="L10" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M10" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="N10" t="n">
-        <v>32.37</v>
+        <v>32.42</v>
       </c>
       <c r="O10" t="n">
-        <v>32.42</v>
+        <v>32.61</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -1376,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="C11" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="D11" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="E11" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0011</v>
       </c>
       <c r="H11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>32.04</v>
+        <v>32.09</v>
       </c>
       <c r="J11" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="K11" t="n">
-        <v>32.17</v>
+        <v>32.23</v>
       </c>
       <c r="L11" t="n">
-        <v>32.3</v>
+        <v>32.33</v>
       </c>
       <c r="M11" t="n">
-        <v>32.36</v>
+        <v>32.4</v>
       </c>
       <c r="N11" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="O11" t="n">
-        <v>32.61</v>
+        <v>32.6</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1427,23 +1427,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1453,34 +1451,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D12" t="n">
         <v>32.28</v>
       </c>
-      <c r="C12" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="D12" t="n">
-        <v>32.23</v>
-      </c>
       <c r="E12" t="n">
-        <v>32.28</v>
+        <v>32.33</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0015</v>
       </c>
       <c r="H12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
         <v>32.09</v>
@@ -1489,19 +1491,19 @@
         <v>32.12</v>
       </c>
       <c r="K12" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="L12" t="n">
-        <v>32.33</v>
+        <v>32.29</v>
       </c>
       <c r="M12" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="N12" t="n">
         <v>32.4</v>
       </c>
-      <c r="N12" t="n">
-        <v>32.47</v>
-      </c>
       <c r="O12" t="n">
-        <v>32.6</v>
+        <v>32.51</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1509,21 +1511,23 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1533,59 +1537,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="C13" t="n">
-        <v>32.49</v>
+        <v>32.38</v>
       </c>
       <c r="D13" t="n">
-        <v>32.28</v>
+        <v>32.24</v>
       </c>
       <c r="E13" t="n">
-        <v>32.33</v>
+        <v>32.38</v>
       </c>
       <c r="F13" t="n">
         <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="J13" t="n">
         <v>32.09</v>
       </c>
-      <c r="J13" t="n">
-        <v>32.12</v>
-      </c>
       <c r="K13" t="n">
-        <v>32.21</v>
+        <v>32.22</v>
       </c>
       <c r="L13" t="n">
-        <v>32.29</v>
+        <v>32.36</v>
       </c>
       <c r="M13" t="n">
-        <v>32.35</v>
+        <v>32.43</v>
       </c>
       <c r="N13" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="O13" t="n">
-        <v>32.51</v>
+        <v>32.69</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1598,18 +1598,14 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1619,55 +1615,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="C14" t="n">
         <v>32.38</v>
       </c>
       <c r="D14" t="n">
-        <v>32.24</v>
+        <v>32.29</v>
       </c>
       <c r="E14" t="n">
-        <v>32.38</v>
+        <v>32.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="I14" t="n">
-        <v>32.08</v>
+        <v>32.11</v>
       </c>
       <c r="J14" t="n">
-        <v>32.09</v>
+        <v>32.28</v>
       </c>
       <c r="K14" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="L14" t="n">
-        <v>32.36</v>
+        <v>32.34</v>
       </c>
       <c r="M14" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="N14" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="O14" t="n">
-        <v>32.69</v>
+        <v>32.52</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1675,12 +1675,14 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1699,57 +1701,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="C15" t="n">
-        <v>32.38</v>
+        <v>32.4</v>
       </c>
       <c r="D15" t="n">
-        <v>32.29</v>
+        <v>32.28</v>
       </c>
       <c r="E15" t="n">
-        <v>32.3</v>
+        <v>32.32</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I15" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="J15" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="K15" t="n">
-        <v>32.31</v>
+        <v>32.25</v>
       </c>
       <c r="L15" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="M15" t="n">
         <v>32.34</v>
       </c>
-      <c r="M15" t="n">
-        <v>32.45</v>
-      </c>
       <c r="N15" t="n">
-        <v>32.55</v>
+        <v>32.37</v>
       </c>
       <c r="O15" t="n">
-        <v>32.52</v>
+        <v>32.47</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1757,21 +1759,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1790,50 +1794,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="C16" t="n">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="D16" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="E16" t="n">
-        <v>32.32</v>
+        <v>32.3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="n">
-        <v>32.21</v>
+        <v>32.16</v>
       </c>
       <c r="J16" t="n">
         <v>32.19</v>
       </c>
       <c r="K16" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="L16" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="M16" t="n">
-        <v>32.34</v>
+        <v>32.38</v>
       </c>
       <c r="N16" t="n">
-        <v>32.37</v>
+        <v>32.43</v>
       </c>
       <c r="O16" t="n">
-        <v>32.47</v>
+        <v>32.53</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1844,9 +1848,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1854,10 +1858,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1876,50 +1878,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="C17" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="D17" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="E17" t="n">
-        <v>32.3</v>
+        <v>32.36</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
         <v>32.16</v>
       </c>
       <c r="J17" t="n">
-        <v>32.19</v>
+        <v>32.13</v>
       </c>
       <c r="K17" t="n">
-        <v>32.26</v>
+        <v>32.23</v>
       </c>
       <c r="L17" t="n">
         <v>32.33</v>
       </c>
       <c r="M17" t="n">
-        <v>32.38</v>
+        <v>32.37</v>
       </c>
       <c r="N17" t="n">
-        <v>32.43</v>
+        <v>32.41</v>
       </c>
       <c r="O17" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1930,18 +1932,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1951,59 +1955,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="C18" t="n">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="D18" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
       <c r="E18" t="n">
-        <v>32.36</v>
+        <v>32.35</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0005</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I18" t="n">
-        <v>32.16</v>
+        <v>32.21</v>
       </c>
       <c r="J18" t="n">
-        <v>32.13</v>
+        <v>32.17</v>
       </c>
       <c r="K18" t="n">
-        <v>32.23</v>
+        <v>32.29</v>
       </c>
       <c r="L18" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="M18" t="n">
-        <v>32.37</v>
+        <v>32.44</v>
       </c>
       <c r="N18" t="n">
-        <v>32.41</v>
+        <v>32.48</v>
       </c>
       <c r="O18" t="n">
-        <v>32.57</v>
+        <v>32.67</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,14 +2014,14 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -2037,55 +2037,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="C19" t="n">
-        <v>32.55</v>
+        <v>32.48</v>
       </c>
       <c r="D19" t="n">
-        <v>32.32</v>
+        <v>32.21</v>
       </c>
       <c r="E19" t="n">
-        <v>32.35</v>
+        <v>32.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I19" t="n">
-        <v>32.21</v>
+        <v>32.09</v>
       </c>
       <c r="J19" t="n">
-        <v>32.17</v>
+        <v>32.07</v>
       </c>
       <c r="K19" t="n">
-        <v>32.29</v>
+        <v>32.23</v>
       </c>
       <c r="L19" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="M19" t="n">
-        <v>32.44</v>
+        <v>32.46</v>
       </c>
       <c r="N19" t="n">
-        <v>32.48</v>
+        <v>32.54</v>
       </c>
       <c r="O19" t="n">
-        <v>32.67</v>
+        <v>32.78</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2093,12 +2097,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2106,10 +2112,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2128,50 +2132,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="C20" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D20" t="n">
         <v>32.21</v>
       </c>
       <c r="E20" t="n">
-        <v>32.4</v>
+        <v>32.29</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0031</v>
       </c>
       <c r="H20" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I20" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="J20" t="n">
-        <v>32.07</v>
+        <v>32.15</v>
       </c>
       <c r="K20" t="n">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="L20" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="M20" t="n">
-        <v>32.46</v>
+        <v>32.53</v>
       </c>
       <c r="N20" t="n">
-        <v>32.54</v>
+        <v>32.69</v>
       </c>
       <c r="O20" t="n">
-        <v>32.78</v>
+        <v>32.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,18 +2185,16 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2207,57 +2209,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="C21" t="n">
-        <v>32.49</v>
+        <v>32.45</v>
       </c>
       <c r="D21" t="n">
-        <v>32.21</v>
+        <v>32.33</v>
       </c>
       <c r="E21" t="n">
-        <v>32.29</v>
+        <v>32.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I21" t="n">
         <v>31.93</v>
       </c>
       <c r="J21" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="K21" t="n">
         <v>32.15</v>
       </c>
-      <c r="K21" t="n">
-        <v>32.26</v>
-      </c>
       <c r="L21" t="n">
-        <v>32.37</v>
+        <v>32.32</v>
       </c>
       <c r="M21" t="n">
-        <v>32.53</v>
+        <v>32.43</v>
       </c>
       <c r="N21" t="n">
-        <v>32.69</v>
+        <v>32.54</v>
       </c>
       <c r="O21" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,18 +2267,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2298,69 +2300,73 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c